--- a/Auction Tracker v3 latest.xlsx
+++ b/Auction Tracker v3 latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\auction-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D71075F-4A1D-49CF-8F9C-46E65C4B406D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDDF0EC-7530-4F70-B78C-73736ACBE268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form responses 1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="212">
   <si>
     <t>Timestamp</t>
   </si>
@@ -671,6 +671,9 @@
   </si>
   <si>
     <t>Soumyajit Bhattacharjee</t>
+  </si>
+  <si>
+    <t>Susovan Roy</t>
   </si>
 </sst>
 </file>
@@ -917,7 +920,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1007,6 +1010,12 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1028,22 +1037,6 @@
           <bgColor rgb="FFB7E1CD"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1069,13 +1062,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF5B3F86"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF5B3F86"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF5B3F86"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF5B3F86"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Form responses 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="2"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3802,7 +3811,7 @@
         <v>25</v>
       </c>
       <c r="N2" s="22">
-        <f>IF(M2="Icon",20000000,IF(M2="Premium",10000000,IF(M2="Rising",5000000,IF(M2="Impact",2000000,0))))</f>
+        <f t="shared" ref="N2:N46" si="0">IF(M2="Icon",20000000,IF(M2="Premium",10000000,IF(M2="Rising",5000000,IF(M2="Impact",2000000,0))))</f>
         <v>5000000</v>
       </c>
     </row>
@@ -3848,7 +3857,7 @@
         <v>40</v>
       </c>
       <c r="N3" s="22">
-        <f>IF(M3="Icon",20000000,IF(M3="Premium",10000000,IF(M3="Rising",5000000,IF(M3="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>20000000</v>
       </c>
     </row>
@@ -3894,7 +3903,7 @@
         <v>29</v>
       </c>
       <c r="N4" s="22">
-        <f>IF(M4="Icon",20000000,IF(M4="Premium",10000000,IF(M4="Rising",5000000,IF(M4="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3940,7 +3949,7 @@
         <v>25</v>
       </c>
       <c r="N5" s="22">
-        <f>IF(M5="Icon",20000000,IF(M5="Premium",10000000,IF(M5="Rising",5000000,IF(M5="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
     </row>
@@ -3986,7 +3995,7 @@
         <v>25</v>
       </c>
       <c r="N6" s="22">
-        <f>IF(M6="Icon",20000000,IF(M6="Premium",10000000,IF(M6="Rising",5000000,IF(M6="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
     </row>
@@ -4032,7 +4041,7 @@
         <v>50</v>
       </c>
       <c r="N7" s="22">
-        <f>IF(M7="Icon",20000000,IF(M7="Premium",10000000,IF(M7="Rising",5000000,IF(M7="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
       <c r="O7" s="18"/>
@@ -4079,7 +4088,7 @@
         <v>50</v>
       </c>
       <c r="N8" s="22">
-        <f>IF(M8="Icon",20000000,IF(M8="Premium",10000000,IF(M8="Rising",5000000,IF(M8="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
       <c r="O8" s="18"/>
@@ -4126,7 +4135,7 @@
         <v>50</v>
       </c>
       <c r="N9" s="22">
-        <f>IF(M9="Icon",20000000,IF(M9="Premium",10000000,IF(M9="Rising",5000000,IF(M9="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
       <c r="O9" s="18"/>
@@ -4173,7 +4182,7 @@
         <v>25</v>
       </c>
       <c r="N10" s="22">
-        <f>IF(M10="Icon",20000000,IF(M10="Premium",10000000,IF(M10="Rising",5000000,IF(M10="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
       <c r="O10" s="23"/>
@@ -4220,7 +4229,7 @@
         <v>45</v>
       </c>
       <c r="N11" s="22">
-        <f>IF(M11="Icon",20000000,IF(M11="Premium",10000000,IF(M11="Rising",5000000,IF(M11="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>2000000</v>
       </c>
       <c r="O11" s="18"/>
@@ -4244,7 +4253,7 @@
         <v>45</v>
       </c>
       <c r="N12" s="22">
-        <f>IF(M12="Icon",20000000,IF(M12="Premium",10000000,IF(M12="Rising",5000000,IF(M12="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>2000000</v>
       </c>
       <c r="O12" s="18"/>
@@ -4291,7 +4300,7 @@
         <v>45</v>
       </c>
       <c r="N13" s="22">
-        <f>IF(M13="Icon",20000000,IF(M13="Premium",10000000,IF(M13="Rising",5000000,IF(M13="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>2000000</v>
       </c>
       <c r="O13" s="18"/>
@@ -4338,7 +4347,7 @@
         <v>40</v>
       </c>
       <c r="N14" s="22">
-        <f>IF(M14="Icon",20000000,IF(M14="Premium",10000000,IF(M14="Rising",5000000,IF(M14="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>20000000</v>
       </c>
     </row>
@@ -4384,7 +4393,7 @@
         <v>25</v>
       </c>
       <c r="N15" s="22">
-        <f>IF(M15="Icon",20000000,IF(M15="Premium",10000000,IF(M15="Rising",5000000,IF(M15="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
       <c r="O15" s="18"/>
@@ -4431,7 +4440,7 @@
         <v>50</v>
       </c>
       <c r="N16" s="22">
-        <f>IF(M16="Icon",20000000,IF(M16="Premium",10000000,IF(M16="Rising",5000000,IF(M16="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
       <c r="O16" s="18"/>
@@ -4478,7 +4487,7 @@
         <v>40</v>
       </c>
       <c r="N17" s="22">
-        <f>IF(M17="Icon",20000000,IF(M17="Premium",10000000,IF(M17="Rising",5000000,IF(M17="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>20000000</v>
       </c>
       <c r="O17" s="18"/>
@@ -4525,7 +4534,7 @@
         <v>25</v>
       </c>
       <c r="N18" s="22">
-        <f>IF(M18="Icon",20000000,IF(M18="Premium",10000000,IF(M18="Rising",5000000,IF(M18="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
       <c r="O18" s="23"/>
@@ -4572,7 +4581,7 @@
         <v>29</v>
       </c>
       <c r="N19" s="22">
-        <f>IF(M19="Icon",20000000,IF(M19="Premium",10000000,IF(M19="Rising",5000000,IF(M19="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O19" s="23"/>
@@ -4619,7 +4628,7 @@
         <v>25</v>
       </c>
       <c r="N20" s="22">
-        <f>IF(M20="Icon",20000000,IF(M20="Premium",10000000,IF(M20="Rising",5000000,IF(M20="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
       <c r="O20" s="23"/>
@@ -4666,7 +4675,7 @@
         <v>50</v>
       </c>
       <c r="N21" s="22">
-        <f>IF(M21="Icon",20000000,IF(M21="Premium",10000000,IF(M21="Rising",5000000,IF(M21="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
       <c r="O21" s="23"/>
@@ -4713,7 +4722,7 @@
         <v>40</v>
       </c>
       <c r="N22" s="22">
-        <f>IF(M22="Icon",20000000,IF(M22="Premium",10000000,IF(M22="Rising",5000000,IF(M22="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>20000000</v>
       </c>
       <c r="O22" s="18"/>
@@ -4760,7 +4769,7 @@
         <v>45</v>
       </c>
       <c r="N23" s="22">
-        <f>IF(M23="Icon",20000000,IF(M23="Premium",10000000,IF(M23="Rising",5000000,IF(M23="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>2000000</v>
       </c>
       <c r="O23" s="18"/>
@@ -4807,7 +4816,7 @@
         <v>50</v>
       </c>
       <c r="N24" s="22">
-        <f>IF(M24="Icon",20000000,IF(M24="Premium",10000000,IF(M24="Rising",5000000,IF(M24="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
       <c r="O24" s="18"/>
@@ -4854,7 +4863,7 @@
         <v>50</v>
       </c>
       <c r="N25" s="22">
-        <f>IF(M25="Icon",20000000,IF(M25="Premium",10000000,IF(M25="Rising",5000000,IF(M25="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
       <c r="O25" s="23"/>
@@ -4901,11 +4910,11 @@
         <v>25</v>
       </c>
       <c r="N26" s="22">
-        <f>IF(M26="Icon",20000000,IF(M26="Premium",10000000,IF(M26="Rising",5000000,IF(M26="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" ht="13.2">
       <c r="A27" s="19">
         <v>31751306</v>
       </c>
@@ -4941,12 +4950,12 @@
         <v>50</v>
       </c>
       <c r="N27" s="22">
-        <f>IF(M27="Icon",20000000,IF(M27="Premium",10000000,IF(M27="Rising",5000000,IF(M27="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
       <c r="O27" s="23"/>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" ht="13.2">
       <c r="A28" s="19">
         <v>30299329</v>
       </c>
@@ -4988,11 +4997,11 @@
         <v>45</v>
       </c>
       <c r="N28" s="22">
-        <f>IF(M28="Icon",20000000,IF(M28="Premium",10000000,IF(M28="Rising",5000000,IF(M28="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>2000000</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" ht="13.2">
       <c r="A29" s="19">
         <v>42598564</v>
       </c>
@@ -5034,11 +5043,11 @@
         <v>50</v>
       </c>
       <c r="N29" s="22">
-        <f>IF(M29="Icon",20000000,IF(M29="Premium",10000000,IF(M29="Rising",5000000,IF(M29="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" ht="13.2">
       <c r="A30" s="19">
         <v>28643694</v>
       </c>
@@ -5080,11 +5089,11 @@
         <v>25</v>
       </c>
       <c r="N30" s="22">
-        <f>IF(M30="Icon",20000000,IF(M30="Premium",10000000,IF(M30="Rising",5000000,IF(M30="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" ht="13.2">
       <c r="A31" s="19">
         <v>45002297</v>
       </c>
@@ -5126,11 +5135,11 @@
         <v>25</v>
       </c>
       <c r="N31" s="22">
-        <f>IF(M31="Icon",20000000,IF(M31="Premium",10000000,IF(M31="Rising",5000000,IF(M31="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" ht="13.2">
       <c r="A32" s="19">
         <v>36055152</v>
       </c>
@@ -5172,11 +5181,11 @@
         <v>45</v>
       </c>
       <c r="N32" s="22">
-        <f>IF(M32="Icon",20000000,IF(M32="Premium",10000000,IF(M32="Rising",5000000,IF(M32="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>2000000</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" ht="13.2">
       <c r="A33" s="19">
         <v>44011252</v>
       </c>
@@ -5218,11 +5227,11 @@
         <v>40</v>
       </c>
       <c r="N33" s="22">
-        <f>IF(M33="Icon",20000000,IF(M33="Premium",10000000,IF(M33="Rising",5000000,IF(M33="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>20000000</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" ht="13.2">
       <c r="A34" s="19">
         <v>8026613</v>
       </c>
@@ -5264,11 +5273,11 @@
         <v>45</v>
       </c>
       <c r="N34" s="22">
-        <f>IF(M34="Icon",20000000,IF(M34="Premium",10000000,IF(M34="Rising",5000000,IF(M34="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>2000000</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" ht="13.2">
       <c r="A35" s="19">
         <v>46477829</v>
       </c>
@@ -5310,11 +5319,11 @@
         <v>45</v>
       </c>
       <c r="N35" s="22">
-        <f>IF(M35="Icon",20000000,IF(M35="Premium",10000000,IF(M35="Rising",5000000,IF(M35="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>2000000</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" ht="13.2">
       <c r="A36" s="19">
         <v>7183132</v>
       </c>
@@ -5356,11 +5365,11 @@
         <v>50</v>
       </c>
       <c r="N36" s="22">
-        <f>IF(M36="Icon",20000000,IF(M36="Premium",10000000,IF(M36="Rising",5000000,IF(M36="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" ht="13.2">
       <c r="A37" s="19">
         <v>10967531</v>
       </c>
@@ -5402,11 +5411,11 @@
         <v>29</v>
       </c>
       <c r="N37" s="22">
-        <f>IF(M37="Icon",20000000,IF(M37="Premium",10000000,IF(M37="Rising",5000000,IF(M37="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" ht="13.2">
       <c r="A38" s="19">
         <v>47133527</v>
       </c>
@@ -5448,11 +5457,11 @@
         <v>25</v>
       </c>
       <c r="N38" s="22">
-        <f>IF(M38="Icon",20000000,IF(M38="Premium",10000000,IF(M38="Rising",5000000,IF(M38="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" ht="13.2">
       <c r="A39" s="19">
         <v>11616298</v>
       </c>
@@ -5494,11 +5503,11 @@
         <v>45</v>
       </c>
       <c r="N39" s="22">
-        <f>IF(M39="Icon",20000000,IF(M39="Premium",10000000,IF(M39="Rising",5000000,IF(M39="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>2000000</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" ht="13.2">
       <c r="A40" s="19">
         <v>33758093</v>
       </c>
@@ -5540,11 +5549,11 @@
         <v>50</v>
       </c>
       <c r="N40" s="22">
-        <f>IF(M40="Icon",20000000,IF(M40="Premium",10000000,IF(M40="Rising",5000000,IF(M40="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" ht="13.2">
       <c r="A41" s="19">
         <v>14374771</v>
       </c>
@@ -5586,11 +5595,11 @@
         <v>45</v>
       </c>
       <c r="N41" s="22">
-        <f>IF(M41="Icon",20000000,IF(M41="Premium",10000000,IF(M41="Rising",5000000,IF(M41="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>2000000</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" ht="13.2">
       <c r="A42" s="19">
         <v>4779842</v>
       </c>
@@ -5632,11 +5641,11 @@
         <v>40</v>
       </c>
       <c r="N42" s="22">
-        <f>IF(M42="Icon",20000000,IF(M42="Premium",10000000,IF(M42="Rising",5000000,IF(M42="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>20000000</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" ht="13.2">
       <c r="A43" s="19">
         <v>24512366</v>
       </c>
@@ -5678,11 +5687,11 @@
         <v>29</v>
       </c>
       <c r="N43" s="22">
-        <f>IF(M43="Icon",20000000,IF(M43="Premium",10000000,IF(M43="Rising",5000000,IF(M43="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" ht="13.2">
       <c r="A44" s="19">
         <v>22819671</v>
       </c>
@@ -5724,11 +5733,11 @@
         <v>25</v>
       </c>
       <c r="N44" s="22">
-        <f>IF(M44="Icon",20000000,IF(M44="Premium",10000000,IF(M44="Rising",5000000,IF(M44="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" ht="13.2">
       <c r="A45" s="19">
         <v>29988182</v>
       </c>
@@ -5770,11 +5779,11 @@
         <v>50</v>
       </c>
       <c r="N45" s="22">
-        <f>IF(M45="Icon",20000000,IF(M45="Premium",10000000,IF(M45="Rising",5000000,IF(M45="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" ht="13.2">
       <c r="A46" s="19">
         <v>10984519</v>
       </c>
@@ -5816,3815 +5825,3815 @@
         <v>40</v>
       </c>
       <c r="N46" s="22">
-        <f>IF(M46="Icon",20000000,IF(M46="Premium",10000000,IF(M46="Rising",5000000,IF(M46="Impact",2000000,0))))</f>
+        <f t="shared" si="0"/>
         <v>20000000</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" ht="13.2">
       <c r="A47" s="19"/>
       <c r="H47" s="20"/>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" ht="13.2">
       <c r="A48" s="19"/>
       <c r="H48" s="20"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" ht="13.2">
       <c r="A49" s="19"/>
       <c r="H49" s="20"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" ht="13.2">
       <c r="A50" s="19"/>
       <c r="H50" s="20"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" ht="13.2">
       <c r="A51" s="19"/>
       <c r="H51" s="20"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" ht="13.2">
       <c r="A52" s="19"/>
       <c r="H52" s="20"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" ht="13.2">
       <c r="A53" s="19"/>
       <c r="H53" s="20"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" ht="13.2">
       <c r="A54" s="19"/>
       <c r="H54" s="20"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" ht="13.2">
       <c r="A55" s="19"/>
       <c r="H55" s="20"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" ht="13.2">
       <c r="A56" s="19"/>
       <c r="H56" s="20"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" ht="13.2">
       <c r="A57" s="19"/>
       <c r="H57" s="20"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" ht="13.2">
       <c r="A58" s="19"/>
       <c r="H58" s="20"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" ht="13.2">
       <c r="A59" s="19"/>
       <c r="H59" s="20"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" ht="13.2">
       <c r="A60" s="19"/>
       <c r="H60" s="20"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" ht="13.2">
       <c r="A61" s="19"/>
       <c r="H61" s="20"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" ht="13.2">
       <c r="A62" s="19"/>
       <c r="H62" s="20"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" ht="13.2">
       <c r="A63" s="19"/>
       <c r="H63" s="20"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" ht="13.2">
       <c r="A64" s="19"/>
       <c r="H64" s="20"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" ht="13.2">
       <c r="A65" s="19"/>
       <c r="H65" s="20"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" ht="13.2">
       <c r="A66" s="19"/>
       <c r="H66" s="20"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" ht="13.2">
       <c r="A67" s="19"/>
       <c r="H67" s="20"/>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" ht="13.2">
       <c r="A68" s="19"/>
       <c r="H68" s="20"/>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" ht="13.2">
       <c r="A69" s="19"/>
       <c r="H69" s="20"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" ht="13.2">
       <c r="A70" s="19"/>
       <c r="H70" s="20"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" ht="13.2">
       <c r="A71" s="19"/>
       <c r="H71" s="20"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" ht="13.2">
       <c r="A72" s="19"/>
       <c r="H72" s="20"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" ht="13.2">
       <c r="A73" s="19"/>
       <c r="H73" s="20"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" ht="13.2">
       <c r="A74" s="19"/>
       <c r="H74" s="20"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" ht="13.2">
       <c r="A75" s="19"/>
       <c r="H75" s="20"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" ht="13.2">
       <c r="A76" s="19"/>
       <c r="H76" s="20"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" ht="13.2">
       <c r="A77" s="19"/>
       <c r="H77" s="20"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" ht="13.2">
       <c r="A78" s="19"/>
       <c r="H78" s="20"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" ht="13.2">
       <c r="A79" s="19"/>
       <c r="H79" s="20"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" ht="13.2">
       <c r="A80" s="19"/>
       <c r="H80" s="20"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" ht="13.2">
       <c r="A81" s="19"/>
       <c r="H81" s="20"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" ht="13.2">
       <c r="A82" s="19"/>
       <c r="H82" s="20"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" ht="13.2">
       <c r="A83" s="19"/>
       <c r="H83" s="20"/>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" ht="13.2">
       <c r="A84" s="19"/>
       <c r="H84" s="20"/>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" ht="13.2">
       <c r="A85" s="19"/>
       <c r="H85" s="20"/>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" ht="13.2">
       <c r="A86" s="19"/>
       <c r="H86" s="20"/>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" ht="13.2">
       <c r="A87" s="19"/>
       <c r="H87" s="20"/>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" ht="13.2">
       <c r="A88" s="19"/>
       <c r="H88" s="20"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" ht="13.2">
       <c r="A89" s="19"/>
       <c r="H89" s="20"/>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" ht="13.2">
       <c r="A90" s="19"/>
       <c r="H90" s="20"/>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" ht="13.2">
       <c r="A91" s="19"/>
       <c r="H91" s="20"/>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" ht="13.2">
       <c r="A92" s="19"/>
       <c r="H92" s="20"/>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" ht="13.2">
       <c r="A93" s="19"/>
       <c r="H93" s="20"/>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" ht="13.2">
       <c r="A94" s="19"/>
       <c r="H94" s="20"/>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" ht="13.2">
       <c r="A95" s="19"/>
       <c r="H95" s="20"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" ht="13.2">
       <c r="A96" s="19"/>
       <c r="H96" s="20"/>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" ht="13.2">
       <c r="A97" s="19"/>
       <c r="H97" s="20"/>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" ht="13.2">
       <c r="A98" s="19"/>
       <c r="H98" s="20"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" ht="13.2">
       <c r="A99" s="19"/>
       <c r="H99" s="20"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" ht="13.2">
       <c r="A100" s="19"/>
       <c r="H100" s="20"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" ht="13.2">
       <c r="A101" s="19"/>
       <c r="H101" s="20"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" ht="13.2">
       <c r="A102" s="19"/>
       <c r="H102" s="20"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" ht="13.2">
       <c r="A103" s="19"/>
       <c r="H103" s="20"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" ht="13.2">
       <c r="A104" s="19"/>
       <c r="H104" s="20"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" ht="13.2">
       <c r="A105" s="19"/>
       <c r="H105" s="20"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" ht="13.2">
       <c r="A106" s="19"/>
       <c r="H106" s="20"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" ht="13.2">
       <c r="A107" s="19"/>
       <c r="H107" s="20"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" ht="13.2">
       <c r="A108" s="19"/>
       <c r="H108" s="20"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" ht="13.2">
       <c r="A109" s="19"/>
       <c r="H109" s="20"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" ht="13.2">
       <c r="A110" s="19"/>
       <c r="H110" s="20"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" ht="13.2">
       <c r="A111" s="19"/>
       <c r="H111" s="20"/>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" ht="13.2">
       <c r="A112" s="19"/>
       <c r="H112" s="20"/>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" ht="13.2">
       <c r="A113" s="19"/>
       <c r="H113" s="20"/>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" ht="13.2">
       <c r="A114" s="19"/>
       <c r="H114" s="20"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" ht="13.2">
       <c r="A115" s="19"/>
       <c r="H115" s="20"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" ht="13.2">
       <c r="A116" s="19"/>
       <c r="H116" s="20"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" ht="13.2">
       <c r="A117" s="19"/>
       <c r="H117" s="20"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" ht="13.2">
       <c r="A118" s="19"/>
       <c r="H118" s="20"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" ht="13.2">
       <c r="A119" s="19"/>
       <c r="H119" s="20"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" ht="13.2">
       <c r="A120" s="19"/>
       <c r="H120" s="20"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" ht="13.2">
       <c r="A121" s="19"/>
       <c r="H121" s="20"/>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" ht="13.2">
       <c r="A122" s="19"/>
       <c r="H122" s="20"/>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" ht="13.2">
       <c r="A123" s="19"/>
       <c r="H123" s="20"/>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" ht="13.2">
       <c r="A124" s="19"/>
       <c r="H124" s="20"/>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" ht="13.2">
       <c r="A125" s="19"/>
       <c r="H125" s="20"/>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" ht="13.2">
       <c r="A126" s="19"/>
       <c r="H126" s="20"/>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" ht="13.2">
       <c r="A127" s="19"/>
       <c r="H127" s="20"/>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" ht="13.2">
       <c r="A128" s="19"/>
       <c r="H128" s="20"/>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" ht="13.2">
       <c r="A129" s="19"/>
       <c r="H129" s="20"/>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" ht="13.2">
       <c r="A130" s="19"/>
       <c r="H130" s="20"/>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" ht="13.2">
       <c r="A131" s="19"/>
       <c r="H131" s="20"/>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" ht="13.2">
       <c r="A132" s="19"/>
       <c r="H132" s="20"/>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" ht="13.2">
       <c r="A133" s="19"/>
       <c r="H133" s="20"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" ht="13.2">
       <c r="A134" s="19"/>
       <c r="H134" s="20"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" ht="13.2">
       <c r="A135" s="19"/>
       <c r="H135" s="20"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" ht="13.2">
       <c r="A136" s="19"/>
       <c r="H136" s="20"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" ht="13.2">
       <c r="A137" s="19"/>
       <c r="H137" s="20"/>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" ht="13.2">
       <c r="A138" s="19"/>
       <c r="H138" s="20"/>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" ht="13.2">
       <c r="A139" s="19"/>
       <c r="H139" s="20"/>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" ht="13.2">
       <c r="A140" s="19"/>
       <c r="H140" s="20"/>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" ht="13.2">
       <c r="A141" s="19"/>
       <c r="H141" s="20"/>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" ht="13.2">
       <c r="A142" s="19"/>
       <c r="H142" s="20"/>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" ht="13.2">
       <c r="A143" s="19"/>
       <c r="H143" s="20"/>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" ht="13.2">
       <c r="A144" s="19"/>
       <c r="H144" s="20"/>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" ht="13.2">
       <c r="A145" s="19"/>
       <c r="H145" s="20"/>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" ht="13.2">
       <c r="A146" s="19"/>
       <c r="H146" s="20"/>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" ht="13.2">
       <c r="A147" s="19"/>
       <c r="H147" s="20"/>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" ht="13.2">
       <c r="A148" s="19"/>
       <c r="H148" s="20"/>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" ht="13.2">
       <c r="A149" s="19"/>
       <c r="H149" s="20"/>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" ht="13.2">
       <c r="A150" s="19"/>
       <c r="H150" s="20"/>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" ht="13.2">
       <c r="A151" s="19"/>
       <c r="H151" s="20"/>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" ht="13.2">
       <c r="A152" s="19"/>
       <c r="H152" s="20"/>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" ht="13.2">
       <c r="A153" s="19"/>
       <c r="H153" s="20"/>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" ht="13.2">
       <c r="A154" s="19"/>
       <c r="H154" s="20"/>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" ht="13.2">
       <c r="A155" s="19"/>
       <c r="H155" s="20"/>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" ht="13.2">
       <c r="A156" s="19"/>
       <c r="H156" s="20"/>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" ht="13.2">
       <c r="A157" s="19"/>
       <c r="H157" s="20"/>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" ht="13.2">
       <c r="A158" s="19"/>
       <c r="H158" s="20"/>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" ht="13.2">
       <c r="A159" s="19"/>
       <c r="H159" s="20"/>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" ht="13.2">
       <c r="A160" s="19"/>
       <c r="H160" s="20"/>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" ht="13.2">
       <c r="A161" s="19"/>
       <c r="H161" s="20"/>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" ht="13.2">
       <c r="A162" s="19"/>
       <c r="H162" s="20"/>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" ht="13.2">
       <c r="A163" s="19"/>
       <c r="H163" s="20"/>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" ht="13.2">
       <c r="A164" s="19"/>
       <c r="H164" s="20"/>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" ht="13.2">
       <c r="A165" s="19"/>
       <c r="H165" s="20"/>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" ht="13.2">
       <c r="A166" s="19"/>
       <c r="H166" s="20"/>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" ht="13.2">
       <c r="A167" s="19"/>
       <c r="H167" s="20"/>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" ht="13.2">
       <c r="A168" s="19"/>
       <c r="H168" s="20"/>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" ht="13.2">
       <c r="A169" s="19"/>
       <c r="H169" s="20"/>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" ht="13.2">
       <c r="A170" s="19"/>
       <c r="H170" s="20"/>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" ht="13.2">
       <c r="A171" s="19"/>
       <c r="H171" s="20"/>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" ht="13.2">
       <c r="A172" s="19"/>
       <c r="H172" s="20"/>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" ht="13.2">
       <c r="A173" s="19"/>
       <c r="H173" s="20"/>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" ht="13.2">
       <c r="A174" s="19"/>
       <c r="H174" s="20"/>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" ht="13.2">
       <c r="A175" s="19"/>
       <c r="H175" s="20"/>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" ht="13.2">
       <c r="A176" s="19"/>
       <c r="H176" s="20"/>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" ht="13.2">
       <c r="A177" s="19"/>
       <c r="H177" s="20"/>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" ht="13.2">
       <c r="A178" s="19"/>
       <c r="H178" s="20"/>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" ht="13.2">
       <c r="A179" s="19"/>
       <c r="H179" s="20"/>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" ht="13.2">
       <c r="A180" s="19"/>
       <c r="H180" s="20"/>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" ht="13.2">
       <c r="A181" s="19"/>
       <c r="H181" s="20"/>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" ht="13.2">
       <c r="A182" s="19"/>
       <c r="H182" s="20"/>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" ht="13.2">
       <c r="A183" s="19"/>
       <c r="H183" s="20"/>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" ht="13.2">
       <c r="A184" s="19"/>
       <c r="H184" s="20"/>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" ht="13.2">
       <c r="A185" s="19"/>
       <c r="H185" s="20"/>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" ht="13.2">
       <c r="A186" s="19"/>
       <c r="H186" s="20"/>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" ht="13.2">
       <c r="A187" s="19"/>
       <c r="H187" s="20"/>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" ht="13.2">
       <c r="A188" s="19"/>
       <c r="H188" s="20"/>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" ht="13.2">
       <c r="A189" s="19"/>
       <c r="H189" s="20"/>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" ht="13.2">
       <c r="A190" s="19"/>
       <c r="H190" s="20"/>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" ht="13.2">
       <c r="A191" s="19"/>
       <c r="H191" s="20"/>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" ht="13.2">
       <c r="A192" s="19"/>
       <c r="H192" s="20"/>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" ht="13.2">
       <c r="A193" s="19"/>
       <c r="H193" s="20"/>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" ht="13.2">
       <c r="A194" s="19"/>
       <c r="H194" s="20"/>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" ht="13.2">
       <c r="A195" s="19"/>
       <c r="H195" s="20"/>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" ht="13.2">
       <c r="A196" s="19"/>
       <c r="H196" s="20"/>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" ht="13.2">
       <c r="A197" s="19"/>
       <c r="H197" s="20"/>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" ht="13.2">
       <c r="A198" s="19"/>
       <c r="H198" s="20"/>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" ht="13.2">
       <c r="A199" s="19"/>
       <c r="H199" s="20"/>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" ht="13.2">
       <c r="A200" s="19"/>
       <c r="H200" s="20"/>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" ht="13.2">
       <c r="A201" s="19"/>
       <c r="H201" s="20"/>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" ht="13.2">
       <c r="A202" s="19"/>
       <c r="H202" s="20"/>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" ht="13.2">
       <c r="A203" s="19"/>
       <c r="H203" s="20"/>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" ht="13.2">
       <c r="A204" s="19"/>
       <c r="H204" s="20"/>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" ht="13.2">
       <c r="A205" s="19"/>
       <c r="H205" s="20"/>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" ht="13.2">
       <c r="A206" s="19"/>
       <c r="H206" s="20"/>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" ht="13.2">
       <c r="A207" s="19"/>
       <c r="H207" s="20"/>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" ht="13.2">
       <c r="A208" s="19"/>
       <c r="H208" s="20"/>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" ht="13.2">
       <c r="A209" s="19"/>
       <c r="H209" s="20"/>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" ht="13.2">
       <c r="A210" s="19"/>
       <c r="H210" s="20"/>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" ht="13.2">
       <c r="A211" s="19"/>
       <c r="H211" s="20"/>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" ht="13.2">
       <c r="A212" s="19"/>
       <c r="H212" s="20"/>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" ht="13.2">
       <c r="A213" s="19"/>
       <c r="H213" s="20"/>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" ht="13.2">
       <c r="A214" s="19"/>
       <c r="H214" s="20"/>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" ht="13.2">
       <c r="A215" s="19"/>
       <c r="H215" s="20"/>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" ht="13.2">
       <c r="A216" s="19"/>
       <c r="H216" s="20"/>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" ht="13.2">
       <c r="A217" s="19"/>
       <c r="H217" s="20"/>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" ht="13.2">
       <c r="A218" s="19"/>
       <c r="H218" s="20"/>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" ht="13.2">
       <c r="A219" s="19"/>
       <c r="H219" s="20"/>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" ht="13.2">
       <c r="A220" s="19"/>
       <c r="H220" s="20"/>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" ht="13.2">
       <c r="A221" s="19"/>
       <c r="H221" s="20"/>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" ht="13.2">
       <c r="A222" s="19"/>
       <c r="H222" s="20"/>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" ht="13.2">
       <c r="A223" s="19"/>
       <c r="H223" s="20"/>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" ht="13.2">
       <c r="A224" s="19"/>
       <c r="H224" s="20"/>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" ht="13.2">
       <c r="A225" s="19"/>
       <c r="H225" s="20"/>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" ht="13.2">
       <c r="A226" s="19"/>
       <c r="H226" s="20"/>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" ht="13.2">
       <c r="A227" s="19"/>
       <c r="H227" s="20"/>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:8" ht="13.2">
       <c r="A228" s="19"/>
       <c r="H228" s="20"/>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:8" ht="13.2">
       <c r="A229" s="19"/>
       <c r="H229" s="20"/>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:8" ht="13.2">
       <c r="A230" s="19"/>
       <c r="H230" s="20"/>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:8" ht="13.2">
       <c r="A231" s="19"/>
       <c r="H231" s="20"/>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" ht="13.2">
       <c r="A232" s="19"/>
       <c r="H232" s="20"/>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" ht="13.2">
       <c r="A233" s="19"/>
       <c r="H233" s="20"/>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" ht="13.2">
       <c r="A234" s="19"/>
       <c r="H234" s="20"/>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:8" ht="13.2">
       <c r="A235" s="19"/>
       <c r="H235" s="20"/>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:8" ht="13.2">
       <c r="A236" s="19"/>
       <c r="H236" s="20"/>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" ht="13.2">
       <c r="A237" s="19"/>
       <c r="H237" s="20"/>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:8" ht="13.2">
       <c r="A238" s="19"/>
       <c r="H238" s="20"/>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" ht="13.2">
       <c r="A239" s="19"/>
       <c r="H239" s="20"/>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:8" ht="13.2">
       <c r="A240" s="19"/>
       <c r="H240" s="20"/>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" ht="13.2">
       <c r="A241" s="19"/>
       <c r="H241" s="20"/>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:8" ht="13.2">
       <c r="A242" s="19"/>
       <c r="H242" s="20"/>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:8" ht="13.2">
       <c r="A243" s="19"/>
       <c r="H243" s="20"/>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:8" ht="13.2">
       <c r="A244" s="19"/>
       <c r="H244" s="20"/>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:8" ht="13.2">
       <c r="A245" s="19"/>
       <c r="H245" s="20"/>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" spans="1:8" ht="13.2">
       <c r="A246" s="19"/>
       <c r="H246" s="20"/>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:8" ht="13.2">
       <c r="A247" s="19"/>
       <c r="H247" s="20"/>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" spans="1:8" ht="13.2">
       <c r="A248" s="19"/>
       <c r="H248" s="20"/>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" spans="1:8" ht="13.2">
       <c r="A249" s="19"/>
       <c r="H249" s="20"/>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" spans="1:8" ht="13.2">
       <c r="A250" s="19"/>
       <c r="H250" s="20"/>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" spans="1:8" ht="13.2">
       <c r="A251" s="19"/>
       <c r="H251" s="20"/>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" spans="1:8" ht="13.2">
       <c r="A252" s="19"/>
       <c r="H252" s="20"/>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" spans="1:8" ht="13.2">
       <c r="A253" s="19"/>
       <c r="H253" s="20"/>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:8" ht="13.2">
       <c r="A254" s="19"/>
       <c r="H254" s="20"/>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" spans="1:8" ht="13.2">
       <c r="A255" s="19"/>
       <c r="H255" s="20"/>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:8" ht="13.2">
       <c r="A256" s="19"/>
       <c r="H256" s="20"/>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:8" ht="13.2">
       <c r="A257" s="19"/>
       <c r="H257" s="20"/>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:8" ht="13.2">
       <c r="A258" s="19"/>
       <c r="H258" s="20"/>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:8" ht="13.2">
       <c r="A259" s="19"/>
       <c r="H259" s="20"/>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:8" ht="13.2">
       <c r="A260" s="19"/>
       <c r="H260" s="20"/>
     </row>
-    <row r="261" spans="1:8">
+    <row r="261" spans="1:8" ht="13.2">
       <c r="A261" s="19"/>
       <c r="H261" s="20"/>
     </row>
-    <row r="262" spans="1:8">
+    <row r="262" spans="1:8" ht="13.2">
       <c r="A262" s="19"/>
       <c r="H262" s="20"/>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:8" ht="13.2">
       <c r="A263" s="19"/>
       <c r="H263" s="20"/>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:8" ht="13.2">
       <c r="A264" s="19"/>
       <c r="H264" s="20"/>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:8" ht="13.2">
       <c r="A265" s="19"/>
       <c r="H265" s="20"/>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:8" ht="13.2">
       <c r="A266" s="19"/>
       <c r="H266" s="20"/>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:8" ht="13.2">
       <c r="A267" s="19"/>
       <c r="H267" s="20"/>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" spans="1:8" ht="13.2">
       <c r="A268" s="19"/>
       <c r="H268" s="20"/>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:8" ht="13.2">
       <c r="A269" s="19"/>
       <c r="H269" s="20"/>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:8" ht="13.2">
       <c r="A270" s="19"/>
       <c r="H270" s="20"/>
     </row>
-    <row r="271" spans="1:8">
+    <row r="271" spans="1:8" ht="13.2">
       <c r="A271" s="19"/>
       <c r="H271" s="20"/>
     </row>
-    <row r="272" spans="1:8">
+    <row r="272" spans="1:8" ht="13.2">
       <c r="A272" s="19"/>
       <c r="H272" s="20"/>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" spans="1:8" ht="13.2">
       <c r="A273" s="19"/>
       <c r="H273" s="20"/>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" spans="1:8" ht="13.2">
       <c r="A274" s="19"/>
       <c r="H274" s="20"/>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" spans="1:8" ht="13.2">
       <c r="A275" s="19"/>
       <c r="H275" s="20"/>
     </row>
-    <row r="276" spans="1:8">
+    <row r="276" spans="1:8" ht="13.2">
       <c r="A276" s="19"/>
       <c r="H276" s="20"/>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:8" ht="13.2">
       <c r="A277" s="19"/>
       <c r="H277" s="20"/>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:8" ht="13.2">
       <c r="A278" s="19"/>
       <c r="H278" s="20"/>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:8" ht="13.2">
       <c r="A279" s="19"/>
       <c r="H279" s="20"/>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:8" ht="13.2">
       <c r="A280" s="19"/>
       <c r="H280" s="20"/>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" spans="1:8" ht="13.2">
       <c r="A281" s="19"/>
       <c r="H281" s="20"/>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" spans="1:8" ht="13.2">
       <c r="A282" s="19"/>
       <c r="H282" s="20"/>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" spans="1:8" ht="13.2">
       <c r="A283" s="19"/>
       <c r="H283" s="20"/>
     </row>
-    <row r="284" spans="1:8">
+    <row r="284" spans="1:8" ht="13.2">
       <c r="A284" s="19"/>
       <c r="H284" s="20"/>
     </row>
-    <row r="285" spans="1:8">
+    <row r="285" spans="1:8" ht="13.2">
       <c r="A285" s="19"/>
       <c r="H285" s="20"/>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" spans="1:8" ht="13.2">
       <c r="A286" s="19"/>
       <c r="H286" s="20"/>
     </row>
-    <row r="287" spans="1:8">
+    <row r="287" spans="1:8" ht="13.2">
       <c r="A287" s="19"/>
       <c r="H287" s="20"/>
     </row>
-    <row r="288" spans="1:8">
+    <row r="288" spans="1:8" ht="13.2">
       <c r="A288" s="19"/>
       <c r="H288" s="20"/>
     </row>
-    <row r="289" spans="1:8">
+    <row r="289" spans="1:8" ht="13.2">
       <c r="A289" s="19"/>
       <c r="H289" s="20"/>
     </row>
-    <row r="290" spans="1:8">
+    <row r="290" spans="1:8" ht="13.2">
       <c r="A290" s="19"/>
       <c r="H290" s="20"/>
     </row>
-    <row r="291" spans="1:8">
+    <row r="291" spans="1:8" ht="13.2">
       <c r="A291" s="19"/>
       <c r="H291" s="20"/>
     </row>
-    <row r="292" spans="1:8">
+    <row r="292" spans="1:8" ht="13.2">
       <c r="A292" s="19"/>
       <c r="H292" s="20"/>
     </row>
-    <row r="293" spans="1:8">
+    <row r="293" spans="1:8" ht="13.2">
       <c r="A293" s="19"/>
       <c r="H293" s="20"/>
     </row>
-    <row r="294" spans="1:8">
+    <row r="294" spans="1:8" ht="13.2">
       <c r="A294" s="19"/>
       <c r="H294" s="20"/>
     </row>
-    <row r="295" spans="1:8">
+    <row r="295" spans="1:8" ht="13.2">
       <c r="A295" s="19"/>
       <c r="H295" s="20"/>
     </row>
-    <row r="296" spans="1:8">
+    <row r="296" spans="1:8" ht="13.2">
       <c r="A296" s="19"/>
       <c r="H296" s="20"/>
     </row>
-    <row r="297" spans="1:8">
+    <row r="297" spans="1:8" ht="13.2">
       <c r="A297" s="19"/>
       <c r="H297" s="20"/>
     </row>
-    <row r="298" spans="1:8">
+    <row r="298" spans="1:8" ht="13.2">
       <c r="A298" s="19"/>
       <c r="H298" s="20"/>
     </row>
-    <row r="299" spans="1:8">
+    <row r="299" spans="1:8" ht="13.2">
       <c r="A299" s="19"/>
       <c r="H299" s="20"/>
     </row>
-    <row r="300" spans="1:8">
+    <row r="300" spans="1:8" ht="13.2">
       <c r="A300" s="19"/>
       <c r="H300" s="20"/>
     </row>
-    <row r="301" spans="1:8">
+    <row r="301" spans="1:8" ht="13.2">
       <c r="A301" s="19"/>
       <c r="H301" s="20"/>
     </row>
-    <row r="302" spans="1:8">
+    <row r="302" spans="1:8" ht="13.2">
       <c r="A302" s="19"/>
       <c r="H302" s="20"/>
     </row>
-    <row r="303" spans="1:8">
+    <row r="303" spans="1:8" ht="13.2">
       <c r="A303" s="19"/>
       <c r="H303" s="20"/>
     </row>
-    <row r="304" spans="1:8">
+    <row r="304" spans="1:8" ht="13.2">
       <c r="A304" s="19"/>
       <c r="H304" s="20"/>
     </row>
-    <row r="305" spans="1:8">
+    <row r="305" spans="1:8" ht="13.2">
       <c r="A305" s="19"/>
       <c r="H305" s="20"/>
     </row>
-    <row r="306" spans="1:8">
+    <row r="306" spans="1:8" ht="13.2">
       <c r="A306" s="19"/>
       <c r="H306" s="20"/>
     </row>
-    <row r="307" spans="1:8">
+    <row r="307" spans="1:8" ht="13.2">
       <c r="A307" s="19"/>
       <c r="H307" s="20"/>
     </row>
-    <row r="308" spans="1:8">
+    <row r="308" spans="1:8" ht="13.2">
       <c r="A308" s="19"/>
       <c r="H308" s="20"/>
     </row>
-    <row r="309" spans="1:8">
+    <row r="309" spans="1:8" ht="13.2">
       <c r="A309" s="19"/>
       <c r="H309" s="20"/>
     </row>
-    <row r="310" spans="1:8">
+    <row r="310" spans="1:8" ht="13.2">
       <c r="A310" s="19"/>
       <c r="H310" s="20"/>
     </row>
-    <row r="311" spans="1:8">
+    <row r="311" spans="1:8" ht="13.2">
       <c r="A311" s="19"/>
       <c r="H311" s="20"/>
     </row>
-    <row r="312" spans="1:8">
+    <row r="312" spans="1:8" ht="13.2">
       <c r="A312" s="19"/>
       <c r="H312" s="20"/>
     </row>
-    <row r="313" spans="1:8">
+    <row r="313" spans="1:8" ht="13.2">
       <c r="A313" s="19"/>
       <c r="H313" s="20"/>
     </row>
-    <row r="314" spans="1:8">
+    <row r="314" spans="1:8" ht="13.2">
       <c r="A314" s="19"/>
       <c r="H314" s="20"/>
     </row>
-    <row r="315" spans="1:8">
+    <row r="315" spans="1:8" ht="13.2">
       <c r="A315" s="19"/>
       <c r="H315" s="20"/>
     </row>
-    <row r="316" spans="1:8">
+    <row r="316" spans="1:8" ht="13.2">
       <c r="A316" s="19"/>
       <c r="H316" s="20"/>
     </row>
-    <row r="317" spans="1:8">
+    <row r="317" spans="1:8" ht="13.2">
       <c r="A317" s="19"/>
       <c r="H317" s="20"/>
     </row>
-    <row r="318" spans="1:8">
+    <row r="318" spans="1:8" ht="13.2">
       <c r="A318" s="19"/>
       <c r="H318" s="20"/>
     </row>
-    <row r="319" spans="1:8">
+    <row r="319" spans="1:8" ht="13.2">
       <c r="A319" s="19"/>
       <c r="H319" s="20"/>
     </row>
-    <row r="320" spans="1:8">
+    <row r="320" spans="1:8" ht="13.2">
       <c r="A320" s="19"/>
       <c r="H320" s="20"/>
     </row>
-    <row r="321" spans="1:8">
+    <row r="321" spans="1:8" ht="13.2">
       <c r="A321" s="19"/>
       <c r="H321" s="20"/>
     </row>
-    <row r="322" spans="1:8">
+    <row r="322" spans="1:8" ht="13.2">
       <c r="A322" s="19"/>
       <c r="H322" s="20"/>
     </row>
-    <row r="323" spans="1:8">
+    <row r="323" spans="1:8" ht="13.2">
       <c r="A323" s="19"/>
       <c r="H323" s="20"/>
     </row>
-    <row r="324" spans="1:8">
+    <row r="324" spans="1:8" ht="13.2">
       <c r="A324" s="19"/>
       <c r="H324" s="20"/>
     </row>
-    <row r="325" spans="1:8">
+    <row r="325" spans="1:8" ht="13.2">
       <c r="A325" s="19"/>
       <c r="H325" s="20"/>
     </row>
-    <row r="326" spans="1:8">
+    <row r="326" spans="1:8" ht="13.2">
       <c r="A326" s="19"/>
       <c r="H326" s="20"/>
     </row>
-    <row r="327" spans="1:8">
+    <row r="327" spans="1:8" ht="13.2">
       <c r="A327" s="19"/>
       <c r="H327" s="20"/>
     </row>
-    <row r="328" spans="1:8">
+    <row r="328" spans="1:8" ht="13.2">
       <c r="A328" s="19"/>
       <c r="H328" s="20"/>
     </row>
-    <row r="329" spans="1:8">
+    <row r="329" spans="1:8" ht="13.2">
       <c r="A329" s="19"/>
       <c r="H329" s="20"/>
     </row>
-    <row r="330" spans="1:8">
+    <row r="330" spans="1:8" ht="13.2">
       <c r="A330" s="19"/>
       <c r="H330" s="20"/>
     </row>
-    <row r="331" spans="1:8">
+    <row r="331" spans="1:8" ht="13.2">
       <c r="A331" s="19"/>
       <c r="H331" s="20"/>
     </row>
-    <row r="332" spans="1:8">
+    <row r="332" spans="1:8" ht="13.2">
       <c r="A332" s="19"/>
       <c r="H332" s="20"/>
     </row>
-    <row r="333" spans="1:8">
+    <row r="333" spans="1:8" ht="13.2">
       <c r="A333" s="19"/>
       <c r="H333" s="20"/>
     </row>
-    <row r="334" spans="1:8">
+    <row r="334" spans="1:8" ht="13.2">
       <c r="A334" s="19"/>
       <c r="H334" s="20"/>
     </row>
-    <row r="335" spans="1:8">
+    <row r="335" spans="1:8" ht="13.2">
       <c r="A335" s="19"/>
       <c r="H335" s="20"/>
     </row>
-    <row r="336" spans="1:8">
+    <row r="336" spans="1:8" ht="13.2">
       <c r="A336" s="19"/>
       <c r="H336" s="20"/>
     </row>
-    <row r="337" spans="1:8">
+    <row r="337" spans="1:8" ht="13.2">
       <c r="A337" s="19"/>
       <c r="H337" s="20"/>
     </row>
-    <row r="338" spans="1:8">
+    <row r="338" spans="1:8" ht="13.2">
       <c r="A338" s="19"/>
       <c r="H338" s="20"/>
     </row>
-    <row r="339" spans="1:8">
+    <row r="339" spans="1:8" ht="13.2">
       <c r="A339" s="19"/>
       <c r="H339" s="20"/>
     </row>
-    <row r="340" spans="1:8">
+    <row r="340" spans="1:8" ht="13.2">
       <c r="A340" s="19"/>
       <c r="H340" s="20"/>
     </row>
-    <row r="341" spans="1:8">
+    <row r="341" spans="1:8" ht="13.2">
       <c r="A341" s="19"/>
       <c r="H341" s="20"/>
     </row>
-    <row r="342" spans="1:8">
+    <row r="342" spans="1:8" ht="13.2">
       <c r="A342" s="19"/>
       <c r="H342" s="20"/>
     </row>
-    <row r="343" spans="1:8">
+    <row r="343" spans="1:8" ht="13.2">
       <c r="A343" s="19"/>
       <c r="H343" s="20"/>
     </row>
-    <row r="344" spans="1:8">
+    <row r="344" spans="1:8" ht="13.2">
       <c r="A344" s="19"/>
       <c r="H344" s="20"/>
     </row>
-    <row r="345" spans="1:8">
+    <row r="345" spans="1:8" ht="13.2">
       <c r="A345" s="19"/>
       <c r="H345" s="20"/>
     </row>
-    <row r="346" spans="1:8">
+    <row r="346" spans="1:8" ht="13.2">
       <c r="A346" s="19"/>
       <c r="H346" s="20"/>
     </row>
-    <row r="347" spans="1:8">
+    <row r="347" spans="1:8" ht="13.2">
       <c r="A347" s="19"/>
       <c r="H347" s="20"/>
     </row>
-    <row r="348" spans="1:8">
+    <row r="348" spans="1:8" ht="13.2">
       <c r="A348" s="19"/>
       <c r="H348" s="20"/>
     </row>
-    <row r="349" spans="1:8">
+    <row r="349" spans="1:8" ht="13.2">
       <c r="A349" s="19"/>
       <c r="H349" s="20"/>
     </row>
-    <row r="350" spans="1:8">
+    <row r="350" spans="1:8" ht="13.2">
       <c r="A350" s="19"/>
       <c r="H350" s="20"/>
     </row>
-    <row r="351" spans="1:8">
+    <row r="351" spans="1:8" ht="13.2">
       <c r="A351" s="19"/>
       <c r="H351" s="20"/>
     </row>
-    <row r="352" spans="1:8">
+    <row r="352" spans="1:8" ht="13.2">
       <c r="A352" s="19"/>
       <c r="H352" s="20"/>
     </row>
-    <row r="353" spans="1:8">
+    <row r="353" spans="1:8" ht="13.2">
       <c r="A353" s="19"/>
       <c r="H353" s="20"/>
     </row>
-    <row r="354" spans="1:8">
+    <row r="354" spans="1:8" ht="13.2">
       <c r="A354" s="19"/>
       <c r="H354" s="20"/>
     </row>
-    <row r="355" spans="1:8">
+    <row r="355" spans="1:8" ht="13.2">
       <c r="A355" s="19"/>
       <c r="H355" s="20"/>
     </row>
-    <row r="356" spans="1:8">
+    <row r="356" spans="1:8" ht="13.2">
       <c r="A356" s="19"/>
       <c r="H356" s="20"/>
     </row>
-    <row r="357" spans="1:8">
+    <row r="357" spans="1:8" ht="13.2">
       <c r="A357" s="19"/>
       <c r="H357" s="20"/>
     </row>
-    <row r="358" spans="1:8">
+    <row r="358" spans="1:8" ht="13.2">
       <c r="A358" s="19"/>
       <c r="H358" s="20"/>
     </row>
-    <row r="359" spans="1:8">
+    <row r="359" spans="1:8" ht="13.2">
       <c r="A359" s="19"/>
       <c r="H359" s="20"/>
     </row>
-    <row r="360" spans="1:8">
+    <row r="360" spans="1:8" ht="13.2">
       <c r="A360" s="19"/>
       <c r="H360" s="20"/>
     </row>
-    <row r="361" spans="1:8">
+    <row r="361" spans="1:8" ht="13.2">
       <c r="A361" s="19"/>
       <c r="H361" s="20"/>
     </row>
-    <row r="362" spans="1:8">
+    <row r="362" spans="1:8" ht="13.2">
       <c r="A362" s="19"/>
       <c r="H362" s="20"/>
     </row>
-    <row r="363" spans="1:8">
+    <row r="363" spans="1:8" ht="13.2">
       <c r="A363" s="19"/>
       <c r="H363" s="20"/>
     </row>
-    <row r="364" spans="1:8">
+    <row r="364" spans="1:8" ht="13.2">
       <c r="A364" s="19"/>
       <c r="H364" s="20"/>
     </row>
-    <row r="365" spans="1:8">
+    <row r="365" spans="1:8" ht="13.2">
       <c r="A365" s="19"/>
       <c r="H365" s="20"/>
     </row>
-    <row r="366" spans="1:8">
+    <row r="366" spans="1:8" ht="13.2">
       <c r="A366" s="19"/>
       <c r="H366" s="20"/>
     </row>
-    <row r="367" spans="1:8">
+    <row r="367" spans="1:8" ht="13.2">
       <c r="A367" s="19"/>
       <c r="H367" s="20"/>
     </row>
-    <row r="368" spans="1:8">
+    <row r="368" spans="1:8" ht="13.2">
       <c r="A368" s="19"/>
       <c r="H368" s="20"/>
     </row>
-    <row r="369" spans="1:8">
+    <row r="369" spans="1:8" ht="13.2">
       <c r="A369" s="19"/>
       <c r="H369" s="20"/>
     </row>
-    <row r="370" spans="1:8">
+    <row r="370" spans="1:8" ht="13.2">
       <c r="A370" s="19"/>
       <c r="H370" s="20"/>
     </row>
-    <row r="371" spans="1:8">
+    <row r="371" spans="1:8" ht="13.2">
       <c r="A371" s="19"/>
       <c r="H371" s="20"/>
     </row>
-    <row r="372" spans="1:8">
+    <row r="372" spans="1:8" ht="13.2">
       <c r="A372" s="19"/>
       <c r="H372" s="20"/>
     </row>
-    <row r="373" spans="1:8">
+    <row r="373" spans="1:8" ht="13.2">
       <c r="A373" s="19"/>
       <c r="H373" s="20"/>
     </row>
-    <row r="374" spans="1:8">
+    <row r="374" spans="1:8" ht="13.2">
       <c r="A374" s="19"/>
       <c r="H374" s="20"/>
     </row>
-    <row r="375" spans="1:8">
+    <row r="375" spans="1:8" ht="13.2">
       <c r="A375" s="19"/>
       <c r="H375" s="20"/>
     </row>
-    <row r="376" spans="1:8">
+    <row r="376" spans="1:8" ht="13.2">
       <c r="A376" s="19"/>
       <c r="H376" s="20"/>
     </row>
-    <row r="377" spans="1:8">
+    <row r="377" spans="1:8" ht="13.2">
       <c r="A377" s="19"/>
       <c r="H377" s="20"/>
     </row>
-    <row r="378" spans="1:8">
+    <row r="378" spans="1:8" ht="13.2">
       <c r="A378" s="19"/>
       <c r="H378" s="20"/>
     </row>
-    <row r="379" spans="1:8">
+    <row r="379" spans="1:8" ht="13.2">
       <c r="A379" s="19"/>
       <c r="H379" s="20"/>
     </row>
-    <row r="380" spans="1:8">
+    <row r="380" spans="1:8" ht="13.2">
       <c r="A380" s="19"/>
       <c r="H380" s="20"/>
     </row>
-    <row r="381" spans="1:8">
+    <row r="381" spans="1:8" ht="13.2">
       <c r="A381" s="19"/>
       <c r="H381" s="20"/>
     </row>
-    <row r="382" spans="1:8">
+    <row r="382" spans="1:8" ht="13.2">
       <c r="A382" s="19"/>
       <c r="H382" s="20"/>
     </row>
-    <row r="383" spans="1:8">
+    <row r="383" spans="1:8" ht="13.2">
       <c r="A383" s="19"/>
       <c r="H383" s="20"/>
     </row>
-    <row r="384" spans="1:8">
+    <row r="384" spans="1:8" ht="13.2">
       <c r="A384" s="19"/>
       <c r="H384" s="20"/>
     </row>
-    <row r="385" spans="1:8">
+    <row r="385" spans="1:8" ht="13.2">
       <c r="A385" s="19"/>
       <c r="H385" s="20"/>
     </row>
-    <row r="386" spans="1:8">
+    <row r="386" spans="1:8" ht="13.2">
       <c r="A386" s="19"/>
       <c r="H386" s="20"/>
     </row>
-    <row r="387" spans="1:8">
+    <row r="387" spans="1:8" ht="13.2">
       <c r="A387" s="19"/>
       <c r="H387" s="20"/>
     </row>
-    <row r="388" spans="1:8">
+    <row r="388" spans="1:8" ht="13.2">
       <c r="A388" s="19"/>
       <c r="H388" s="20"/>
     </row>
-    <row r="389" spans="1:8">
+    <row r="389" spans="1:8" ht="13.2">
       <c r="A389" s="19"/>
       <c r="H389" s="20"/>
     </row>
-    <row r="390" spans="1:8">
+    <row r="390" spans="1:8" ht="13.2">
       <c r="A390" s="19"/>
       <c r="H390" s="20"/>
     </row>
-    <row r="391" spans="1:8">
+    <row r="391" spans="1:8" ht="13.2">
       <c r="A391" s="19"/>
       <c r="H391" s="20"/>
     </row>
-    <row r="392" spans="1:8">
+    <row r="392" spans="1:8" ht="13.2">
       <c r="A392" s="19"/>
       <c r="H392" s="20"/>
     </row>
-    <row r="393" spans="1:8">
+    <row r="393" spans="1:8" ht="13.2">
       <c r="A393" s="19"/>
       <c r="H393" s="20"/>
     </row>
-    <row r="394" spans="1:8">
+    <row r="394" spans="1:8" ht="13.2">
       <c r="A394" s="19"/>
       <c r="H394" s="20"/>
     </row>
-    <row r="395" spans="1:8">
+    <row r="395" spans="1:8" ht="13.2">
       <c r="A395" s="19"/>
       <c r="H395" s="20"/>
     </row>
-    <row r="396" spans="1:8">
+    <row r="396" spans="1:8" ht="13.2">
       <c r="A396" s="19"/>
       <c r="H396" s="20"/>
     </row>
-    <row r="397" spans="1:8">
+    <row r="397" spans="1:8" ht="13.2">
       <c r="A397" s="19"/>
       <c r="H397" s="20"/>
     </row>
-    <row r="398" spans="1:8">
+    <row r="398" spans="1:8" ht="13.2">
       <c r="A398" s="19"/>
       <c r="H398" s="20"/>
     </row>
-    <row r="399" spans="1:8">
+    <row r="399" spans="1:8" ht="13.2">
       <c r="A399" s="19"/>
       <c r="H399" s="20"/>
     </row>
-    <row r="400" spans="1:8">
+    <row r="400" spans="1:8" ht="13.2">
       <c r="A400" s="19"/>
       <c r="H400" s="20"/>
     </row>
-    <row r="401" spans="1:8">
+    <row r="401" spans="1:8" ht="13.2">
       <c r="A401" s="19"/>
       <c r="H401" s="20"/>
     </row>
-    <row r="402" spans="1:8">
+    <row r="402" spans="1:8" ht="13.2">
       <c r="A402" s="19"/>
       <c r="H402" s="20"/>
     </row>
-    <row r="403" spans="1:8">
+    <row r="403" spans="1:8" ht="13.2">
       <c r="A403" s="19"/>
       <c r="H403" s="20"/>
     </row>
-    <row r="404" spans="1:8">
+    <row r="404" spans="1:8" ht="13.2">
       <c r="A404" s="19"/>
       <c r="H404" s="20"/>
     </row>
-    <row r="405" spans="1:8">
+    <row r="405" spans="1:8" ht="13.2">
       <c r="A405" s="19"/>
       <c r="H405" s="20"/>
     </row>
-    <row r="406" spans="1:8">
+    <row r="406" spans="1:8" ht="13.2">
       <c r="A406" s="19"/>
       <c r="H406" s="20"/>
     </row>
-    <row r="407" spans="1:8">
+    <row r="407" spans="1:8" ht="13.2">
       <c r="A407" s="19"/>
       <c r="H407" s="20"/>
     </row>
-    <row r="408" spans="1:8">
+    <row r="408" spans="1:8" ht="13.2">
       <c r="A408" s="19"/>
       <c r="H408" s="20"/>
     </row>
-    <row r="409" spans="1:8">
+    <row r="409" spans="1:8" ht="13.2">
       <c r="A409" s="19"/>
       <c r="H409" s="20"/>
     </row>
-    <row r="410" spans="1:8">
+    <row r="410" spans="1:8" ht="13.2">
       <c r="A410" s="19"/>
       <c r="H410" s="20"/>
     </row>
-    <row r="411" spans="1:8">
+    <row r="411" spans="1:8" ht="13.2">
       <c r="A411" s="19"/>
       <c r="H411" s="20"/>
     </row>
-    <row r="412" spans="1:8">
+    <row r="412" spans="1:8" ht="13.2">
       <c r="A412" s="19"/>
       <c r="H412" s="20"/>
     </row>
-    <row r="413" spans="1:8">
+    <row r="413" spans="1:8" ht="13.2">
       <c r="A413" s="19"/>
       <c r="H413" s="20"/>
     </row>
-    <row r="414" spans="1:8">
+    <row r="414" spans="1:8" ht="13.2">
       <c r="A414" s="19"/>
       <c r="H414" s="20"/>
     </row>
-    <row r="415" spans="1:8">
+    <row r="415" spans="1:8" ht="13.2">
       <c r="A415" s="19"/>
       <c r="H415" s="20"/>
     </row>
-    <row r="416" spans="1:8">
+    <row r="416" spans="1:8" ht="13.2">
       <c r="A416" s="19"/>
       <c r="H416" s="20"/>
     </row>
-    <row r="417" spans="1:8">
+    <row r="417" spans="1:8" ht="13.2">
       <c r="A417" s="19"/>
       <c r="H417" s="20"/>
     </row>
-    <row r="418" spans="1:8">
+    <row r="418" spans="1:8" ht="13.2">
       <c r="A418" s="19"/>
       <c r="H418" s="20"/>
     </row>
-    <row r="419" spans="1:8">
+    <row r="419" spans="1:8" ht="13.2">
       <c r="A419" s="19"/>
       <c r="H419" s="20"/>
     </row>
-    <row r="420" spans="1:8">
+    <row r="420" spans="1:8" ht="13.2">
       <c r="A420" s="19"/>
       <c r="H420" s="20"/>
     </row>
-    <row r="421" spans="1:8">
+    <row r="421" spans="1:8" ht="13.2">
       <c r="A421" s="19"/>
       <c r="H421" s="20"/>
     </row>
-    <row r="422" spans="1:8">
+    <row r="422" spans="1:8" ht="13.2">
       <c r="A422" s="19"/>
       <c r="H422" s="20"/>
     </row>
-    <row r="423" spans="1:8">
+    <row r="423" spans="1:8" ht="13.2">
       <c r="A423" s="19"/>
       <c r="H423" s="20"/>
     </row>
-    <row r="424" spans="1:8">
+    <row r="424" spans="1:8" ht="13.2">
       <c r="A424" s="19"/>
       <c r="H424" s="20"/>
     </row>
-    <row r="425" spans="1:8">
+    <row r="425" spans="1:8" ht="13.2">
       <c r="A425" s="19"/>
       <c r="H425" s="20"/>
     </row>
-    <row r="426" spans="1:8">
+    <row r="426" spans="1:8" ht="13.2">
       <c r="A426" s="19"/>
       <c r="H426" s="20"/>
     </row>
-    <row r="427" spans="1:8">
+    <row r="427" spans="1:8" ht="13.2">
       <c r="A427" s="19"/>
       <c r="H427" s="20"/>
     </row>
-    <row r="428" spans="1:8">
+    <row r="428" spans="1:8" ht="13.2">
       <c r="A428" s="19"/>
       <c r="H428" s="20"/>
     </row>
-    <row r="429" spans="1:8">
+    <row r="429" spans="1:8" ht="13.2">
       <c r="A429" s="19"/>
       <c r="H429" s="20"/>
     </row>
-    <row r="430" spans="1:8">
+    <row r="430" spans="1:8" ht="13.2">
       <c r="A430" s="19"/>
       <c r="H430" s="20"/>
     </row>
-    <row r="431" spans="1:8">
+    <row r="431" spans="1:8" ht="13.2">
       <c r="A431" s="19"/>
       <c r="H431" s="20"/>
     </row>
-    <row r="432" spans="1:8">
+    <row r="432" spans="1:8" ht="13.2">
       <c r="A432" s="19"/>
       <c r="H432" s="20"/>
     </row>
-    <row r="433" spans="1:8">
+    <row r="433" spans="1:8" ht="13.2">
       <c r="A433" s="19"/>
       <c r="H433" s="20"/>
     </row>
-    <row r="434" spans="1:8">
+    <row r="434" spans="1:8" ht="13.2">
       <c r="A434" s="19"/>
       <c r="H434" s="20"/>
     </row>
-    <row r="435" spans="1:8">
+    <row r="435" spans="1:8" ht="13.2">
       <c r="A435" s="19"/>
       <c r="H435" s="20"/>
     </row>
-    <row r="436" spans="1:8">
+    <row r="436" spans="1:8" ht="13.2">
       <c r="A436" s="19"/>
       <c r="H436" s="20"/>
     </row>
-    <row r="437" spans="1:8">
+    <row r="437" spans="1:8" ht="13.2">
       <c r="A437" s="19"/>
       <c r="H437" s="20"/>
     </row>
-    <row r="438" spans="1:8">
+    <row r="438" spans="1:8" ht="13.2">
       <c r="A438" s="19"/>
       <c r="H438" s="20"/>
     </row>
-    <row r="439" spans="1:8">
+    <row r="439" spans="1:8" ht="13.2">
       <c r="A439" s="19"/>
       <c r="H439" s="20"/>
     </row>
-    <row r="440" spans="1:8">
+    <row r="440" spans="1:8" ht="13.2">
       <c r="A440" s="19"/>
       <c r="H440" s="20"/>
     </row>
-    <row r="441" spans="1:8">
+    <row r="441" spans="1:8" ht="13.2">
       <c r="A441" s="19"/>
       <c r="H441" s="20"/>
     </row>
-    <row r="442" spans="1:8">
+    <row r="442" spans="1:8" ht="13.2">
       <c r="A442" s="19"/>
       <c r="H442" s="20"/>
     </row>
-    <row r="443" spans="1:8">
+    <row r="443" spans="1:8" ht="13.2">
       <c r="A443" s="19"/>
       <c r="H443" s="20"/>
     </row>
-    <row r="444" spans="1:8">
+    <row r="444" spans="1:8" ht="13.2">
       <c r="A444" s="19"/>
       <c r="H444" s="20"/>
     </row>
-    <row r="445" spans="1:8">
+    <row r="445" spans="1:8" ht="13.2">
       <c r="A445" s="19"/>
       <c r="H445" s="20"/>
     </row>
-    <row r="446" spans="1:8">
+    <row r="446" spans="1:8" ht="13.2">
       <c r="A446" s="19"/>
       <c r="H446" s="20"/>
     </row>
-    <row r="447" spans="1:8">
+    <row r="447" spans="1:8" ht="13.2">
       <c r="A447" s="19"/>
       <c r="H447" s="20"/>
     </row>
-    <row r="448" spans="1:8">
+    <row r="448" spans="1:8" ht="13.2">
       <c r="A448" s="19"/>
       <c r="H448" s="20"/>
     </row>
-    <row r="449" spans="1:8">
+    <row r="449" spans="1:8" ht="13.2">
       <c r="A449" s="19"/>
       <c r="H449" s="20"/>
     </row>
-    <row r="450" spans="1:8">
+    <row r="450" spans="1:8" ht="13.2">
       <c r="A450" s="19"/>
       <c r="H450" s="20"/>
     </row>
-    <row r="451" spans="1:8">
+    <row r="451" spans="1:8" ht="13.2">
       <c r="A451" s="19"/>
       <c r="H451" s="20"/>
     </row>
-    <row r="452" spans="1:8">
+    <row r="452" spans="1:8" ht="13.2">
       <c r="A452" s="19"/>
       <c r="H452" s="20"/>
     </row>
-    <row r="453" spans="1:8">
+    <row r="453" spans="1:8" ht="13.2">
       <c r="A453" s="19"/>
       <c r="H453" s="20"/>
     </row>
-    <row r="454" spans="1:8">
+    <row r="454" spans="1:8" ht="13.2">
       <c r="A454" s="19"/>
       <c r="H454" s="20"/>
     </row>
-    <row r="455" spans="1:8">
+    <row r="455" spans="1:8" ht="13.2">
       <c r="A455" s="19"/>
       <c r="H455" s="20"/>
     </row>
-    <row r="456" spans="1:8">
+    <row r="456" spans="1:8" ht="13.2">
       <c r="A456" s="19"/>
       <c r="H456" s="20"/>
     </row>
-    <row r="457" spans="1:8">
+    <row r="457" spans="1:8" ht="13.2">
       <c r="A457" s="19"/>
       <c r="H457" s="20"/>
     </row>
-    <row r="458" spans="1:8">
+    <row r="458" spans="1:8" ht="13.2">
       <c r="A458" s="19"/>
       <c r="H458" s="20"/>
     </row>
-    <row r="459" spans="1:8">
+    <row r="459" spans="1:8" ht="13.2">
       <c r="A459" s="19"/>
       <c r="H459" s="20"/>
     </row>
-    <row r="460" spans="1:8">
+    <row r="460" spans="1:8" ht="13.2">
       <c r="A460" s="19"/>
       <c r="H460" s="20"/>
     </row>
-    <row r="461" spans="1:8">
+    <row r="461" spans="1:8" ht="13.2">
       <c r="A461" s="19"/>
       <c r="H461" s="20"/>
     </row>
-    <row r="462" spans="1:8">
+    <row r="462" spans="1:8" ht="13.2">
       <c r="A462" s="19"/>
       <c r="H462" s="20"/>
     </row>
-    <row r="463" spans="1:8">
+    <row r="463" spans="1:8" ht="13.2">
       <c r="A463" s="19"/>
       <c r="H463" s="20"/>
     </row>
-    <row r="464" spans="1:8">
+    <row r="464" spans="1:8" ht="13.2">
       <c r="A464" s="19"/>
       <c r="H464" s="20"/>
     </row>
-    <row r="465" spans="1:8">
+    <row r="465" spans="1:8" ht="13.2">
       <c r="A465" s="19"/>
       <c r="H465" s="20"/>
     </row>
-    <row r="466" spans="1:8">
+    <row r="466" spans="1:8" ht="13.2">
       <c r="A466" s="19"/>
       <c r="H466" s="20"/>
     </row>
-    <row r="467" spans="1:8">
+    <row r="467" spans="1:8" ht="13.2">
       <c r="A467" s="19"/>
       <c r="H467" s="20"/>
     </row>
-    <row r="468" spans="1:8">
+    <row r="468" spans="1:8" ht="13.2">
       <c r="A468" s="19"/>
       <c r="H468" s="20"/>
     </row>
-    <row r="469" spans="1:8">
+    <row r="469" spans="1:8" ht="13.2">
       <c r="A469" s="19"/>
       <c r="H469" s="20"/>
     </row>
-    <row r="470" spans="1:8">
+    <row r="470" spans="1:8" ht="13.2">
       <c r="A470" s="19"/>
       <c r="H470" s="20"/>
     </row>
-    <row r="471" spans="1:8">
+    <row r="471" spans="1:8" ht="13.2">
       <c r="A471" s="19"/>
       <c r="H471" s="20"/>
     </row>
-    <row r="472" spans="1:8">
+    <row r="472" spans="1:8" ht="13.2">
       <c r="A472" s="19"/>
       <c r="H472" s="20"/>
     </row>
-    <row r="473" spans="1:8">
+    <row r="473" spans="1:8" ht="13.2">
       <c r="A473" s="19"/>
       <c r="H473" s="20"/>
     </row>
-    <row r="474" spans="1:8">
+    <row r="474" spans="1:8" ht="13.2">
       <c r="A474" s="19"/>
       <c r="H474" s="20"/>
     </row>
-    <row r="475" spans="1:8">
+    <row r="475" spans="1:8" ht="13.2">
       <c r="A475" s="19"/>
       <c r="H475" s="20"/>
     </row>
-    <row r="476" spans="1:8">
+    <row r="476" spans="1:8" ht="13.2">
       <c r="A476" s="19"/>
       <c r="H476" s="20"/>
     </row>
-    <row r="477" spans="1:8">
+    <row r="477" spans="1:8" ht="13.2">
       <c r="A477" s="19"/>
       <c r="H477" s="20"/>
     </row>
-    <row r="478" spans="1:8">
+    <row r="478" spans="1:8" ht="13.2">
       <c r="A478" s="19"/>
       <c r="H478" s="20"/>
     </row>
-    <row r="479" spans="1:8">
+    <row r="479" spans="1:8" ht="13.2">
       <c r="A479" s="19"/>
       <c r="H479" s="20"/>
     </row>
-    <row r="480" spans="1:8">
+    <row r="480" spans="1:8" ht="13.2">
       <c r="A480" s="19"/>
       <c r="H480" s="20"/>
     </row>
-    <row r="481" spans="1:8">
+    <row r="481" spans="1:8" ht="13.2">
       <c r="A481" s="19"/>
       <c r="H481" s="20"/>
     </row>
-    <row r="482" spans="1:8">
+    <row r="482" spans="1:8" ht="13.2">
       <c r="A482" s="19"/>
       <c r="H482" s="20"/>
     </row>
-    <row r="483" spans="1:8">
+    <row r="483" spans="1:8" ht="13.2">
       <c r="A483" s="19"/>
       <c r="H483" s="20"/>
     </row>
-    <row r="484" spans="1:8">
+    <row r="484" spans="1:8" ht="13.2">
       <c r="A484" s="19"/>
       <c r="H484" s="20"/>
     </row>
-    <row r="485" spans="1:8">
+    <row r="485" spans="1:8" ht="13.2">
       <c r="A485" s="19"/>
       <c r="H485" s="20"/>
     </row>
-    <row r="486" spans="1:8">
+    <row r="486" spans="1:8" ht="13.2">
       <c r="A486" s="19"/>
       <c r="H486" s="20"/>
     </row>
-    <row r="487" spans="1:8">
+    <row r="487" spans="1:8" ht="13.2">
       <c r="A487" s="19"/>
       <c r="H487" s="20"/>
     </row>
-    <row r="488" spans="1:8">
+    <row r="488" spans="1:8" ht="13.2">
       <c r="A488" s="19"/>
       <c r="H488" s="20"/>
     </row>
-    <row r="489" spans="1:8">
+    <row r="489" spans="1:8" ht="13.2">
       <c r="A489" s="19"/>
       <c r="H489" s="20"/>
     </row>
-    <row r="490" spans="1:8">
+    <row r="490" spans="1:8" ht="13.2">
       <c r="A490" s="19"/>
       <c r="H490" s="20"/>
     </row>
-    <row r="491" spans="1:8">
+    <row r="491" spans="1:8" ht="13.2">
       <c r="A491" s="19"/>
       <c r="H491" s="20"/>
     </row>
-    <row r="492" spans="1:8">
+    <row r="492" spans="1:8" ht="13.2">
       <c r="A492" s="19"/>
       <c r="H492" s="20"/>
     </row>
-    <row r="493" spans="1:8">
+    <row r="493" spans="1:8" ht="13.2">
       <c r="A493" s="19"/>
       <c r="H493" s="20"/>
     </row>
-    <row r="494" spans="1:8">
+    <row r="494" spans="1:8" ht="13.2">
       <c r="A494" s="19"/>
       <c r="H494" s="20"/>
     </row>
-    <row r="495" spans="1:8">
+    <row r="495" spans="1:8" ht="13.2">
       <c r="A495" s="19"/>
       <c r="H495" s="20"/>
     </row>
-    <row r="496" spans="1:8">
+    <row r="496" spans="1:8" ht="13.2">
       <c r="A496" s="19"/>
       <c r="H496" s="20"/>
     </row>
-    <row r="497" spans="1:8">
+    <row r="497" spans="1:8" ht="13.2">
       <c r="A497" s="19"/>
       <c r="H497" s="20"/>
     </row>
-    <row r="498" spans="1:8">
+    <row r="498" spans="1:8" ht="13.2">
       <c r="A498" s="19"/>
       <c r="H498" s="20"/>
     </row>
-    <row r="499" spans="1:8">
+    <row r="499" spans="1:8" ht="13.2">
       <c r="A499" s="19"/>
       <c r="H499" s="20"/>
     </row>
-    <row r="500" spans="1:8">
+    <row r="500" spans="1:8" ht="13.2">
       <c r="A500" s="19"/>
       <c r="H500" s="20"/>
     </row>
-    <row r="501" spans="1:8">
+    <row r="501" spans="1:8" ht="13.2">
       <c r="A501" s="19"/>
       <c r="H501" s="20"/>
     </row>
-    <row r="502" spans="1:8">
+    <row r="502" spans="1:8" ht="13.2">
       <c r="A502" s="19"/>
       <c r="H502" s="20"/>
     </row>
-    <row r="503" spans="1:8">
+    <row r="503" spans="1:8" ht="13.2">
       <c r="A503" s="19"/>
       <c r="H503" s="20"/>
     </row>
-    <row r="504" spans="1:8">
+    <row r="504" spans="1:8" ht="13.2">
       <c r="A504" s="19"/>
       <c r="H504" s="20"/>
     </row>
-    <row r="505" spans="1:8">
+    <row r="505" spans="1:8" ht="13.2">
       <c r="A505" s="19"/>
       <c r="H505" s="20"/>
     </row>
-    <row r="506" spans="1:8">
+    <row r="506" spans="1:8" ht="13.2">
       <c r="A506" s="19"/>
       <c r="H506" s="20"/>
     </row>
-    <row r="507" spans="1:8">
+    <row r="507" spans="1:8" ht="13.2">
       <c r="A507" s="19"/>
       <c r="H507" s="20"/>
     </row>
-    <row r="508" spans="1:8">
+    <row r="508" spans="1:8" ht="13.2">
       <c r="A508" s="19"/>
       <c r="H508" s="20"/>
     </row>
-    <row r="509" spans="1:8">
+    <row r="509" spans="1:8" ht="13.2">
       <c r="A509" s="19"/>
       <c r="H509" s="20"/>
     </row>
-    <row r="510" spans="1:8">
+    <row r="510" spans="1:8" ht="13.2">
       <c r="A510" s="19"/>
       <c r="H510" s="20"/>
     </row>
-    <row r="511" spans="1:8">
+    <row r="511" spans="1:8" ht="13.2">
       <c r="A511" s="19"/>
       <c r="H511" s="20"/>
     </row>
-    <row r="512" spans="1:8">
+    <row r="512" spans="1:8" ht="13.2">
       <c r="A512" s="19"/>
       <c r="H512" s="20"/>
     </row>
-    <row r="513" spans="1:8">
+    <row r="513" spans="1:8" ht="13.2">
       <c r="A513" s="19"/>
       <c r="H513" s="20"/>
     </row>
-    <row r="514" spans="1:8">
+    <row r="514" spans="1:8" ht="13.2">
       <c r="A514" s="19"/>
       <c r="H514" s="20"/>
     </row>
-    <row r="515" spans="1:8">
+    <row r="515" spans="1:8" ht="13.2">
       <c r="A515" s="19"/>
       <c r="H515" s="20"/>
     </row>
-    <row r="516" spans="1:8">
+    <row r="516" spans="1:8" ht="13.2">
       <c r="A516" s="19"/>
       <c r="H516" s="20"/>
     </row>
-    <row r="517" spans="1:8">
+    <row r="517" spans="1:8" ht="13.2">
       <c r="A517" s="19"/>
       <c r="H517" s="20"/>
     </row>
-    <row r="518" spans="1:8">
+    <row r="518" spans="1:8" ht="13.2">
       <c r="A518" s="19"/>
       <c r="H518" s="20"/>
     </row>
-    <row r="519" spans="1:8">
+    <row r="519" spans="1:8" ht="13.2">
       <c r="A519" s="19"/>
       <c r="H519" s="20"/>
     </row>
-    <row r="520" spans="1:8">
+    <row r="520" spans="1:8" ht="13.2">
       <c r="A520" s="19"/>
       <c r="H520" s="20"/>
     </row>
-    <row r="521" spans="1:8">
+    <row r="521" spans="1:8" ht="13.2">
       <c r="A521" s="19"/>
       <c r="H521" s="20"/>
     </row>
-    <row r="522" spans="1:8">
+    <row r="522" spans="1:8" ht="13.2">
       <c r="A522" s="19"/>
       <c r="H522" s="20"/>
     </row>
-    <row r="523" spans="1:8">
+    <row r="523" spans="1:8" ht="13.2">
       <c r="A523" s="19"/>
       <c r="H523" s="20"/>
     </row>
-    <row r="524" spans="1:8">
+    <row r="524" spans="1:8" ht="13.2">
       <c r="A524" s="19"/>
       <c r="H524" s="20"/>
     </row>
-    <row r="525" spans="1:8">
+    <row r="525" spans="1:8" ht="13.2">
       <c r="A525" s="19"/>
       <c r="H525" s="20"/>
     </row>
-    <row r="526" spans="1:8">
+    <row r="526" spans="1:8" ht="13.2">
       <c r="A526" s="19"/>
       <c r="H526" s="20"/>
     </row>
-    <row r="527" spans="1:8">
+    <row r="527" spans="1:8" ht="13.2">
       <c r="A527" s="19"/>
       <c r="H527" s="20"/>
     </row>
-    <row r="528" spans="1:8">
+    <row r="528" spans="1:8" ht="13.2">
       <c r="A528" s="19"/>
       <c r="H528" s="20"/>
     </row>
-    <row r="529" spans="1:8">
+    <row r="529" spans="1:8" ht="13.2">
       <c r="A529" s="19"/>
       <c r="H529" s="20"/>
     </row>
-    <row r="530" spans="1:8">
+    <row r="530" spans="1:8" ht="13.2">
       <c r="A530" s="19"/>
       <c r="H530" s="20"/>
     </row>
-    <row r="531" spans="1:8">
+    <row r="531" spans="1:8" ht="13.2">
       <c r="A531" s="19"/>
       <c r="H531" s="20"/>
     </row>
-    <row r="532" spans="1:8">
+    <row r="532" spans="1:8" ht="13.2">
       <c r="A532" s="19"/>
       <c r="H532" s="20"/>
     </row>
-    <row r="533" spans="1:8">
+    <row r="533" spans="1:8" ht="13.2">
       <c r="A533" s="19"/>
       <c r="H533" s="20"/>
     </row>
-    <row r="534" spans="1:8">
+    <row r="534" spans="1:8" ht="13.2">
       <c r="A534" s="19"/>
       <c r="H534" s="20"/>
     </row>
-    <row r="535" spans="1:8">
+    <row r="535" spans="1:8" ht="13.2">
       <c r="A535" s="19"/>
       <c r="H535" s="20"/>
     </row>
-    <row r="536" spans="1:8">
+    <row r="536" spans="1:8" ht="13.2">
       <c r="A536" s="19"/>
       <c r="H536" s="20"/>
     </row>
-    <row r="537" spans="1:8">
+    <row r="537" spans="1:8" ht="13.2">
       <c r="A537" s="19"/>
       <c r="H537" s="20"/>
     </row>
-    <row r="538" spans="1:8">
+    <row r="538" spans="1:8" ht="13.2">
       <c r="A538" s="19"/>
       <c r="H538" s="20"/>
     </row>
-    <row r="539" spans="1:8">
+    <row r="539" spans="1:8" ht="13.2">
       <c r="A539" s="19"/>
       <c r="H539" s="20"/>
     </row>
-    <row r="540" spans="1:8">
+    <row r="540" spans="1:8" ht="13.2">
       <c r="A540" s="19"/>
       <c r="H540" s="20"/>
     </row>
-    <row r="541" spans="1:8">
+    <row r="541" spans="1:8" ht="13.2">
       <c r="A541" s="19"/>
       <c r="H541" s="20"/>
     </row>
-    <row r="542" spans="1:8">
+    <row r="542" spans="1:8" ht="13.2">
       <c r="A542" s="19"/>
       <c r="H542" s="20"/>
     </row>
-    <row r="543" spans="1:8">
+    <row r="543" spans="1:8" ht="13.2">
       <c r="A543" s="19"/>
       <c r="H543" s="20"/>
     </row>
-    <row r="544" spans="1:8">
+    <row r="544" spans="1:8" ht="13.2">
       <c r="A544" s="19"/>
       <c r="H544" s="20"/>
     </row>
-    <row r="545" spans="1:8">
+    <row r="545" spans="1:8" ht="13.2">
       <c r="A545" s="19"/>
       <c r="H545" s="20"/>
     </row>
-    <row r="546" spans="1:8">
+    <row r="546" spans="1:8" ht="13.2">
       <c r="A546" s="19"/>
       <c r="H546" s="20"/>
     </row>
-    <row r="547" spans="1:8">
+    <row r="547" spans="1:8" ht="13.2">
       <c r="A547" s="19"/>
       <c r="H547" s="20"/>
     </row>
-    <row r="548" spans="1:8">
+    <row r="548" spans="1:8" ht="13.2">
       <c r="A548" s="19"/>
       <c r="H548" s="20"/>
     </row>
-    <row r="549" spans="1:8">
+    <row r="549" spans="1:8" ht="13.2">
       <c r="A549" s="19"/>
       <c r="H549" s="20"/>
     </row>
-    <row r="550" spans="1:8">
+    <row r="550" spans="1:8" ht="13.2">
       <c r="A550" s="19"/>
       <c r="H550" s="20"/>
     </row>
-    <row r="551" spans="1:8">
+    <row r="551" spans="1:8" ht="13.2">
       <c r="A551" s="19"/>
       <c r="H551" s="20"/>
     </row>
-    <row r="552" spans="1:8">
+    <row r="552" spans="1:8" ht="13.2">
       <c r="A552" s="19"/>
       <c r="H552" s="20"/>
     </row>
-    <row r="553" spans="1:8">
+    <row r="553" spans="1:8" ht="13.2">
       <c r="A553" s="19"/>
       <c r="H553" s="20"/>
     </row>
-    <row r="554" spans="1:8">
+    <row r="554" spans="1:8" ht="13.2">
       <c r="A554" s="19"/>
       <c r="H554" s="20"/>
     </row>
-    <row r="555" spans="1:8">
+    <row r="555" spans="1:8" ht="13.2">
       <c r="A555" s="19"/>
       <c r="H555" s="20"/>
     </row>
-    <row r="556" spans="1:8">
+    <row r="556" spans="1:8" ht="13.2">
       <c r="A556" s="19"/>
       <c r="H556" s="20"/>
     </row>
-    <row r="557" spans="1:8">
+    <row r="557" spans="1:8" ht="13.2">
       <c r="A557" s="19"/>
       <c r="H557" s="20"/>
     </row>
-    <row r="558" spans="1:8">
+    <row r="558" spans="1:8" ht="13.2">
       <c r="A558" s="19"/>
       <c r="H558" s="20"/>
     </row>
-    <row r="559" spans="1:8">
+    <row r="559" spans="1:8" ht="13.2">
       <c r="A559" s="19"/>
       <c r="H559" s="20"/>
     </row>
-    <row r="560" spans="1:8">
+    <row r="560" spans="1:8" ht="13.2">
       <c r="A560" s="19"/>
       <c r="H560" s="20"/>
     </row>
-    <row r="561" spans="1:8">
+    <row r="561" spans="1:8" ht="13.2">
       <c r="A561" s="19"/>
       <c r="H561" s="20"/>
     </row>
-    <row r="562" spans="1:8">
+    <row r="562" spans="1:8" ht="13.2">
       <c r="A562" s="19"/>
       <c r="H562" s="20"/>
     </row>
-    <row r="563" spans="1:8">
+    <row r="563" spans="1:8" ht="13.2">
       <c r="A563" s="19"/>
       <c r="H563" s="20"/>
     </row>
-    <row r="564" spans="1:8">
+    <row r="564" spans="1:8" ht="13.2">
       <c r="A564" s="19"/>
       <c r="H564" s="20"/>
     </row>
-    <row r="565" spans="1:8">
+    <row r="565" spans="1:8" ht="13.2">
       <c r="A565" s="19"/>
       <c r="H565" s="20"/>
     </row>
-    <row r="566" spans="1:8">
+    <row r="566" spans="1:8" ht="13.2">
       <c r="A566" s="19"/>
       <c r="H566" s="20"/>
     </row>
-    <row r="567" spans="1:8">
+    <row r="567" spans="1:8" ht="13.2">
       <c r="A567" s="19"/>
       <c r="H567" s="20"/>
     </row>
-    <row r="568" spans="1:8">
+    <row r="568" spans="1:8" ht="13.2">
       <c r="A568" s="19"/>
       <c r="H568" s="20"/>
     </row>
-    <row r="569" spans="1:8">
+    <row r="569" spans="1:8" ht="13.2">
       <c r="A569" s="19"/>
       <c r="H569" s="20"/>
     </row>
-    <row r="570" spans="1:8">
+    <row r="570" spans="1:8" ht="13.2">
       <c r="A570" s="19"/>
       <c r="H570" s="20"/>
     </row>
-    <row r="571" spans="1:8">
+    <row r="571" spans="1:8" ht="13.2">
       <c r="A571" s="19"/>
       <c r="H571" s="20"/>
     </row>
-    <row r="572" spans="1:8">
+    <row r="572" spans="1:8" ht="13.2">
       <c r="A572" s="19"/>
       <c r="H572" s="20"/>
     </row>
-    <row r="573" spans="1:8">
+    <row r="573" spans="1:8" ht="13.2">
       <c r="A573" s="19"/>
       <c r="H573" s="20"/>
     </row>
-    <row r="574" spans="1:8">
+    <row r="574" spans="1:8" ht="13.2">
       <c r="A574" s="19"/>
       <c r="H574" s="20"/>
     </row>
-    <row r="575" spans="1:8">
+    <row r="575" spans="1:8" ht="13.2">
       <c r="A575" s="19"/>
       <c r="H575" s="20"/>
     </row>
-    <row r="576" spans="1:8">
+    <row r="576" spans="1:8" ht="13.2">
       <c r="A576" s="19"/>
       <c r="H576" s="20"/>
     </row>
-    <row r="577" spans="1:8">
+    <row r="577" spans="1:8" ht="13.2">
       <c r="A577" s="19"/>
       <c r="H577" s="20"/>
     </row>
-    <row r="578" spans="1:8">
+    <row r="578" spans="1:8" ht="13.2">
       <c r="A578" s="19"/>
       <c r="H578" s="20"/>
     </row>
-    <row r="579" spans="1:8">
+    <row r="579" spans="1:8" ht="13.2">
       <c r="A579" s="19"/>
       <c r="H579" s="20"/>
     </row>
-    <row r="580" spans="1:8">
+    <row r="580" spans="1:8" ht="13.2">
       <c r="A580" s="19"/>
       <c r="H580" s="20"/>
     </row>
-    <row r="581" spans="1:8">
+    <row r="581" spans="1:8" ht="13.2">
       <c r="A581" s="19"/>
       <c r="H581" s="20"/>
     </row>
-    <row r="582" spans="1:8">
+    <row r="582" spans="1:8" ht="13.2">
       <c r="A582" s="19"/>
       <c r="H582" s="20"/>
     </row>
-    <row r="583" spans="1:8">
+    <row r="583" spans="1:8" ht="13.2">
       <c r="A583" s="19"/>
       <c r="H583" s="20"/>
     </row>
-    <row r="584" spans="1:8">
+    <row r="584" spans="1:8" ht="13.2">
       <c r="A584" s="19"/>
       <c r="H584" s="20"/>
     </row>
-    <row r="585" spans="1:8">
+    <row r="585" spans="1:8" ht="13.2">
       <c r="A585" s="19"/>
       <c r="H585" s="20"/>
     </row>
-    <row r="586" spans="1:8">
+    <row r="586" spans="1:8" ht="13.2">
       <c r="A586" s="19"/>
       <c r="H586" s="20"/>
     </row>
-    <row r="587" spans="1:8">
+    <row r="587" spans="1:8" ht="13.2">
       <c r="A587" s="19"/>
       <c r="H587" s="20"/>
     </row>
-    <row r="588" spans="1:8">
+    <row r="588" spans="1:8" ht="13.2">
       <c r="A588" s="19"/>
       <c r="H588" s="20"/>
     </row>
-    <row r="589" spans="1:8">
+    <row r="589" spans="1:8" ht="13.2">
       <c r="A589" s="19"/>
       <c r="H589" s="20"/>
     </row>
-    <row r="590" spans="1:8">
+    <row r="590" spans="1:8" ht="13.2">
       <c r="A590" s="19"/>
       <c r="H590" s="20"/>
     </row>
-    <row r="591" spans="1:8">
+    <row r="591" spans="1:8" ht="13.2">
       <c r="A591" s="19"/>
       <c r="H591" s="20"/>
     </row>
-    <row r="592" spans="1:8">
+    <row r="592" spans="1:8" ht="13.2">
       <c r="A592" s="19"/>
       <c r="H592" s="20"/>
     </row>
-    <row r="593" spans="1:8">
+    <row r="593" spans="1:8" ht="13.2">
       <c r="A593" s="19"/>
       <c r="H593" s="20"/>
     </row>
-    <row r="594" spans="1:8">
+    <row r="594" spans="1:8" ht="13.2">
       <c r="A594" s="19"/>
       <c r="H594" s="20"/>
     </row>
-    <row r="595" spans="1:8">
+    <row r="595" spans="1:8" ht="13.2">
       <c r="A595" s="19"/>
       <c r="H595" s="20"/>
     </row>
-    <row r="596" spans="1:8">
+    <row r="596" spans="1:8" ht="13.2">
       <c r="A596" s="19"/>
       <c r="H596" s="20"/>
     </row>
-    <row r="597" spans="1:8">
+    <row r="597" spans="1:8" ht="13.2">
       <c r="A597" s="19"/>
       <c r="H597" s="20"/>
     </row>
-    <row r="598" spans="1:8">
+    <row r="598" spans="1:8" ht="13.2">
       <c r="A598" s="19"/>
       <c r="H598" s="20"/>
     </row>
-    <row r="599" spans="1:8">
+    <row r="599" spans="1:8" ht="13.2">
       <c r="A599" s="19"/>
       <c r="H599" s="20"/>
     </row>
-    <row r="600" spans="1:8">
+    <row r="600" spans="1:8" ht="13.2">
       <c r="A600" s="19"/>
       <c r="H600" s="20"/>
     </row>
-    <row r="601" spans="1:8">
+    <row r="601" spans="1:8" ht="13.2">
       <c r="A601" s="19"/>
       <c r="H601" s="20"/>
     </row>
-    <row r="602" spans="1:8">
+    <row r="602" spans="1:8" ht="13.2">
       <c r="A602" s="19"/>
       <c r="H602" s="20"/>
     </row>
-    <row r="603" spans="1:8">
+    <row r="603" spans="1:8" ht="13.2">
       <c r="A603" s="19"/>
       <c r="H603" s="20"/>
     </row>
-    <row r="604" spans="1:8">
+    <row r="604" spans="1:8" ht="13.2">
       <c r="A604" s="19"/>
       <c r="H604" s="20"/>
     </row>
-    <row r="605" spans="1:8">
+    <row r="605" spans="1:8" ht="13.2">
       <c r="A605" s="19"/>
       <c r="H605" s="20"/>
     </row>
-    <row r="606" spans="1:8">
+    <row r="606" spans="1:8" ht="13.2">
       <c r="A606" s="19"/>
       <c r="H606" s="20"/>
     </row>
-    <row r="607" spans="1:8">
+    <row r="607" spans="1:8" ht="13.2">
       <c r="A607" s="19"/>
       <c r="H607" s="20"/>
     </row>
-    <row r="608" spans="1:8">
+    <row r="608" spans="1:8" ht="13.2">
       <c r="A608" s="19"/>
       <c r="H608" s="20"/>
     </row>
-    <row r="609" spans="1:8">
+    <row r="609" spans="1:8" ht="13.2">
       <c r="A609" s="19"/>
       <c r="H609" s="20"/>
     </row>
-    <row r="610" spans="1:8">
+    <row r="610" spans="1:8" ht="13.2">
       <c r="A610" s="19"/>
       <c r="H610" s="20"/>
     </row>
-    <row r="611" spans="1:8">
+    <row r="611" spans="1:8" ht="13.2">
       <c r="A611" s="19"/>
       <c r="H611" s="20"/>
     </row>
-    <row r="612" spans="1:8">
+    <row r="612" spans="1:8" ht="13.2">
       <c r="A612" s="19"/>
       <c r="H612" s="20"/>
     </row>
-    <row r="613" spans="1:8">
+    <row r="613" spans="1:8" ht="13.2">
       <c r="A613" s="19"/>
       <c r="H613" s="20"/>
     </row>
-    <row r="614" spans="1:8">
+    <row r="614" spans="1:8" ht="13.2">
       <c r="A614" s="19"/>
       <c r="H614" s="20"/>
     </row>
-    <row r="615" spans="1:8">
+    <row r="615" spans="1:8" ht="13.2">
       <c r="A615" s="19"/>
       <c r="H615" s="20"/>
     </row>
-    <row r="616" spans="1:8">
+    <row r="616" spans="1:8" ht="13.2">
       <c r="A616" s="19"/>
       <c r="H616" s="20"/>
     </row>
-    <row r="617" spans="1:8">
+    <row r="617" spans="1:8" ht="13.2">
       <c r="A617" s="19"/>
       <c r="H617" s="20"/>
     </row>
-    <row r="618" spans="1:8">
+    <row r="618" spans="1:8" ht="13.2">
       <c r="A618" s="19"/>
       <c r="H618" s="20"/>
     </row>
-    <row r="619" spans="1:8">
+    <row r="619" spans="1:8" ht="13.2">
       <c r="A619" s="19"/>
       <c r="H619" s="20"/>
     </row>
-    <row r="620" spans="1:8">
+    <row r="620" spans="1:8" ht="13.2">
       <c r="A620" s="19"/>
       <c r="H620" s="20"/>
     </row>
-    <row r="621" spans="1:8">
+    <row r="621" spans="1:8" ht="13.2">
       <c r="A621" s="19"/>
       <c r="H621" s="20"/>
     </row>
-    <row r="622" spans="1:8">
+    <row r="622" spans="1:8" ht="13.2">
       <c r="A622" s="19"/>
       <c r="H622" s="20"/>
     </row>
-    <row r="623" spans="1:8">
+    <row r="623" spans="1:8" ht="13.2">
       <c r="A623" s="19"/>
       <c r="H623" s="20"/>
     </row>
-    <row r="624" spans="1:8">
+    <row r="624" spans="1:8" ht="13.2">
       <c r="A624" s="19"/>
       <c r="H624" s="20"/>
     </row>
-    <row r="625" spans="1:8">
+    <row r="625" spans="1:8" ht="13.2">
       <c r="A625" s="19"/>
       <c r="H625" s="20"/>
     </row>
-    <row r="626" spans="1:8">
+    <row r="626" spans="1:8" ht="13.2">
       <c r="A626" s="19"/>
       <c r="H626" s="20"/>
     </row>
-    <row r="627" spans="1:8">
+    <row r="627" spans="1:8" ht="13.2">
       <c r="A627" s="19"/>
       <c r="H627" s="20"/>
     </row>
-    <row r="628" spans="1:8">
+    <row r="628" spans="1:8" ht="13.2">
       <c r="A628" s="19"/>
       <c r="H628" s="20"/>
     </row>
-    <row r="629" spans="1:8">
+    <row r="629" spans="1:8" ht="13.2">
       <c r="A629" s="19"/>
       <c r="H629" s="20"/>
     </row>
-    <row r="630" spans="1:8">
+    <row r="630" spans="1:8" ht="13.2">
       <c r="A630" s="19"/>
       <c r="H630" s="20"/>
     </row>
-    <row r="631" spans="1:8">
+    <row r="631" spans="1:8" ht="13.2">
       <c r="A631" s="19"/>
       <c r="H631" s="20"/>
     </row>
-    <row r="632" spans="1:8">
+    <row r="632" spans="1:8" ht="13.2">
       <c r="A632" s="19"/>
       <c r="H632" s="20"/>
     </row>
-    <row r="633" spans="1:8">
+    <row r="633" spans="1:8" ht="13.2">
       <c r="A633" s="19"/>
       <c r="H633" s="20"/>
     </row>
-    <row r="634" spans="1:8">
+    <row r="634" spans="1:8" ht="13.2">
       <c r="A634" s="19"/>
       <c r="H634" s="20"/>
     </row>
-    <row r="635" spans="1:8">
+    <row r="635" spans="1:8" ht="13.2">
       <c r="A635" s="19"/>
       <c r="H635" s="20"/>
     </row>
-    <row r="636" spans="1:8">
+    <row r="636" spans="1:8" ht="13.2">
       <c r="A636" s="19"/>
       <c r="H636" s="20"/>
     </row>
-    <row r="637" spans="1:8">
+    <row r="637" spans="1:8" ht="13.2">
       <c r="A637" s="19"/>
       <c r="H637" s="20"/>
     </row>
-    <row r="638" spans="1:8">
+    <row r="638" spans="1:8" ht="13.2">
       <c r="A638" s="19"/>
       <c r="H638" s="20"/>
     </row>
-    <row r="639" spans="1:8">
+    <row r="639" spans="1:8" ht="13.2">
       <c r="A639" s="19"/>
       <c r="H639" s="20"/>
     </row>
-    <row r="640" spans="1:8">
+    <row r="640" spans="1:8" ht="13.2">
       <c r="A640" s="19"/>
       <c r="H640" s="20"/>
     </row>
-    <row r="641" spans="1:8">
+    <row r="641" spans="1:8" ht="13.2">
       <c r="A641" s="19"/>
       <c r="H641" s="20"/>
     </row>
-    <row r="642" spans="1:8">
+    <row r="642" spans="1:8" ht="13.2">
       <c r="A642" s="19"/>
       <c r="H642" s="20"/>
     </row>
-    <row r="643" spans="1:8">
+    <row r="643" spans="1:8" ht="13.2">
       <c r="A643" s="19"/>
       <c r="H643" s="20"/>
     </row>
-    <row r="644" spans="1:8">
+    <row r="644" spans="1:8" ht="13.2">
       <c r="A644" s="19"/>
       <c r="H644" s="20"/>
     </row>
-    <row r="645" spans="1:8">
+    <row r="645" spans="1:8" ht="13.2">
       <c r="A645" s="19"/>
       <c r="H645" s="20"/>
     </row>
-    <row r="646" spans="1:8">
+    <row r="646" spans="1:8" ht="13.2">
       <c r="A646" s="19"/>
       <c r="H646" s="20"/>
     </row>
-    <row r="647" spans="1:8">
+    <row r="647" spans="1:8" ht="13.2">
       <c r="A647" s="19"/>
       <c r="H647" s="20"/>
     </row>
-    <row r="648" spans="1:8">
+    <row r="648" spans="1:8" ht="13.2">
       <c r="A648" s="19"/>
       <c r="H648" s="20"/>
     </row>
-    <row r="649" spans="1:8">
+    <row r="649" spans="1:8" ht="13.2">
       <c r="A649" s="19"/>
       <c r="H649" s="20"/>
     </row>
-    <row r="650" spans="1:8">
+    <row r="650" spans="1:8" ht="13.2">
       <c r="A650" s="19"/>
       <c r="H650" s="20"/>
     </row>
-    <row r="651" spans="1:8">
+    <row r="651" spans="1:8" ht="13.2">
       <c r="A651" s="19"/>
       <c r="H651" s="20"/>
     </row>
-    <row r="652" spans="1:8">
+    <row r="652" spans="1:8" ht="13.2">
       <c r="A652" s="19"/>
       <c r="H652" s="20"/>
     </row>
-    <row r="653" spans="1:8">
+    <row r="653" spans="1:8" ht="13.2">
       <c r="A653" s="19"/>
       <c r="H653" s="20"/>
     </row>
-    <row r="654" spans="1:8">
+    <row r="654" spans="1:8" ht="13.2">
       <c r="A654" s="19"/>
       <c r="H654" s="20"/>
     </row>
-    <row r="655" spans="1:8">
+    <row r="655" spans="1:8" ht="13.2">
       <c r="A655" s="19"/>
       <c r="H655" s="20"/>
     </row>
-    <row r="656" spans="1:8">
+    <row r="656" spans="1:8" ht="13.2">
       <c r="A656" s="19"/>
       <c r="H656" s="20"/>
     </row>
-    <row r="657" spans="1:8">
+    <row r="657" spans="1:8" ht="13.2">
       <c r="A657" s="19"/>
       <c r="H657" s="20"/>
     </row>
-    <row r="658" spans="1:8">
+    <row r="658" spans="1:8" ht="13.2">
       <c r="A658" s="19"/>
       <c r="H658" s="20"/>
     </row>
-    <row r="659" spans="1:8">
+    <row r="659" spans="1:8" ht="13.2">
       <c r="A659" s="19"/>
       <c r="H659" s="20"/>
     </row>
-    <row r="660" spans="1:8">
+    <row r="660" spans="1:8" ht="13.2">
       <c r="A660" s="19"/>
       <c r="H660" s="20"/>
     </row>
-    <row r="661" spans="1:8">
+    <row r="661" spans="1:8" ht="13.2">
       <c r="A661" s="19"/>
       <c r="H661" s="20"/>
     </row>
-    <row r="662" spans="1:8">
+    <row r="662" spans="1:8" ht="13.2">
       <c r="A662" s="19"/>
       <c r="H662" s="20"/>
     </row>
-    <row r="663" spans="1:8">
+    <row r="663" spans="1:8" ht="13.2">
       <c r="A663" s="19"/>
       <c r="H663" s="20"/>
     </row>
-    <row r="664" spans="1:8">
+    <row r="664" spans="1:8" ht="13.2">
       <c r="A664" s="19"/>
       <c r="H664" s="20"/>
     </row>
-    <row r="665" spans="1:8">
+    <row r="665" spans="1:8" ht="13.2">
       <c r="A665" s="19"/>
       <c r="H665" s="20"/>
     </row>
-    <row r="666" spans="1:8">
+    <row r="666" spans="1:8" ht="13.2">
       <c r="A666" s="19"/>
       <c r="H666" s="20"/>
     </row>
-    <row r="667" spans="1:8">
+    <row r="667" spans="1:8" ht="13.2">
       <c r="A667" s="19"/>
       <c r="H667" s="20"/>
     </row>
-    <row r="668" spans="1:8">
+    <row r="668" spans="1:8" ht="13.2">
       <c r="A668" s="19"/>
       <c r="H668" s="20"/>
     </row>
-    <row r="669" spans="1:8">
+    <row r="669" spans="1:8" ht="13.2">
       <c r="A669" s="19"/>
       <c r="H669" s="20"/>
     </row>
-    <row r="670" spans="1:8">
+    <row r="670" spans="1:8" ht="13.2">
       <c r="A670" s="19"/>
       <c r="H670" s="20"/>
     </row>
-    <row r="671" spans="1:8">
+    <row r="671" spans="1:8" ht="13.2">
       <c r="A671" s="19"/>
       <c r="H671" s="20"/>
     </row>
-    <row r="672" spans="1:8">
+    <row r="672" spans="1:8" ht="13.2">
       <c r="A672" s="19"/>
       <c r="H672" s="20"/>
     </row>
-    <row r="673" spans="1:8">
+    <row r="673" spans="1:8" ht="13.2">
       <c r="A673" s="19"/>
       <c r="H673" s="20"/>
     </row>
-    <row r="674" spans="1:8">
+    <row r="674" spans="1:8" ht="13.2">
       <c r="A674" s="19"/>
       <c r="H674" s="20"/>
     </row>
-    <row r="675" spans="1:8">
+    <row r="675" spans="1:8" ht="13.2">
       <c r="A675" s="19"/>
       <c r="H675" s="20"/>
     </row>
-    <row r="676" spans="1:8">
+    <row r="676" spans="1:8" ht="13.2">
       <c r="A676" s="19"/>
       <c r="H676" s="20"/>
     </row>
-    <row r="677" spans="1:8">
+    <row r="677" spans="1:8" ht="13.2">
       <c r="A677" s="19"/>
       <c r="H677" s="20"/>
     </row>
-    <row r="678" spans="1:8">
+    <row r="678" spans="1:8" ht="13.2">
       <c r="A678" s="19"/>
       <c r="H678" s="20"/>
     </row>
-    <row r="679" spans="1:8">
+    <row r="679" spans="1:8" ht="13.2">
       <c r="A679" s="19"/>
       <c r="H679" s="20"/>
     </row>
-    <row r="680" spans="1:8">
+    <row r="680" spans="1:8" ht="13.2">
       <c r="A680" s="19"/>
       <c r="H680" s="20"/>
     </row>
-    <row r="681" spans="1:8">
+    <row r="681" spans="1:8" ht="13.2">
       <c r="A681" s="19"/>
       <c r="H681" s="20"/>
     </row>
-    <row r="682" spans="1:8">
+    <row r="682" spans="1:8" ht="13.2">
       <c r="A682" s="19"/>
       <c r="H682" s="20"/>
     </row>
-    <row r="683" spans="1:8">
+    <row r="683" spans="1:8" ht="13.2">
       <c r="A683" s="19"/>
       <c r="H683" s="20"/>
     </row>
-    <row r="684" spans="1:8">
+    <row r="684" spans="1:8" ht="13.2">
       <c r="A684" s="19"/>
       <c r="H684" s="20"/>
     </row>
-    <row r="685" spans="1:8">
+    <row r="685" spans="1:8" ht="13.2">
       <c r="A685" s="19"/>
       <c r="H685" s="20"/>
     </row>
-    <row r="686" spans="1:8">
+    <row r="686" spans="1:8" ht="13.2">
       <c r="A686" s="19"/>
       <c r="H686" s="20"/>
     </row>
-    <row r="687" spans="1:8">
+    <row r="687" spans="1:8" ht="13.2">
       <c r="A687" s="19"/>
       <c r="H687" s="20"/>
     </row>
-    <row r="688" spans="1:8">
+    <row r="688" spans="1:8" ht="13.2">
       <c r="A688" s="19"/>
       <c r="H688" s="20"/>
     </row>
-    <row r="689" spans="1:8">
+    <row r="689" spans="1:8" ht="13.2">
       <c r="A689" s="19"/>
       <c r="H689" s="20"/>
     </row>
-    <row r="690" spans="1:8">
+    <row r="690" spans="1:8" ht="13.2">
       <c r="A690" s="19"/>
       <c r="H690" s="20"/>
     </row>
-    <row r="691" spans="1:8">
+    <row r="691" spans="1:8" ht="13.2">
       <c r="A691" s="19"/>
       <c r="H691" s="20"/>
     </row>
-    <row r="692" spans="1:8">
+    <row r="692" spans="1:8" ht="13.2">
       <c r="A692" s="19"/>
       <c r="H692" s="20"/>
     </row>
-    <row r="693" spans="1:8">
+    <row r="693" spans="1:8" ht="13.2">
       <c r="A693" s="19"/>
       <c r="H693" s="20"/>
     </row>
-    <row r="694" spans="1:8">
+    <row r="694" spans="1:8" ht="13.2">
       <c r="A694" s="19"/>
       <c r="H694" s="20"/>
     </row>
-    <row r="695" spans="1:8">
+    <row r="695" spans="1:8" ht="13.2">
       <c r="A695" s="19"/>
       <c r="H695" s="20"/>
     </row>
-    <row r="696" spans="1:8">
+    <row r="696" spans="1:8" ht="13.2">
       <c r="A696" s="19"/>
       <c r="H696" s="20"/>
     </row>
-    <row r="697" spans="1:8">
+    <row r="697" spans="1:8" ht="13.2">
       <c r="A697" s="19"/>
       <c r="H697" s="20"/>
     </row>
-    <row r="698" spans="1:8">
+    <row r="698" spans="1:8" ht="13.2">
       <c r="A698" s="19"/>
       <c r="H698" s="20"/>
     </row>
-    <row r="699" spans="1:8">
+    <row r="699" spans="1:8" ht="13.2">
       <c r="A699" s="19"/>
       <c r="H699" s="20"/>
     </row>
-    <row r="700" spans="1:8">
+    <row r="700" spans="1:8" ht="13.2">
       <c r="A700" s="19"/>
       <c r="H700" s="20"/>
     </row>
-    <row r="701" spans="1:8">
+    <row r="701" spans="1:8" ht="13.2">
       <c r="A701" s="19"/>
       <c r="H701" s="20"/>
     </row>
-    <row r="702" spans="1:8">
+    <row r="702" spans="1:8" ht="13.2">
       <c r="A702" s="19"/>
       <c r="H702" s="20"/>
     </row>
-    <row r="703" spans="1:8">
+    <row r="703" spans="1:8" ht="13.2">
       <c r="A703" s="19"/>
       <c r="H703" s="20"/>
     </row>
-    <row r="704" spans="1:8">
+    <row r="704" spans="1:8" ht="13.2">
       <c r="A704" s="19"/>
       <c r="H704" s="20"/>
     </row>
-    <row r="705" spans="1:8">
+    <row r="705" spans="1:8" ht="13.2">
       <c r="A705" s="19"/>
       <c r="H705" s="20"/>
     </row>
-    <row r="706" spans="1:8">
+    <row r="706" spans="1:8" ht="13.2">
       <c r="A706" s="19"/>
       <c r="H706" s="20"/>
     </row>
-    <row r="707" spans="1:8">
+    <row r="707" spans="1:8" ht="13.2">
       <c r="A707" s="19"/>
       <c r="H707" s="20"/>
     </row>
-    <row r="708" spans="1:8">
+    <row r="708" spans="1:8" ht="13.2">
       <c r="A708" s="19"/>
       <c r="H708" s="20"/>
     </row>
-    <row r="709" spans="1:8">
+    <row r="709" spans="1:8" ht="13.2">
       <c r="A709" s="19"/>
       <c r="H709" s="20"/>
     </row>
-    <row r="710" spans="1:8">
+    <row r="710" spans="1:8" ht="13.2">
       <c r="A710" s="19"/>
       <c r="H710" s="20"/>
     </row>
-    <row r="711" spans="1:8">
+    <row r="711" spans="1:8" ht="13.2">
       <c r="A711" s="19"/>
       <c r="H711" s="20"/>
     </row>
-    <row r="712" spans="1:8">
+    <row r="712" spans="1:8" ht="13.2">
       <c r="A712" s="19"/>
       <c r="H712" s="20"/>
     </row>
-    <row r="713" spans="1:8">
+    <row r="713" spans="1:8" ht="13.2">
       <c r="A713" s="19"/>
       <c r="H713" s="20"/>
     </row>
-    <row r="714" spans="1:8">
+    <row r="714" spans="1:8" ht="13.2">
       <c r="A714" s="19"/>
       <c r="H714" s="20"/>
     </row>
-    <row r="715" spans="1:8">
+    <row r="715" spans="1:8" ht="13.2">
       <c r="A715" s="19"/>
       <c r="H715" s="20"/>
     </row>
-    <row r="716" spans="1:8">
+    <row r="716" spans="1:8" ht="13.2">
       <c r="A716" s="19"/>
       <c r="H716" s="20"/>
     </row>
-    <row r="717" spans="1:8">
+    <row r="717" spans="1:8" ht="13.2">
       <c r="A717" s="19"/>
       <c r="H717" s="20"/>
     </row>
-    <row r="718" spans="1:8">
+    <row r="718" spans="1:8" ht="13.2">
       <c r="A718" s="19"/>
       <c r="H718" s="20"/>
     </row>
-    <row r="719" spans="1:8">
+    <row r="719" spans="1:8" ht="13.2">
       <c r="A719" s="19"/>
       <c r="H719" s="20"/>
     </row>
-    <row r="720" spans="1:8">
+    <row r="720" spans="1:8" ht="13.2">
       <c r="A720" s="19"/>
       <c r="H720" s="20"/>
     </row>
-    <row r="721" spans="1:8">
+    <row r="721" spans="1:8" ht="13.2">
       <c r="A721" s="19"/>
       <c r="H721" s="20"/>
     </row>
-    <row r="722" spans="1:8">
+    <row r="722" spans="1:8" ht="13.2">
       <c r="A722" s="19"/>
       <c r="H722" s="20"/>
     </row>
-    <row r="723" spans="1:8">
+    <row r="723" spans="1:8" ht="13.2">
       <c r="A723" s="19"/>
       <c r="H723" s="20"/>
     </row>
-    <row r="724" spans="1:8">
+    <row r="724" spans="1:8" ht="13.2">
       <c r="A724" s="19"/>
       <c r="H724" s="20"/>
     </row>
-    <row r="725" spans="1:8">
+    <row r="725" spans="1:8" ht="13.2">
       <c r="A725" s="19"/>
       <c r="H725" s="20"/>
     </row>
-    <row r="726" spans="1:8">
+    <row r="726" spans="1:8" ht="13.2">
       <c r="A726" s="19"/>
       <c r="H726" s="20"/>
     </row>
-    <row r="727" spans="1:8">
+    <row r="727" spans="1:8" ht="13.2">
       <c r="A727" s="19"/>
       <c r="H727" s="20"/>
     </row>
-    <row r="728" spans="1:8">
+    <row r="728" spans="1:8" ht="13.2">
       <c r="A728" s="19"/>
       <c r="H728" s="20"/>
     </row>
-    <row r="729" spans="1:8">
+    <row r="729" spans="1:8" ht="13.2">
       <c r="A729" s="19"/>
       <c r="H729" s="20"/>
     </row>
-    <row r="730" spans="1:8">
+    <row r="730" spans="1:8" ht="13.2">
       <c r="A730" s="19"/>
       <c r="H730" s="20"/>
     </row>
-    <row r="731" spans="1:8">
+    <row r="731" spans="1:8" ht="13.2">
       <c r="A731" s="19"/>
       <c r="H731" s="20"/>
     </row>
-    <row r="732" spans="1:8">
+    <row r="732" spans="1:8" ht="13.2">
       <c r="A732" s="19"/>
       <c r="H732" s="20"/>
     </row>
-    <row r="733" spans="1:8">
+    <row r="733" spans="1:8" ht="13.2">
       <c r="A733" s="19"/>
       <c r="H733" s="20"/>
     </row>
-    <row r="734" spans="1:8">
+    <row r="734" spans="1:8" ht="13.2">
       <c r="A734" s="19"/>
       <c r="H734" s="20"/>
     </row>
-    <row r="735" spans="1:8">
+    <row r="735" spans="1:8" ht="13.2">
       <c r="A735" s="19"/>
       <c r="H735" s="20"/>
     </row>
-    <row r="736" spans="1:8">
+    <row r="736" spans="1:8" ht="13.2">
       <c r="A736" s="19"/>
       <c r="H736" s="20"/>
     </row>
-    <row r="737" spans="1:8">
+    <row r="737" spans="1:8" ht="13.2">
       <c r="A737" s="19"/>
       <c r="H737" s="20"/>
     </row>
-    <row r="738" spans="1:8">
+    <row r="738" spans="1:8" ht="13.2">
       <c r="A738" s="19"/>
       <c r="H738" s="20"/>
     </row>
-    <row r="739" spans="1:8">
+    <row r="739" spans="1:8" ht="13.2">
       <c r="A739" s="19"/>
       <c r="H739" s="20"/>
     </row>
-    <row r="740" spans="1:8">
+    <row r="740" spans="1:8" ht="13.2">
       <c r="A740" s="19"/>
       <c r="H740" s="20"/>
     </row>
-    <row r="741" spans="1:8">
+    <row r="741" spans="1:8" ht="13.2">
       <c r="A741" s="19"/>
       <c r="H741" s="20"/>
     </row>
-    <row r="742" spans="1:8">
+    <row r="742" spans="1:8" ht="13.2">
       <c r="A742" s="19"/>
       <c r="H742" s="20"/>
     </row>
-    <row r="743" spans="1:8">
+    <row r="743" spans="1:8" ht="13.2">
       <c r="A743" s="19"/>
       <c r="H743" s="20"/>
     </row>
-    <row r="744" spans="1:8">
+    <row r="744" spans="1:8" ht="13.2">
       <c r="A744" s="19"/>
       <c r="H744" s="20"/>
     </row>
-    <row r="745" spans="1:8">
+    <row r="745" spans="1:8" ht="13.2">
       <c r="A745" s="19"/>
       <c r="H745" s="20"/>
     </row>
-    <row r="746" spans="1:8">
+    <row r="746" spans="1:8" ht="13.2">
       <c r="A746" s="19"/>
       <c r="H746" s="20"/>
     </row>
-    <row r="747" spans="1:8">
+    <row r="747" spans="1:8" ht="13.2">
       <c r="A747" s="19"/>
       <c r="H747" s="20"/>
     </row>
-    <row r="748" spans="1:8">
+    <row r="748" spans="1:8" ht="13.2">
       <c r="A748" s="19"/>
       <c r="H748" s="20"/>
     </row>
-    <row r="749" spans="1:8">
+    <row r="749" spans="1:8" ht="13.2">
       <c r="A749" s="19"/>
       <c r="H749" s="20"/>
     </row>
-    <row r="750" spans="1:8">
+    <row r="750" spans="1:8" ht="13.2">
       <c r="A750" s="19"/>
       <c r="H750" s="20"/>
     </row>
-    <row r="751" spans="1:8">
+    <row r="751" spans="1:8" ht="13.2">
       <c r="A751" s="19"/>
       <c r="H751" s="20"/>
     </row>
-    <row r="752" spans="1:8">
+    <row r="752" spans="1:8" ht="13.2">
       <c r="A752" s="19"/>
       <c r="H752" s="20"/>
     </row>
-    <row r="753" spans="1:8">
+    <row r="753" spans="1:8" ht="13.2">
       <c r="A753" s="19"/>
       <c r="H753" s="20"/>
     </row>
-    <row r="754" spans="1:8">
+    <row r="754" spans="1:8" ht="13.2">
       <c r="A754" s="19"/>
       <c r="H754" s="20"/>
     </row>
-    <row r="755" spans="1:8">
+    <row r="755" spans="1:8" ht="13.2">
       <c r="A755" s="19"/>
       <c r="H755" s="20"/>
     </row>
-    <row r="756" spans="1:8">
+    <row r="756" spans="1:8" ht="13.2">
       <c r="A756" s="19"/>
       <c r="H756" s="20"/>
     </row>
-    <row r="757" spans="1:8">
+    <row r="757" spans="1:8" ht="13.2">
       <c r="A757" s="19"/>
       <c r="H757" s="20"/>
     </row>
-    <row r="758" spans="1:8">
+    <row r="758" spans="1:8" ht="13.2">
       <c r="A758" s="19"/>
       <c r="H758" s="20"/>
     </row>
-    <row r="759" spans="1:8">
+    <row r="759" spans="1:8" ht="13.2">
       <c r="A759" s="19"/>
       <c r="H759" s="20"/>
     </row>
-    <row r="760" spans="1:8">
+    <row r="760" spans="1:8" ht="13.2">
       <c r="A760" s="19"/>
       <c r="H760" s="20"/>
     </row>
-    <row r="761" spans="1:8">
+    <row r="761" spans="1:8" ht="13.2">
       <c r="A761" s="19"/>
       <c r="H761" s="20"/>
     </row>
-    <row r="762" spans="1:8">
+    <row r="762" spans="1:8" ht="13.2">
       <c r="A762" s="19"/>
       <c r="H762" s="20"/>
     </row>
-    <row r="763" spans="1:8">
+    <row r="763" spans="1:8" ht="13.2">
       <c r="A763" s="19"/>
       <c r="H763" s="20"/>
     </row>
-    <row r="764" spans="1:8">
+    <row r="764" spans="1:8" ht="13.2">
       <c r="A764" s="19"/>
       <c r="H764" s="20"/>
     </row>
-    <row r="765" spans="1:8">
+    <row r="765" spans="1:8" ht="13.2">
       <c r="A765" s="19"/>
       <c r="H765" s="20"/>
     </row>
-    <row r="766" spans="1:8">
+    <row r="766" spans="1:8" ht="13.2">
       <c r="A766" s="19"/>
       <c r="H766" s="20"/>
     </row>
-    <row r="767" spans="1:8">
+    <row r="767" spans="1:8" ht="13.2">
       <c r="A767" s="19"/>
       <c r="H767" s="20"/>
     </row>
-    <row r="768" spans="1:8">
+    <row r="768" spans="1:8" ht="13.2">
       <c r="A768" s="19"/>
       <c r="H768" s="20"/>
     </row>
-    <row r="769" spans="1:8">
+    <row r="769" spans="1:8" ht="13.2">
       <c r="A769" s="19"/>
       <c r="H769" s="20"/>
     </row>
-    <row r="770" spans="1:8">
+    <row r="770" spans="1:8" ht="13.2">
       <c r="A770" s="19"/>
       <c r="H770" s="20"/>
     </row>
-    <row r="771" spans="1:8">
+    <row r="771" spans="1:8" ht="13.2">
       <c r="A771" s="19"/>
       <c r="H771" s="20"/>
     </row>
-    <row r="772" spans="1:8">
+    <row r="772" spans="1:8" ht="13.2">
       <c r="A772" s="19"/>
       <c r="H772" s="20"/>
     </row>
-    <row r="773" spans="1:8">
+    <row r="773" spans="1:8" ht="13.2">
       <c r="A773" s="19"/>
       <c r="H773" s="20"/>
     </row>
-    <row r="774" spans="1:8">
+    <row r="774" spans="1:8" ht="13.2">
       <c r="A774" s="19"/>
       <c r="H774" s="20"/>
     </row>
-    <row r="775" spans="1:8">
+    <row r="775" spans="1:8" ht="13.2">
       <c r="A775" s="19"/>
       <c r="H775" s="20"/>
     </row>
-    <row r="776" spans="1:8">
+    <row r="776" spans="1:8" ht="13.2">
       <c r="A776" s="19"/>
       <c r="H776" s="20"/>
     </row>
-    <row r="777" spans="1:8">
+    <row r="777" spans="1:8" ht="13.2">
       <c r="A777" s="19"/>
       <c r="H777" s="20"/>
     </row>
-    <row r="778" spans="1:8">
+    <row r="778" spans="1:8" ht="13.2">
       <c r="A778" s="19"/>
       <c r="H778" s="20"/>
     </row>
-    <row r="779" spans="1:8">
+    <row r="779" spans="1:8" ht="13.2">
       <c r="A779" s="19"/>
       <c r="H779" s="20"/>
     </row>
-    <row r="780" spans="1:8">
+    <row r="780" spans="1:8" ht="13.2">
       <c r="A780" s="19"/>
       <c r="H780" s="20"/>
     </row>
-    <row r="781" spans="1:8">
+    <row r="781" spans="1:8" ht="13.2">
       <c r="A781" s="19"/>
       <c r="H781" s="20"/>
     </row>
-    <row r="782" spans="1:8">
+    <row r="782" spans="1:8" ht="13.2">
       <c r="A782" s="19"/>
       <c r="H782" s="20"/>
     </row>
-    <row r="783" spans="1:8">
+    <row r="783" spans="1:8" ht="13.2">
       <c r="A783" s="19"/>
       <c r="H783" s="20"/>
     </row>
-    <row r="784" spans="1:8">
+    <row r="784" spans="1:8" ht="13.2">
       <c r="A784" s="19"/>
       <c r="H784" s="20"/>
     </row>
-    <row r="785" spans="1:8">
+    <row r="785" spans="1:8" ht="13.2">
       <c r="A785" s="19"/>
       <c r="H785" s="20"/>
     </row>
-    <row r="786" spans="1:8">
+    <row r="786" spans="1:8" ht="13.2">
       <c r="A786" s="19"/>
       <c r="H786" s="20"/>
     </row>
-    <row r="787" spans="1:8">
+    <row r="787" spans="1:8" ht="13.2">
       <c r="A787" s="19"/>
       <c r="H787" s="20"/>
     </row>
-    <row r="788" spans="1:8">
+    <row r="788" spans="1:8" ht="13.2">
       <c r="A788" s="19"/>
       <c r="H788" s="20"/>
     </row>
-    <row r="789" spans="1:8">
+    <row r="789" spans="1:8" ht="13.2">
       <c r="A789" s="19"/>
       <c r="H789" s="20"/>
     </row>
-    <row r="790" spans="1:8">
+    <row r="790" spans="1:8" ht="13.2">
       <c r="A790" s="19"/>
       <c r="H790" s="20"/>
     </row>
-    <row r="791" spans="1:8">
+    <row r="791" spans="1:8" ht="13.2">
       <c r="A791" s="19"/>
       <c r="H791" s="20"/>
     </row>
-    <row r="792" spans="1:8">
+    <row r="792" spans="1:8" ht="13.2">
       <c r="A792" s="19"/>
       <c r="H792" s="20"/>
     </row>
-    <row r="793" spans="1:8">
+    <row r="793" spans="1:8" ht="13.2">
       <c r="A793" s="19"/>
       <c r="H793" s="20"/>
     </row>
-    <row r="794" spans="1:8">
+    <row r="794" spans="1:8" ht="13.2">
       <c r="A794" s="19"/>
       <c r="H794" s="20"/>
     </row>
-    <row r="795" spans="1:8">
+    <row r="795" spans="1:8" ht="13.2">
       <c r="A795" s="19"/>
       <c r="H795" s="20"/>
     </row>
-    <row r="796" spans="1:8">
+    <row r="796" spans="1:8" ht="13.2">
       <c r="A796" s="19"/>
       <c r="H796" s="20"/>
     </row>
-    <row r="797" spans="1:8">
+    <row r="797" spans="1:8" ht="13.2">
       <c r="A797" s="19"/>
       <c r="H797" s="20"/>
     </row>
-    <row r="798" spans="1:8">
+    <row r="798" spans="1:8" ht="13.2">
       <c r="A798" s="19"/>
       <c r="H798" s="20"/>
     </row>
-    <row r="799" spans="1:8">
+    <row r="799" spans="1:8" ht="13.2">
       <c r="A799" s="19"/>
       <c r="H799" s="20"/>
     </row>
-    <row r="800" spans="1:8">
+    <row r="800" spans="1:8" ht="13.2">
       <c r="A800" s="19"/>
       <c r="H800" s="20"/>
     </row>
-    <row r="801" spans="1:8">
+    <row r="801" spans="1:8" ht="13.2">
       <c r="A801" s="19"/>
       <c r="H801" s="20"/>
     </row>
-    <row r="802" spans="1:8">
+    <row r="802" spans="1:8" ht="13.2">
       <c r="A802" s="19"/>
       <c r="H802" s="20"/>
     </row>
-    <row r="803" spans="1:8">
+    <row r="803" spans="1:8" ht="13.2">
       <c r="A803" s="19"/>
       <c r="H803" s="20"/>
     </row>
-    <row r="804" spans="1:8">
+    <row r="804" spans="1:8" ht="13.2">
       <c r="A804" s="19"/>
       <c r="H804" s="20"/>
     </row>
-    <row r="805" spans="1:8">
+    <row r="805" spans="1:8" ht="13.2">
       <c r="A805" s="19"/>
       <c r="H805" s="20"/>
     </row>
-    <row r="806" spans="1:8">
+    <row r="806" spans="1:8" ht="13.2">
       <c r="A806" s="19"/>
       <c r="H806" s="20"/>
     </row>
-    <row r="807" spans="1:8">
+    <row r="807" spans="1:8" ht="13.2">
       <c r="A807" s="19"/>
       <c r="H807" s="20"/>
     </row>
-    <row r="808" spans="1:8">
+    <row r="808" spans="1:8" ht="13.2">
       <c r="A808" s="19"/>
       <c r="H808" s="20"/>
     </row>
-    <row r="809" spans="1:8">
+    <row r="809" spans="1:8" ht="13.2">
       <c r="A809" s="19"/>
       <c r="H809" s="20"/>
     </row>
-    <row r="810" spans="1:8">
+    <row r="810" spans="1:8" ht="13.2">
       <c r="A810" s="19"/>
       <c r="H810" s="20"/>
     </row>
-    <row r="811" spans="1:8">
+    <row r="811" spans="1:8" ht="13.2">
       <c r="A811" s="19"/>
       <c r="H811" s="20"/>
     </row>
-    <row r="812" spans="1:8">
+    <row r="812" spans="1:8" ht="13.2">
       <c r="A812" s="19"/>
       <c r="H812" s="20"/>
     </row>
-    <row r="813" spans="1:8">
+    <row r="813" spans="1:8" ht="13.2">
       <c r="A813" s="19"/>
       <c r="H813" s="20"/>
     </row>
-    <row r="814" spans="1:8">
+    <row r="814" spans="1:8" ht="13.2">
       <c r="A814" s="19"/>
       <c r="H814" s="20"/>
     </row>
-    <row r="815" spans="1:8">
+    <row r="815" spans="1:8" ht="13.2">
       <c r="A815" s="19"/>
       <c r="H815" s="20"/>
     </row>
-    <row r="816" spans="1:8">
+    <row r="816" spans="1:8" ht="13.2">
       <c r="A816" s="19"/>
       <c r="H816" s="20"/>
     </row>
-    <row r="817" spans="1:8">
+    <row r="817" spans="1:8" ht="13.2">
       <c r="A817" s="19"/>
       <c r="H817" s="20"/>
     </row>
-    <row r="818" spans="1:8">
+    <row r="818" spans="1:8" ht="13.2">
       <c r="A818" s="19"/>
       <c r="H818" s="20"/>
     </row>
-    <row r="819" spans="1:8">
+    <row r="819" spans="1:8" ht="13.2">
       <c r="A819" s="19"/>
       <c r="H819" s="20"/>
     </row>
-    <row r="820" spans="1:8">
+    <row r="820" spans="1:8" ht="13.2">
       <c r="A820" s="19"/>
       <c r="H820" s="20"/>
     </row>
-    <row r="821" spans="1:8">
+    <row r="821" spans="1:8" ht="13.2">
       <c r="A821" s="19"/>
       <c r="H821" s="20"/>
     </row>
-    <row r="822" spans="1:8">
+    <row r="822" spans="1:8" ht="13.2">
       <c r="A822" s="19"/>
       <c r="H822" s="20"/>
     </row>
-    <row r="823" spans="1:8">
+    <row r="823" spans="1:8" ht="13.2">
       <c r="A823" s="19"/>
       <c r="H823" s="20"/>
     </row>
-    <row r="824" spans="1:8">
+    <row r="824" spans="1:8" ht="13.2">
       <c r="A824" s="19"/>
       <c r="H824" s="20"/>
     </row>
-    <row r="825" spans="1:8">
+    <row r="825" spans="1:8" ht="13.2">
       <c r="A825" s="19"/>
       <c r="H825" s="20"/>
     </row>
-    <row r="826" spans="1:8">
+    <row r="826" spans="1:8" ht="13.2">
       <c r="A826" s="19"/>
       <c r="H826" s="20"/>
     </row>
-    <row r="827" spans="1:8">
+    <row r="827" spans="1:8" ht="13.2">
       <c r="A827" s="19"/>
       <c r="H827" s="20"/>
     </row>
-    <row r="828" spans="1:8">
+    <row r="828" spans="1:8" ht="13.2">
       <c r="A828" s="19"/>
       <c r="H828" s="20"/>
     </row>
-    <row r="829" spans="1:8">
+    <row r="829" spans="1:8" ht="13.2">
       <c r="A829" s="19"/>
       <c r="H829" s="20"/>
     </row>
-    <row r="830" spans="1:8">
+    <row r="830" spans="1:8" ht="13.2">
       <c r="A830" s="19"/>
       <c r="H830" s="20"/>
     </row>
-    <row r="831" spans="1:8">
+    <row r="831" spans="1:8" ht="13.2">
       <c r="A831" s="19"/>
       <c r="H831" s="20"/>
     </row>
-    <row r="832" spans="1:8">
+    <row r="832" spans="1:8" ht="13.2">
       <c r="A832" s="19"/>
       <c r="H832" s="20"/>
     </row>
-    <row r="833" spans="1:8">
+    <row r="833" spans="1:8" ht="13.2">
       <c r="A833" s="19"/>
       <c r="H833" s="20"/>
     </row>
-    <row r="834" spans="1:8">
+    <row r="834" spans="1:8" ht="13.2">
       <c r="A834" s="19"/>
       <c r="H834" s="20"/>
     </row>
-    <row r="835" spans="1:8">
+    <row r="835" spans="1:8" ht="13.2">
       <c r="A835" s="19"/>
       <c r="H835" s="20"/>
     </row>
-    <row r="836" spans="1:8">
+    <row r="836" spans="1:8" ht="13.2">
       <c r="A836" s="19"/>
       <c r="H836" s="20"/>
     </row>
-    <row r="837" spans="1:8">
+    <row r="837" spans="1:8" ht="13.2">
       <c r="A837" s="19"/>
       <c r="H837" s="20"/>
     </row>
-    <row r="838" spans="1:8">
+    <row r="838" spans="1:8" ht="13.2">
       <c r="A838" s="19"/>
       <c r="H838" s="20"/>
     </row>
-    <row r="839" spans="1:8">
+    <row r="839" spans="1:8" ht="13.2">
       <c r="A839" s="19"/>
       <c r="H839" s="20"/>
     </row>
-    <row r="840" spans="1:8">
+    <row r="840" spans="1:8" ht="13.2">
       <c r="A840" s="19"/>
       <c r="H840" s="20"/>
     </row>
-    <row r="841" spans="1:8">
+    <row r="841" spans="1:8" ht="13.2">
       <c r="A841" s="19"/>
       <c r="H841" s="20"/>
     </row>
-    <row r="842" spans="1:8">
+    <row r="842" spans="1:8" ht="13.2">
       <c r="A842" s="19"/>
       <c r="H842" s="20"/>
     </row>
-    <row r="843" spans="1:8">
+    <row r="843" spans="1:8" ht="13.2">
       <c r="A843" s="19"/>
       <c r="H843" s="20"/>
     </row>
-    <row r="844" spans="1:8">
+    <row r="844" spans="1:8" ht="13.2">
       <c r="A844" s="19"/>
       <c r="H844" s="20"/>
     </row>
-    <row r="845" spans="1:8">
+    <row r="845" spans="1:8" ht="13.2">
       <c r="A845" s="19"/>
       <c r="H845" s="20"/>
     </row>
-    <row r="846" spans="1:8">
+    <row r="846" spans="1:8" ht="13.2">
       <c r="A846" s="19"/>
       <c r="H846" s="20"/>
     </row>
-    <row r="847" spans="1:8">
+    <row r="847" spans="1:8" ht="13.2">
       <c r="A847" s="19"/>
       <c r="H847" s="20"/>
     </row>
-    <row r="848" spans="1:8">
+    <row r="848" spans="1:8" ht="13.2">
       <c r="A848" s="19"/>
       <c r="H848" s="20"/>
     </row>
-    <row r="849" spans="1:8">
+    <row r="849" spans="1:8" ht="13.2">
       <c r="A849" s="19"/>
       <c r="H849" s="20"/>
     </row>
-    <row r="850" spans="1:8">
+    <row r="850" spans="1:8" ht="13.2">
       <c r="A850" s="19"/>
       <c r="H850" s="20"/>
     </row>
-    <row r="851" spans="1:8">
+    <row r="851" spans="1:8" ht="13.2">
       <c r="A851" s="19"/>
       <c r="H851" s="20"/>
     </row>
-    <row r="852" spans="1:8">
+    <row r="852" spans="1:8" ht="13.2">
       <c r="A852" s="19"/>
       <c r="H852" s="20"/>
     </row>
-    <row r="853" spans="1:8">
+    <row r="853" spans="1:8" ht="13.2">
       <c r="A853" s="19"/>
       <c r="H853" s="20"/>
     </row>
-    <row r="854" spans="1:8">
+    <row r="854" spans="1:8" ht="13.2">
       <c r="A854" s="19"/>
       <c r="H854" s="20"/>
     </row>
-    <row r="855" spans="1:8">
+    <row r="855" spans="1:8" ht="13.2">
       <c r="A855" s="19"/>
       <c r="H855" s="20"/>
     </row>
-    <row r="856" spans="1:8">
+    <row r="856" spans="1:8" ht="13.2">
       <c r="A856" s="19"/>
       <c r="H856" s="20"/>
     </row>
-    <row r="857" spans="1:8">
+    <row r="857" spans="1:8" ht="13.2">
       <c r="A857" s="19"/>
       <c r="H857" s="20"/>
     </row>
-    <row r="858" spans="1:8">
+    <row r="858" spans="1:8" ht="13.2">
       <c r="A858" s="19"/>
       <c r="H858" s="20"/>
     </row>
-    <row r="859" spans="1:8">
+    <row r="859" spans="1:8" ht="13.2">
       <c r="A859" s="19"/>
       <c r="H859" s="20"/>
     </row>
-    <row r="860" spans="1:8">
+    <row r="860" spans="1:8" ht="13.2">
       <c r="A860" s="19"/>
       <c r="H860" s="20"/>
     </row>
-    <row r="861" spans="1:8">
+    <row r="861" spans="1:8" ht="13.2">
       <c r="A861" s="19"/>
       <c r="H861" s="20"/>
     </row>
-    <row r="862" spans="1:8">
+    <row r="862" spans="1:8" ht="13.2">
       <c r="A862" s="19"/>
       <c r="H862" s="20"/>
     </row>
-    <row r="863" spans="1:8">
+    <row r="863" spans="1:8" ht="13.2">
       <c r="A863" s="19"/>
       <c r="H863" s="20"/>
     </row>
-    <row r="864" spans="1:8">
+    <row r="864" spans="1:8" ht="13.2">
       <c r="A864" s="19"/>
       <c r="H864" s="20"/>
     </row>
-    <row r="865" spans="1:8">
+    <row r="865" spans="1:8" ht="13.2">
       <c r="A865" s="19"/>
       <c r="H865" s="20"/>
     </row>
-    <row r="866" spans="1:8">
+    <row r="866" spans="1:8" ht="13.2">
       <c r="A866" s="19"/>
       <c r="H866" s="20"/>
     </row>
-    <row r="867" spans="1:8">
+    <row r="867" spans="1:8" ht="13.2">
       <c r="A867" s="19"/>
       <c r="H867" s="20"/>
     </row>
-    <row r="868" spans="1:8">
+    <row r="868" spans="1:8" ht="13.2">
       <c r="A868" s="19"/>
       <c r="H868" s="20"/>
     </row>
-    <row r="869" spans="1:8">
+    <row r="869" spans="1:8" ht="13.2">
       <c r="A869" s="19"/>
       <c r="H869" s="20"/>
     </row>
-    <row r="870" spans="1:8">
+    <row r="870" spans="1:8" ht="13.2">
       <c r="A870" s="19"/>
       <c r="H870" s="20"/>
     </row>
-    <row r="871" spans="1:8">
+    <row r="871" spans="1:8" ht="13.2">
       <c r="A871" s="19"/>
       <c r="H871" s="20"/>
     </row>
-    <row r="872" spans="1:8">
+    <row r="872" spans="1:8" ht="13.2">
       <c r="A872" s="19"/>
       <c r="H872" s="20"/>
     </row>
-    <row r="873" spans="1:8">
+    <row r="873" spans="1:8" ht="13.2">
       <c r="A873" s="19"/>
       <c r="H873" s="20"/>
     </row>
-    <row r="874" spans="1:8">
+    <row r="874" spans="1:8" ht="13.2">
       <c r="A874" s="19"/>
       <c r="H874" s="20"/>
     </row>
-    <row r="875" spans="1:8">
+    <row r="875" spans="1:8" ht="13.2">
       <c r="A875" s="19"/>
       <c r="H875" s="20"/>
     </row>
-    <row r="876" spans="1:8">
+    <row r="876" spans="1:8" ht="13.2">
       <c r="A876" s="19"/>
       <c r="H876" s="20"/>
     </row>
-    <row r="877" spans="1:8">
+    <row r="877" spans="1:8" ht="13.2">
       <c r="A877" s="19"/>
       <c r="H877" s="20"/>
     </row>
-    <row r="878" spans="1:8">
+    <row r="878" spans="1:8" ht="13.2">
       <c r="A878" s="19"/>
       <c r="H878" s="20"/>
     </row>
-    <row r="879" spans="1:8">
+    <row r="879" spans="1:8" ht="13.2">
       <c r="A879" s="19"/>
       <c r="H879" s="20"/>
     </row>
-    <row r="880" spans="1:8">
+    <row r="880" spans="1:8" ht="13.2">
       <c r="A880" s="19"/>
       <c r="H880" s="20"/>
     </row>
-    <row r="881" spans="1:8">
+    <row r="881" spans="1:8" ht="13.2">
       <c r="A881" s="19"/>
       <c r="H881" s="20"/>
     </row>
-    <row r="882" spans="1:8">
+    <row r="882" spans="1:8" ht="13.2">
       <c r="A882" s="19"/>
       <c r="H882" s="20"/>
     </row>
-    <row r="883" spans="1:8">
+    <row r="883" spans="1:8" ht="13.2">
       <c r="A883" s="19"/>
       <c r="H883" s="20"/>
     </row>
-    <row r="884" spans="1:8">
+    <row r="884" spans="1:8" ht="13.2">
       <c r="A884" s="19"/>
       <c r="H884" s="20"/>
     </row>
-    <row r="885" spans="1:8">
+    <row r="885" spans="1:8" ht="13.2">
       <c r="A885" s="19"/>
       <c r="H885" s="20"/>
     </row>
-    <row r="886" spans="1:8">
+    <row r="886" spans="1:8" ht="13.2">
       <c r="A886" s="19"/>
       <c r="H886" s="20"/>
     </row>
-    <row r="887" spans="1:8">
+    <row r="887" spans="1:8" ht="13.2">
       <c r="A887" s="19"/>
       <c r="H887" s="20"/>
     </row>
-    <row r="888" spans="1:8">
+    <row r="888" spans="1:8" ht="13.2">
       <c r="A888" s="19"/>
       <c r="H888" s="20"/>
     </row>
-    <row r="889" spans="1:8">
+    <row r="889" spans="1:8" ht="13.2">
       <c r="A889" s="19"/>
       <c r="H889" s="20"/>
     </row>
-    <row r="890" spans="1:8">
+    <row r="890" spans="1:8" ht="13.2">
       <c r="A890" s="19"/>
       <c r="H890" s="20"/>
     </row>
-    <row r="891" spans="1:8">
+    <row r="891" spans="1:8" ht="13.2">
       <c r="A891" s="19"/>
       <c r="H891" s="20"/>
     </row>
-    <row r="892" spans="1:8">
+    <row r="892" spans="1:8" ht="13.2">
       <c r="A892" s="19"/>
       <c r="H892" s="20"/>
     </row>
-    <row r="893" spans="1:8">
+    <row r="893" spans="1:8" ht="13.2">
       <c r="A893" s="19"/>
       <c r="H893" s="20"/>
     </row>
-    <row r="894" spans="1:8">
+    <row r="894" spans="1:8" ht="13.2">
       <c r="A894" s="19"/>
       <c r="H894" s="20"/>
     </row>
-    <row r="895" spans="1:8">
+    <row r="895" spans="1:8" ht="13.2">
       <c r="A895" s="19"/>
       <c r="H895" s="20"/>
     </row>
-    <row r="896" spans="1:8">
+    <row r="896" spans="1:8" ht="13.2">
       <c r="A896" s="19"/>
       <c r="H896" s="20"/>
     </row>
-    <row r="897" spans="1:8">
+    <row r="897" spans="1:8" ht="13.2">
       <c r="A897" s="19"/>
       <c r="H897" s="20"/>
     </row>
-    <row r="898" spans="1:8">
+    <row r="898" spans="1:8" ht="13.2">
       <c r="A898" s="19"/>
       <c r="H898" s="20"/>
     </row>
-    <row r="899" spans="1:8">
+    <row r="899" spans="1:8" ht="13.2">
       <c r="A899" s="19"/>
       <c r="H899" s="20"/>
     </row>
-    <row r="900" spans="1:8">
+    <row r="900" spans="1:8" ht="13.2">
       <c r="A900" s="19"/>
       <c r="H900" s="20"/>
     </row>
-    <row r="901" spans="1:8">
+    <row r="901" spans="1:8" ht="13.2">
       <c r="A901" s="19"/>
       <c r="H901" s="20"/>
     </row>
-    <row r="902" spans="1:8">
+    <row r="902" spans="1:8" ht="13.2">
       <c r="A902" s="19"/>
       <c r="H902" s="20"/>
     </row>
-    <row r="903" spans="1:8">
+    <row r="903" spans="1:8" ht="13.2">
       <c r="A903" s="19"/>
       <c r="H903" s="20"/>
     </row>
-    <row r="904" spans="1:8">
+    <row r="904" spans="1:8" ht="13.2">
       <c r="A904" s="19"/>
       <c r="H904" s="20"/>
     </row>
-    <row r="905" spans="1:8">
+    <row r="905" spans="1:8" ht="13.2">
       <c r="A905" s="19"/>
       <c r="H905" s="20"/>
     </row>
-    <row r="906" spans="1:8">
+    <row r="906" spans="1:8" ht="13.2">
       <c r="A906" s="19"/>
       <c r="H906" s="20"/>
     </row>
-    <row r="907" spans="1:8">
+    <row r="907" spans="1:8" ht="13.2">
       <c r="A907" s="19"/>
       <c r="H907" s="20"/>
     </row>
-    <row r="908" spans="1:8">
+    <row r="908" spans="1:8" ht="13.2">
       <c r="A908" s="19"/>
       <c r="H908" s="20"/>
     </row>
-    <row r="909" spans="1:8">
+    <row r="909" spans="1:8" ht="13.2">
       <c r="A909" s="19"/>
       <c r="H909" s="20"/>
     </row>
-    <row r="910" spans="1:8">
+    <row r="910" spans="1:8" ht="13.2">
       <c r="A910" s="19"/>
       <c r="H910" s="20"/>
     </row>
-    <row r="911" spans="1:8">
+    <row r="911" spans="1:8" ht="13.2">
       <c r="A911" s="19"/>
       <c r="H911" s="20"/>
     </row>
-    <row r="912" spans="1:8">
+    <row r="912" spans="1:8" ht="13.2">
       <c r="A912" s="19"/>
       <c r="H912" s="20"/>
     </row>
-    <row r="913" spans="1:8">
+    <row r="913" spans="1:8" ht="13.2">
       <c r="A913" s="19"/>
       <c r="H913" s="20"/>
     </row>
-    <row r="914" spans="1:8">
+    <row r="914" spans="1:8" ht="13.2">
       <c r="A914" s="19"/>
       <c r="H914" s="20"/>
     </row>
-    <row r="915" spans="1:8">
+    <row r="915" spans="1:8" ht="13.2">
       <c r="A915" s="19"/>
       <c r="H915" s="20"/>
     </row>
-    <row r="916" spans="1:8">
+    <row r="916" spans="1:8" ht="13.2">
       <c r="A916" s="19"/>
       <c r="H916" s="20"/>
     </row>
-    <row r="917" spans="1:8">
+    <row r="917" spans="1:8" ht="13.2">
       <c r="A917" s="19"/>
       <c r="H917" s="20"/>
     </row>
-    <row r="918" spans="1:8">
+    <row r="918" spans="1:8" ht="13.2">
       <c r="A918" s="19"/>
       <c r="H918" s="20"/>
     </row>
-    <row r="919" spans="1:8">
+    <row r="919" spans="1:8" ht="13.2">
       <c r="A919" s="19"/>
       <c r="H919" s="20"/>
     </row>
-    <row r="920" spans="1:8">
+    <row r="920" spans="1:8" ht="13.2">
       <c r="A920" s="19"/>
       <c r="H920" s="20"/>
     </row>
-    <row r="921" spans="1:8">
+    <row r="921" spans="1:8" ht="13.2">
       <c r="A921" s="19"/>
       <c r="H921" s="20"/>
     </row>
-    <row r="922" spans="1:8">
+    <row r="922" spans="1:8" ht="13.2">
       <c r="A922" s="19"/>
       <c r="H922" s="20"/>
     </row>
-    <row r="923" spans="1:8">
+    <row r="923" spans="1:8" ht="13.2">
       <c r="A923" s="19"/>
       <c r="H923" s="20"/>
     </row>
-    <row r="924" spans="1:8">
+    <row r="924" spans="1:8" ht="13.2">
       <c r="A924" s="19"/>
       <c r="H924" s="20"/>
     </row>
-    <row r="925" spans="1:8">
+    <row r="925" spans="1:8" ht="13.2">
       <c r="A925" s="19"/>
       <c r="H925" s="20"/>
     </row>
-    <row r="926" spans="1:8">
+    <row r="926" spans="1:8" ht="13.2">
       <c r="A926" s="19"/>
       <c r="H926" s="20"/>
     </row>
-    <row r="927" spans="1:8">
+    <row r="927" spans="1:8" ht="13.2">
       <c r="A927" s="19"/>
       <c r="H927" s="20"/>
     </row>
-    <row r="928" spans="1:8">
+    <row r="928" spans="1:8" ht="13.2">
       <c r="A928" s="19"/>
       <c r="H928" s="20"/>
     </row>
-    <row r="929" spans="1:8">
+    <row r="929" spans="1:8" ht="13.2">
       <c r="A929" s="19"/>
       <c r="H929" s="20"/>
     </row>
-    <row r="930" spans="1:8">
+    <row r="930" spans="1:8" ht="13.2">
       <c r="A930" s="19"/>
       <c r="H930" s="20"/>
     </row>
-    <row r="931" spans="1:8">
+    <row r="931" spans="1:8" ht="13.2">
       <c r="A931" s="19"/>
       <c r="H931" s="20"/>
     </row>
-    <row r="932" spans="1:8">
+    <row r="932" spans="1:8" ht="13.2">
       <c r="A932" s="19"/>
       <c r="H932" s="20"/>
     </row>
-    <row r="933" spans="1:8">
+    <row r="933" spans="1:8" ht="13.2">
       <c r="A933" s="19"/>
       <c r="H933" s="20"/>
     </row>
-    <row r="934" spans="1:8">
+    <row r="934" spans="1:8" ht="13.2">
       <c r="A934" s="19"/>
       <c r="H934" s="20"/>
     </row>
-    <row r="935" spans="1:8">
+    <row r="935" spans="1:8" ht="13.2">
       <c r="A935" s="19"/>
       <c r="H935" s="20"/>
     </row>
-    <row r="936" spans="1:8">
+    <row r="936" spans="1:8" ht="13.2">
       <c r="A936" s="19"/>
       <c r="H936" s="20"/>
     </row>
-    <row r="937" spans="1:8">
+    <row r="937" spans="1:8" ht="13.2">
       <c r="A937" s="19"/>
       <c r="H937" s="20"/>
     </row>
-    <row r="938" spans="1:8">
+    <row r="938" spans="1:8" ht="13.2">
       <c r="A938" s="19"/>
       <c r="H938" s="20"/>
     </row>
-    <row r="939" spans="1:8">
+    <row r="939" spans="1:8" ht="13.2">
       <c r="A939" s="19"/>
       <c r="H939" s="20"/>
     </row>
-    <row r="940" spans="1:8">
+    <row r="940" spans="1:8" ht="13.2">
       <c r="A940" s="19"/>
       <c r="H940" s="20"/>
     </row>
-    <row r="941" spans="1:8">
+    <row r="941" spans="1:8" ht="13.2">
       <c r="A941" s="19"/>
       <c r="H941" s="20"/>
     </row>
-    <row r="942" spans="1:8">
+    <row r="942" spans="1:8" ht="13.2">
       <c r="A942" s="19"/>
       <c r="H942" s="20"/>
     </row>
-    <row r="943" spans="1:8">
+    <row r="943" spans="1:8" ht="13.2">
       <c r="A943" s="19"/>
       <c r="H943" s="20"/>
     </row>
-    <row r="944" spans="1:8">
+    <row r="944" spans="1:8" ht="13.2">
       <c r="A944" s="19"/>
       <c r="H944" s="20"/>
     </row>
-    <row r="945" spans="1:8">
+    <row r="945" spans="1:8" ht="13.2">
       <c r="A945" s="19"/>
       <c r="H945" s="20"/>
     </row>
-    <row r="946" spans="1:8">
+    <row r="946" spans="1:8" ht="13.2">
       <c r="A946" s="19"/>
       <c r="H946" s="20"/>
     </row>
-    <row r="947" spans="1:8">
+    <row r="947" spans="1:8" ht="13.2">
       <c r="A947" s="19"/>
       <c r="H947" s="20"/>
     </row>
-    <row r="948" spans="1:8">
+    <row r="948" spans="1:8" ht="13.2">
       <c r="A948" s="19"/>
       <c r="H948" s="20"/>
     </row>
-    <row r="949" spans="1:8">
+    <row r="949" spans="1:8" ht="13.2">
       <c r="A949" s="19"/>
       <c r="H949" s="20"/>
     </row>
-    <row r="950" spans="1:8">
+    <row r="950" spans="1:8" ht="13.2">
       <c r="A950" s="19"/>
       <c r="H950" s="20"/>
     </row>
-    <row r="951" spans="1:8">
+    <row r="951" spans="1:8" ht="13.2">
       <c r="A951" s="19"/>
       <c r="H951" s="20"/>
     </row>
-    <row r="952" spans="1:8">
+    <row r="952" spans="1:8" ht="13.2">
       <c r="A952" s="19"/>
       <c r="H952" s="20"/>
     </row>
-    <row r="953" spans="1:8">
+    <row r="953" spans="1:8" ht="13.2">
       <c r="A953" s="19"/>
       <c r="H953" s="20"/>
     </row>
-    <row r="954" spans="1:8">
+    <row r="954" spans="1:8" ht="13.2">
       <c r="A954" s="19"/>
       <c r="H954" s="20"/>
     </row>
-    <row r="955" spans="1:8">
+    <row r="955" spans="1:8" ht="13.2">
       <c r="A955" s="19"/>
       <c r="H955" s="20"/>
     </row>
-    <row r="956" spans="1:8">
+    <row r="956" spans="1:8" ht="13.2">
       <c r="A956" s="19"/>
       <c r="H956" s="20"/>
     </row>
-    <row r="957" spans="1:8">
+    <row r="957" spans="1:8" ht="13.2">
       <c r="A957" s="19"/>
       <c r="H957" s="20"/>
     </row>
-    <row r="958" spans="1:8">
+    <row r="958" spans="1:8" ht="13.2">
       <c r="A958" s="19"/>
       <c r="H958" s="20"/>
     </row>
-    <row r="959" spans="1:8">
+    <row r="959" spans="1:8" ht="13.2">
       <c r="A959" s="19"/>
       <c r="H959" s="20"/>
     </row>
-    <row r="960" spans="1:8">
+    <row r="960" spans="1:8" ht="13.2">
       <c r="A960" s="19"/>
       <c r="H960" s="20"/>
     </row>
-    <row r="961" spans="1:8">
+    <row r="961" spans="1:8" ht="13.2">
       <c r="A961" s="19"/>
       <c r="H961" s="20"/>
     </row>
-    <row r="962" spans="1:8">
+    <row r="962" spans="1:8" ht="13.2">
       <c r="A962" s="19"/>
       <c r="H962" s="20"/>
     </row>
-    <row r="963" spans="1:8">
+    <row r="963" spans="1:8" ht="13.2">
       <c r="A963" s="19"/>
       <c r="H963" s="20"/>
     </row>
-    <row r="964" spans="1:8">
+    <row r="964" spans="1:8" ht="13.2">
       <c r="A964" s="19"/>
       <c r="H964" s="20"/>
     </row>
-    <row r="965" spans="1:8">
+    <row r="965" spans="1:8" ht="13.2">
       <c r="A965" s="19"/>
       <c r="H965" s="20"/>
     </row>
-    <row r="966" spans="1:8">
+    <row r="966" spans="1:8" ht="13.2">
       <c r="A966" s="19"/>
       <c r="H966" s="20"/>
     </row>
-    <row r="967" spans="1:8">
+    <row r="967" spans="1:8" ht="13.2">
       <c r="A967" s="19"/>
       <c r="H967" s="20"/>
     </row>
-    <row r="968" spans="1:8">
+    <row r="968" spans="1:8" ht="13.2">
       <c r="A968" s="19"/>
       <c r="H968" s="20"/>
     </row>
-    <row r="969" spans="1:8">
+    <row r="969" spans="1:8" ht="13.2">
       <c r="A969" s="19"/>
       <c r="H969" s="20"/>
     </row>
-    <row r="970" spans="1:8">
+    <row r="970" spans="1:8" ht="13.2">
       <c r="A970" s="19"/>
       <c r="H970" s="20"/>
     </row>
-    <row r="971" spans="1:8">
+    <row r="971" spans="1:8" ht="13.2">
       <c r="A971" s="19"/>
       <c r="H971" s="20"/>
     </row>
-    <row r="972" spans="1:8">
+    <row r="972" spans="1:8" ht="13.2">
       <c r="A972" s="19"/>
       <c r="H972" s="20"/>
     </row>
-    <row r="973" spans="1:8">
+    <row r="973" spans="1:8" ht="13.2">
       <c r="A973" s="19"/>
       <c r="H973" s="20"/>
     </row>
-    <row r="974" spans="1:8">
+    <row r="974" spans="1:8" ht="13.2">
       <c r="A974" s="19"/>
       <c r="H974" s="20"/>
     </row>
-    <row r="975" spans="1:8">
+    <row r="975" spans="1:8" ht="13.2">
       <c r="A975" s="19"/>
       <c r="H975" s="20"/>
     </row>
-    <row r="976" spans="1:8">
+    <row r="976" spans="1:8" ht="13.2">
       <c r="A976" s="19"/>
       <c r="H976" s="20"/>
     </row>
-    <row r="977" spans="1:8">
+    <row r="977" spans="1:8" ht="13.2">
       <c r="A977" s="19"/>
       <c r="H977" s="20"/>
     </row>
-    <row r="978" spans="1:8">
+    <row r="978" spans="1:8" ht="13.2">
       <c r="A978" s="19"/>
       <c r="H978" s="20"/>
     </row>
-    <row r="979" spans="1:8">
+    <row r="979" spans="1:8" ht="13.2">
       <c r="A979" s="19"/>
       <c r="H979" s="20"/>
     </row>
-    <row r="980" spans="1:8">
+    <row r="980" spans="1:8" ht="13.2">
       <c r="A980" s="19"/>
       <c r="H980" s="20"/>
     </row>
-    <row r="981" spans="1:8">
+    <row r="981" spans="1:8" ht="13.2">
       <c r="A981" s="19"/>
       <c r="H981" s="20"/>
     </row>
-    <row r="982" spans="1:8">
+    <row r="982" spans="1:8" ht="13.2">
       <c r="A982" s="19"/>
       <c r="H982" s="20"/>
     </row>
-    <row r="983" spans="1:8">
+    <row r="983" spans="1:8" ht="13.2">
       <c r="A983" s="19"/>
       <c r="H983" s="20"/>
     </row>
-    <row r="984" spans="1:8">
+    <row r="984" spans="1:8" ht="13.2">
       <c r="A984" s="19"/>
       <c r="H984" s="20"/>
     </row>
-    <row r="985" spans="1:8">
+    <row r="985" spans="1:8" ht="13.2">
       <c r="A985" s="19"/>
       <c r="H985" s="20"/>
     </row>
-    <row r="986" spans="1:8">
+    <row r="986" spans="1:8" ht="13.2">
       <c r="A986" s="19"/>
       <c r="H986" s="20"/>
     </row>
-    <row r="987" spans="1:8">
+    <row r="987" spans="1:8" ht="13.2">
       <c r="A987" s="19"/>
       <c r="H987" s="20"/>
     </row>
-    <row r="988" spans="1:8">
+    <row r="988" spans="1:8" ht="13.2">
       <c r="A988" s="19"/>
       <c r="H988" s="20"/>
     </row>
-    <row r="989" spans="1:8">
+    <row r="989" spans="1:8" ht="13.2">
       <c r="A989" s="19"/>
       <c r="H989" s="20"/>
     </row>
-    <row r="990" spans="1:8">
+    <row r="990" spans="1:8" ht="13.2">
       <c r="A990" s="19"/>
       <c r="H990" s="20"/>
     </row>
-    <row r="991" spans="1:8">
+    <row r="991" spans="1:8" ht="13.2">
       <c r="A991" s="19"/>
       <c r="H991" s="20"/>
     </row>
-    <row r="992" spans="1:8">
+    <row r="992" spans="1:8" ht="13.2">
       <c r="A992" s="19"/>
       <c r="H992" s="20"/>
     </row>
-    <row r="993" spans="1:8">
+    <row r="993" spans="1:8" ht="13.2">
       <c r="A993" s="19"/>
       <c r="H993" s="20"/>
     </row>
-    <row r="994" spans="1:8">
+    <row r="994" spans="1:8" ht="13.2">
       <c r="A994" s="19"/>
       <c r="H994" s="20"/>
     </row>
-    <row r="995" spans="1:8">
+    <row r="995" spans="1:8" ht="13.2">
       <c r="A995" s="19"/>
       <c r="H995" s="20"/>
     </row>
-    <row r="996" spans="1:8">
+    <row r="996" spans="1:8" ht="13.2">
       <c r="A996" s="19"/>
       <c r="H996" s="20"/>
     </row>
-    <row r="997" spans="1:8">
+    <row r="997" spans="1:8" ht="13.2">
       <c r="A997" s="19"/>
       <c r="H997" s="20"/>
     </row>
-    <row r="998" spans="1:8">
+    <row r="998" spans="1:8" ht="13.2">
       <c r="H998" s="20"/>
     </row>
   </sheetData>
@@ -9699,7 +9708,7 @@
       <c r="P1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="27" t="s">
+      <c r="Q1" s="37" t="s">
         <v>203</v>
       </c>
     </row>
@@ -9805,7 +9814,7 @@
       <c r="P3" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="28" t="s">
+      <c r="Q3" s="38" t="s">
         <v>204</v>
       </c>
     </row>
@@ -9858,7 +9867,7 @@
       <c r="P4" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q4" s="28" t="s">
+      <c r="Q4" s="38" t="s">
         <v>204</v>
       </c>
     </row>
@@ -9900,10 +9909,10 @@
         <v>207</v>
       </c>
       <c r="M5" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="29">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="N5" s="32">
+        <v>10000000</v>
       </c>
       <c r="O5" s="28" t="s">
         <v>19</v>
@@ -9911,7 +9920,7 @@
       <c r="P5" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q5" s="28" t="s">
+      <c r="Q5" s="38" t="s">
         <v>204</v>
       </c>
     </row>
@@ -10076,37 +10085,37 @@
     </row>
     <row r="9" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A9" s="29">
-        <v>11077697</v>
+        <v>43016896</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C9" s="29">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D9" s="29">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" s="29">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="F9" s="29">
-        <v>18.78</v>
+        <v>14.35</v>
       </c>
       <c r="G9" s="29">
-        <v>169</v>
-      </c>
-      <c r="H9" s="29">
-        <v>60</v>
+        <v>162.66999999999999</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>163</v>
       </c>
       <c r="I9" s="29">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J9" s="29">
-        <v>9.2899999999999991</v>
+        <v>7.92</v>
       </c>
       <c r="K9" s="29">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>207</v>
@@ -10123,52 +10132,52 @@
       <c r="P9" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q9" s="28" t="s">
-        <v>42</v>
+      <c r="Q9" s="38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A10" s="29">
-        <v>43016896</v>
+        <v>19685723</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="C10" s="29">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="D10" s="29">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="E10" s="29">
-        <v>488</v>
+        <v>589</v>
       </c>
       <c r="F10" s="29">
-        <v>14.35</v>
+        <v>10.91</v>
       </c>
       <c r="G10" s="29">
-        <v>162.66999999999999</v>
-      </c>
-      <c r="H10" s="29" t="s">
-        <v>163</v>
+        <v>130.88999999999999</v>
+      </c>
+      <c r="H10" s="29">
+        <v>37</v>
       </c>
       <c r="I10" s="29">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="J10" s="29">
-        <v>7.92</v>
+        <v>12.07</v>
       </c>
       <c r="K10" s="29">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L10" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M10" s="35" t="s">
-        <v>50</v>
+      <c r="M10" s="34" t="s">
+        <v>25</v>
       </c>
       <c r="N10" s="32">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="O10" s="28" t="s">
         <v>19</v>
@@ -10176,52 +10185,36 @@
       <c r="P10" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q10" s="28" t="s">
+      <c r="Q10" s="38" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A11" s="29">
-        <v>19685723</v>
+        <v>44521368</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11" s="29">
-        <v>113</v>
-      </c>
-      <c r="D11" s="29">
-        <v>75</v>
-      </c>
-      <c r="E11" s="29">
-        <v>589</v>
-      </c>
-      <c r="F11" s="29">
-        <v>10.91</v>
-      </c>
-      <c r="G11" s="29">
-        <v>130.88999999999999</v>
-      </c>
-      <c r="H11" s="29">
-        <v>37</v>
-      </c>
-      <c r="I11" s="29">
-        <v>47</v>
-      </c>
-      <c r="J11" s="29">
-        <v>12.07</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
       <c r="K11" s="29">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L11" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M11" s="34" t="s">
-        <v>25</v>
+      <c r="M11" s="36" t="s">
+        <v>45</v>
       </c>
       <c r="N11" s="32">
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
       <c r="O11" s="28" t="s">
         <v>19</v>
@@ -10230,35 +10223,51 @@
         <v>20</v>
       </c>
       <c r="Q11" s="28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A12" s="29">
-        <v>44521368</v>
+        <v>2320856</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
+        <v>121</v>
+      </c>
+      <c r="C12" s="29">
+        <v>648</v>
+      </c>
+      <c r="D12" s="29">
+        <v>433</v>
+      </c>
+      <c r="E12" s="29">
+        <v>6590</v>
+      </c>
+      <c r="F12" s="29">
+        <v>21.61</v>
+      </c>
+      <c r="G12" s="29">
+        <v>193.77</v>
+      </c>
+      <c r="H12" s="29">
+        <v>88</v>
+      </c>
+      <c r="I12" s="29">
+        <v>575</v>
+      </c>
+      <c r="J12" s="29">
+        <v>11.88</v>
+      </c>
       <c r="K12" s="29">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="L12" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M12" s="36" t="s">
-        <v>45</v>
+      <c r="M12" s="31" t="s">
+        <v>40</v>
       </c>
       <c r="N12" s="32">
-        <v>2000000</v>
+        <v>20000000</v>
       </c>
       <c r="O12" s="28" t="s">
         <v>19</v>
@@ -10272,46 +10281,46 @@
     </row>
     <row r="13" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A13" s="29">
-        <v>2320856</v>
+        <v>37888165</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="C13" s="29">
-        <v>648</v>
+        <v>106</v>
       </c>
       <c r="D13" s="29">
-        <v>433</v>
+        <v>77</v>
       </c>
       <c r="E13" s="29">
-        <v>6590</v>
+        <v>865</v>
       </c>
       <c r="F13" s="29">
-        <v>21.61</v>
+        <v>17.3</v>
       </c>
       <c r="G13" s="29">
-        <v>193.77</v>
-      </c>
-      <c r="H13" s="29">
-        <v>88</v>
+        <v>190.95</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>166</v>
       </c>
       <c r="I13" s="29">
-        <v>575</v>
+        <v>39</v>
       </c>
       <c r="J13" s="29">
-        <v>11.88</v>
+        <v>11.7</v>
       </c>
       <c r="K13" s="29">
-        <v>394</v>
+        <v>61</v>
       </c>
       <c r="L13" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M13" s="31" t="s">
-        <v>40</v>
+      <c r="M13" s="34" t="s">
+        <v>25</v>
       </c>
       <c r="N13" s="32">
-        <v>20000000</v>
+        <v>5000000</v>
       </c>
       <c r="O13" s="28" t="s">
         <v>19</v>
@@ -10325,46 +10334,46 @@
     </row>
     <row r="14" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A14" s="29">
-        <v>37888165</v>
+        <v>12060554</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="C14" s="29">
+        <v>136</v>
+      </c>
+      <c r="D14" s="29">
         <v>106</v>
       </c>
-      <c r="D14" s="29">
-        <v>77</v>
-      </c>
       <c r="E14" s="29">
-        <v>865</v>
+        <v>971</v>
       </c>
       <c r="F14" s="29">
-        <v>17.3</v>
+        <v>12.14</v>
       </c>
       <c r="G14" s="29">
-        <v>190.95</v>
-      </c>
-      <c r="H14" s="29" t="s">
-        <v>166</v>
+        <v>161.30000000000001</v>
+      </c>
+      <c r="H14" s="29">
+        <v>65</v>
       </c>
       <c r="I14" s="29">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="J14" s="29">
-        <v>11.7</v>
+        <v>10.46</v>
       </c>
       <c r="K14" s="29">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="L14" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M14" s="34" t="s">
-        <v>25</v>
+      <c r="M14" s="35" t="s">
+        <v>50</v>
       </c>
       <c r="N14" s="32">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="O14" s="28" t="s">
         <v>19</v>
@@ -10373,51 +10382,51 @@
         <v>20</v>
       </c>
       <c r="Q14" s="28" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A15" s="29">
-        <v>12060554</v>
+        <v>3371745</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>185</v>
+        <v>62</v>
       </c>
       <c r="C15" s="29">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="D15" s="29">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="E15" s="29">
-        <v>971</v>
+        <v>1711</v>
       </c>
       <c r="F15" s="29">
-        <v>12.14</v>
+        <v>21.12</v>
       </c>
       <c r="G15" s="29">
-        <v>161.30000000000001</v>
+        <v>131.21</v>
       </c>
       <c r="H15" s="29">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="I15" s="29">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="J15" s="29">
-        <v>10.46</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="K15" s="29">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="L15" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M15" s="35" t="s">
-        <v>50</v>
+      <c r="M15" s="31" t="s">
+        <v>40</v>
       </c>
       <c r="N15" s="32">
-        <v>10000000</v>
+        <v>20000000</v>
       </c>
       <c r="O15" s="28" t="s">
         <v>19</v>
@@ -10426,51 +10435,51 @@
         <v>20</v>
       </c>
       <c r="Q15" s="28" t="s">
-        <v>42</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A16" s="29">
-        <v>3371745</v>
+        <v>38392651</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C16" s="29">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="D16" s="29">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="E16" s="29">
-        <v>1711</v>
+        <v>623</v>
       </c>
       <c r="F16" s="29">
-        <v>21.12</v>
+        <v>18.88</v>
       </c>
       <c r="G16" s="29">
-        <v>131.21</v>
-      </c>
-      <c r="H16" s="29">
-        <v>105</v>
+        <v>171.15</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>168</v>
       </c>
       <c r="I16" s="29">
-        <v>117</v>
+        <v>28</v>
       </c>
       <c r="J16" s="29">
-        <v>8.8800000000000008</v>
+        <v>10.25</v>
       </c>
       <c r="K16" s="29">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L16" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M16" s="31" t="s">
-        <v>40</v>
+      <c r="M16" s="34" t="s">
+        <v>25</v>
       </c>
       <c r="N16" s="32">
-        <v>20000000</v>
+        <v>5000000</v>
       </c>
       <c r="O16" s="28" t="s">
         <v>19</v>
@@ -10478,52 +10487,52 @@
       <c r="P16" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q16" s="28" t="s">
-        <v>205</v>
+      <c r="Q16" s="38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A17" s="29">
-        <v>38392651</v>
+        <v>11374748</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="C17" s="29">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="D17" s="29">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E17" s="29">
-        <v>623</v>
+        <v>725</v>
       </c>
       <c r="F17" s="29">
-        <v>18.88</v>
+        <v>30.21</v>
       </c>
       <c r="G17" s="29">
-        <v>171.15</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>168</v>
+        <v>183.54</v>
+      </c>
+      <c r="H17" s="29">
+        <v>52</v>
       </c>
       <c r="I17" s="29">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J17" s="29">
-        <v>10.25</v>
+        <v>8.98</v>
       </c>
       <c r="K17" s="29">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L17" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M17" s="34" t="s">
-        <v>25</v>
+      <c r="M17" s="31" t="s">
+        <v>40</v>
       </c>
       <c r="N17" s="32">
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
       <c r="O17" s="28" t="s">
         <v>19</v>
@@ -10532,51 +10541,51 @@
         <v>20</v>
       </c>
       <c r="Q17" s="28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A18" s="29">
-        <v>23646088</v>
+        <v>49414345</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="C18" s="29">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="D18" s="29">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="E18" s="29">
-        <v>1295</v>
+        <v>85</v>
       </c>
       <c r="F18" s="29">
-        <v>18.77</v>
+        <v>17</v>
       </c>
       <c r="G18" s="29">
-        <v>189.6</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>178</v>
+        <v>151.79</v>
+      </c>
+      <c r="H18" s="29">
+        <v>39</v>
       </c>
       <c r="I18" s="29">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="J18" s="29">
-        <v>12.57</v>
+        <v>11.33</v>
       </c>
       <c r="K18" s="29">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="L18" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M18" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="N18" s="29">
-        <v>0</v>
+      <c r="M18" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="N18" s="32">
+        <v>2000000</v>
       </c>
       <c r="O18" s="28" t="s">
         <v>19</v>
@@ -10584,43 +10593,43 @@
       <c r="P18" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q18" s="28" t="s">
-        <v>205</v>
+      <c r="Q18" s="38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A19" s="29">
-        <v>21857884</v>
+        <v>48762345</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="C19" s="29">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="D19" s="29">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="E19" s="29">
-        <v>858</v>
+        <v>144</v>
       </c>
       <c r="F19" s="29">
-        <v>17.16</v>
+        <v>18</v>
       </c>
       <c r="G19" s="29">
-        <v>186.93</v>
+        <v>211.76</v>
       </c>
       <c r="H19" s="29">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="I19" s="29">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J19" s="29">
-        <v>14.33</v>
+        <v>11.6</v>
       </c>
       <c r="K19" s="29">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="L19" s="30" t="s">
         <v>207</v>
@@ -10637,52 +10646,52 @@
       <c r="P19" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q19" s="28" t="s">
-        <v>205</v>
+      <c r="Q19" s="38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A20" s="29">
-        <v>11374748</v>
+        <v>4258050</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
       <c r="C20" s="29">
-        <v>46</v>
+        <v>207</v>
       </c>
       <c r="D20" s="29">
-        <v>36</v>
+        <v>175</v>
       </c>
       <c r="E20" s="29">
-        <v>725</v>
+        <v>1775</v>
       </c>
       <c r="F20" s="29">
-        <v>30.21</v>
+        <v>12.77</v>
       </c>
       <c r="G20" s="29">
-        <v>183.54</v>
-      </c>
-      <c r="H20" s="29">
-        <v>52</v>
+        <v>149.66</v>
+      </c>
+      <c r="H20" s="29" t="s">
+        <v>181</v>
       </c>
       <c r="I20" s="29">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="J20" s="29">
-        <v>8.98</v>
+        <v>10.42</v>
       </c>
       <c r="K20" s="29">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="L20" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M20" s="31" t="s">
-        <v>40</v>
+      <c r="M20" s="35" t="s">
+        <v>50</v>
       </c>
       <c r="N20" s="32">
-        <v>20000000</v>
+        <v>10000000</v>
       </c>
       <c r="O20" s="28" t="s">
         <v>19</v>
@@ -10691,51 +10700,51 @@
         <v>20</v>
       </c>
       <c r="Q20" s="28" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A21" s="29">
-        <v>49414345</v>
+        <v>12060748</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="C21" s="29">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D21" s="29">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="E21" s="29">
-        <v>85</v>
+        <v>389</v>
       </c>
       <c r="F21" s="29">
-        <v>17</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="G21" s="29">
-        <v>151.79</v>
+        <v>136.01</v>
       </c>
       <c r="H21" s="29">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I21" s="29">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="J21" s="29">
-        <v>11.33</v>
+        <v>10.91</v>
       </c>
       <c r="K21" s="29">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="L21" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M21" s="36" t="s">
-        <v>45</v>
+      <c r="M21" s="34" t="s">
+        <v>25</v>
       </c>
       <c r="N21" s="32">
-        <v>2000000</v>
+        <v>5000000</v>
       </c>
       <c r="O21" s="28" t="s">
         <v>19</v>
@@ -10744,42 +10753,38 @@
         <v>20</v>
       </c>
       <c r="Q21" s="28" t="s">
-        <v>204</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A22" s="29">
-        <v>48762345</v>
+        <v>31751306</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="C22" s="29">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D22" s="29">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E22" s="29">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="F22" s="29">
-        <v>18</v>
+        <v>7.5</v>
       </c>
       <c r="G22" s="29">
-        <v>211.76</v>
-      </c>
-      <c r="H22" s="29">
-        <v>35</v>
-      </c>
-      <c r="I22" s="29">
-        <v>5</v>
-      </c>
-      <c r="J22" s="29">
-        <v>11.6</v>
-      </c>
+        <v>93.75</v>
+      </c>
+      <c r="H22" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
       <c r="K22" s="29">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L22" s="30" t="s">
         <v>207</v>
@@ -10797,42 +10802,42 @@
         <v>20</v>
       </c>
       <c r="Q22" s="28" t="s">
-        <v>204</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A23" s="29">
-        <v>4258050</v>
+        <v>42598564</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C23" s="29">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="D23" s="29">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="E23" s="29">
-        <v>1775</v>
+        <v>1570</v>
       </c>
       <c r="F23" s="29">
-        <v>12.77</v>
+        <v>19.38</v>
       </c>
       <c r="G23" s="29">
-        <v>149.66</v>
+        <v>191.46</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I23" s="29">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="J23" s="29">
-        <v>10.42</v>
+        <v>11.86</v>
       </c>
       <c r="K23" s="29">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L23" s="30" t="s">
         <v>207</v>
@@ -10849,43 +10854,43 @@
       <c r="P23" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q23" s="28" t="s">
-        <v>42</v>
+      <c r="Q23" s="38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A24" s="29">
-        <v>12060748</v>
+        <v>45002297</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="C24" s="29">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="D24" s="29">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="E24" s="29">
-        <v>389</v>
+        <v>110</v>
       </c>
       <c r="F24" s="29">
-        <v>9.0500000000000007</v>
+        <v>18.329999999999998</v>
       </c>
       <c r="G24" s="29">
-        <v>136.01</v>
-      </c>
-      <c r="H24" s="29">
-        <v>30</v>
+        <v>142.86000000000001</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>169</v>
       </c>
       <c r="I24" s="29">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="J24" s="29">
-        <v>10.91</v>
+        <v>8.73</v>
       </c>
       <c r="K24" s="29">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="L24" s="30" t="s">
         <v>207</v>
@@ -10908,42 +10913,46 @@
     </row>
     <row r="25" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A25" s="29">
-        <v>31751306</v>
+        <v>36055152</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="C25" s="29">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="D25" s="29">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="E25" s="29">
-        <v>60</v>
+        <v>411</v>
       </c>
       <c r="F25" s="29">
-        <v>7.5</v>
+        <v>11.11</v>
       </c>
       <c r="G25" s="29">
-        <v>93.75</v>
+        <v>132.58000000000001</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
+        <v>171</v>
+      </c>
+      <c r="I25" s="29">
+        <v>25</v>
+      </c>
+      <c r="J25" s="29">
+        <v>12.89</v>
+      </c>
       <c r="K25" s="29">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="L25" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M25" s="35" t="s">
-        <v>50</v>
+      <c r="M25" s="36" t="s">
+        <v>45</v>
       </c>
       <c r="N25" s="32">
-        <v>10000000</v>
+        <v>2000000</v>
       </c>
       <c r="O25" s="28" t="s">
         <v>19</v>
@@ -10951,99 +10960,105 @@
       <c r="P25" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q25" s="28" t="s">
-        <v>42</v>
+      <c r="Q25" s="38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="27" thickBot="1">
       <c r="A26" s="29">
-        <v>30299329</v>
+        <v>47133527</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>172</v>
+        <v>113</v>
       </c>
       <c r="C26" s="29">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D26" s="29">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="E26" s="29">
-        <v>76</v>
+        <v>666</v>
       </c>
       <c r="F26" s="29">
-        <v>3.8</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="G26" s="29">
-        <v>86.36</v>
+        <v>164.44</v>
       </c>
       <c r="H26" s="29">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="I26" s="29">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="J26" s="29">
-        <v>14.97</v>
+        <v>10.14</v>
       </c>
       <c r="K26" s="29">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="L26" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M26" s="36" t="s">
-        <v>45</v>
+      <c r="M26" s="34" t="s">
+        <v>25</v>
       </c>
       <c r="N26" s="32">
-        <v>2000000</v>
-      </c>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
+        <v>5000000</v>
+      </c>
+      <c r="O26" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="P26" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q26" s="28" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="27" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A27" s="29">
-        <v>42598564</v>
+        <v>44011252</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C27" s="29">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="D27" s="29">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="E27" s="29">
-        <v>1570</v>
+        <v>732</v>
       </c>
       <c r="F27" s="29">
-        <v>19.38</v>
+        <v>27.11</v>
       </c>
       <c r="G27" s="29">
-        <v>191.46</v>
+        <v>196.77</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I27" s="29">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="J27" s="29">
-        <v>11.86</v>
+        <v>11.04</v>
       </c>
       <c r="K27" s="29">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="L27" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M27" s="35" t="s">
-        <v>50</v>
+      <c r="M27" s="31" t="s">
+        <v>40</v>
       </c>
       <c r="N27" s="32">
-        <v>10000000</v>
+        <v>20000000</v>
       </c>
       <c r="O27" s="28" t="s">
         <v>19</v>
@@ -11052,51 +11067,51 @@
         <v>20</v>
       </c>
       <c r="Q27" s="28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A28" s="29">
-        <v>45002297</v>
+        <v>8026613</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="C28" s="29">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D28" s="29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E28" s="29">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="F28" s="29">
-        <v>18.329999999999998</v>
+        <v>14.33</v>
       </c>
       <c r="G28" s="29">
-        <v>142.86000000000001</v>
-      </c>
-      <c r="H28" s="29" t="s">
-        <v>169</v>
+        <v>132.31</v>
+      </c>
+      <c r="H28" s="29">
+        <v>33</v>
       </c>
       <c r="I28" s="29">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J28" s="29">
-        <v>8.73</v>
+        <v>18.75</v>
       </c>
       <c r="K28" s="29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L28" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M28" s="34" t="s">
-        <v>25</v>
+      <c r="M28" s="36" t="s">
+        <v>45</v>
       </c>
       <c r="N28" s="32">
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
       <c r="O28" s="28" t="s">
         <v>19</v>
@@ -11110,46 +11125,46 @@
     </row>
     <row r="29" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A29" s="29">
-        <v>36055152</v>
+        <v>7183132</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="C29" s="29">
-        <v>74</v>
+        <v>261</v>
       </c>
       <c r="D29" s="29">
-        <v>51</v>
+        <v>224</v>
       </c>
       <c r="E29" s="29">
-        <v>411</v>
+        <v>4768</v>
       </c>
       <c r="F29" s="29">
-        <v>11.11</v>
+        <v>25.36</v>
       </c>
       <c r="G29" s="29">
-        <v>132.58000000000001</v>
+        <v>185.17</v>
       </c>
       <c r="H29" s="29" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="I29" s="29">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="J29" s="29">
-        <v>12.89</v>
+        <v>8.98</v>
       </c>
       <c r="K29" s="29">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="L29" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M29" s="36" t="s">
-        <v>45</v>
+      <c r="M29" s="35" t="s">
+        <v>50</v>
       </c>
       <c r="N29" s="32">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
       <c r="O29" s="28" t="s">
         <v>19</v>
@@ -11157,55 +11172,55 @@
       <c r="P29" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q29" s="28" t="s">
+      <c r="Q29" s="38" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="27" thickBot="1">
+    <row r="30" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A30" s="29">
-        <v>47133527</v>
+        <v>17365917</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>113</v>
+        <v>210</v>
       </c>
       <c r="C30" s="29">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="D30" s="29">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E30" s="29">
-        <v>666</v>
+        <v>61</v>
       </c>
       <c r="F30" s="29">
-        <v>16.649999999999999</v>
+        <v>10.17</v>
       </c>
       <c r="G30" s="29">
-        <v>164.44</v>
+        <v>164.86</v>
       </c>
       <c r="H30" s="29">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="I30" s="29">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="J30" s="29">
-        <v>10.14</v>
+        <v>10.76</v>
       </c>
       <c r="K30" s="29">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="L30" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M30" s="34" t="s">
-        <v>25</v>
+      <c r="M30" s="36" t="s">
+        <v>45</v>
       </c>
       <c r="N30" s="32">
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
       <c r="O30" s="28" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="P30" s="28" t="s">
         <v>20</v>
@@ -11216,37 +11231,37 @@
     </row>
     <row r="31" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A31" s="29">
-        <v>44011252</v>
+        <v>4779842</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="C31" s="29">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="D31" s="29">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="E31" s="29">
-        <v>732</v>
+        <v>2294</v>
       </c>
       <c r="F31" s="29">
-        <v>27.11</v>
+        <v>22.71</v>
       </c>
       <c r="G31" s="29">
-        <v>196.77</v>
+        <v>183.08</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="I31" s="29">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="J31" s="29">
-        <v>11.04</v>
+        <v>10.5</v>
       </c>
       <c r="K31" s="29">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="L31" s="30" t="s">
         <v>207</v>
@@ -11263,43 +11278,27 @@
       <c r="P31" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q31" s="28" t="s">
-        <v>205</v>
+      <c r="Q31" s="38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A32" s="29">
-        <v>8026613</v>
+        <v>51819205</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="29">
-        <v>17</v>
-      </c>
-      <c r="D32" s="29">
-        <v>10</v>
-      </c>
-      <c r="E32" s="29">
-        <v>86</v>
-      </c>
-      <c r="F32" s="29">
-        <v>14.33</v>
-      </c>
-      <c r="G32" s="29">
-        <v>132.31</v>
-      </c>
-      <c r="H32" s="29">
-        <v>33</v>
-      </c>
-      <c r="I32" s="29">
+        <v>209</v>
+      </c>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="29">
         <v>0</v>
-      </c>
-      <c r="J32" s="29">
-        <v>18.75</v>
-      </c>
-      <c r="K32" s="29">
-        <v>3</v>
       </c>
       <c r="L32" s="30" t="s">
         <v>207</v>
@@ -11322,46 +11321,44 @@
     </row>
     <row r="33" spans="1:27" ht="40.200000000000003" thickBot="1">
       <c r="A33" s="29">
-        <v>46477829</v>
+        <v>12061243</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>46</v>
+        <v>211</v>
       </c>
       <c r="C33" s="29">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="D33" s="29">
-        <v>14</v>
+        <v>211</v>
       </c>
       <c r="E33" s="29">
-        <v>120</v>
+        <v>4736</v>
       </c>
       <c r="F33" s="29">
-        <v>12</v>
+        <v>28.19</v>
       </c>
       <c r="G33" s="29">
-        <v>146.34</v>
+        <v>217.25</v>
       </c>
       <c r="H33" s="29">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="I33" s="29">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="J33" s="29">
-        <v>10.77</v>
+        <v>10.85</v>
       </c>
       <c r="K33" s="29">
-        <v>11</v>
-      </c>
-      <c r="L33" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="M33" s="36" t="s">
-        <v>45</v>
+        <v>119</v>
+      </c>
+      <c r="L33" s="28"/>
+      <c r="M33" s="33" t="s">
+        <v>40</v>
       </c>
       <c r="N33" s="32">
-        <v>2000000</v>
+        <v>20000000</v>
       </c>
       <c r="O33" s="28" t="s">
         <v>19</v>
@@ -11369,105 +11366,105 @@
       <c r="P33" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q33" s="28" t="s">
+      <c r="Q33" s="38" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="40.200000000000003" thickBot="1">
+    <row r="34" spans="1:27" ht="27" thickBot="1">
       <c r="A34" s="29">
-        <v>7183132</v>
+        <v>22819671</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="C34" s="29">
-        <v>261</v>
+        <v>51</v>
       </c>
       <c r="D34" s="29">
-        <v>224</v>
+        <v>37</v>
       </c>
       <c r="E34" s="29">
-        <v>4768</v>
+        <v>264</v>
       </c>
       <c r="F34" s="29">
-        <v>25.36</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="G34" s="29">
-        <v>185.17</v>
-      </c>
-      <c r="H34" s="29" t="s">
-        <v>190</v>
+        <v>96.7</v>
+      </c>
+      <c r="H34" s="29">
+        <v>35</v>
       </c>
       <c r="I34" s="29">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="J34" s="29">
-        <v>8.98</v>
+        <v>6.9</v>
       </c>
       <c r="K34" s="29">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="L34" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M34" s="35" t="s">
-        <v>50</v>
+      <c r="M34" s="34" t="s">
+        <v>25</v>
       </c>
       <c r="N34" s="32">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="O34" s="28" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="P34" s="28" t="s">
-        <v>20</v>
+        <v>208</v>
       </c>
       <c r="Q34" s="28" t="s">
-        <v>204</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="40.200000000000003" thickBot="1">
       <c r="A35" s="29">
-        <v>10967531</v>
+        <v>29988182</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="C35" s="29">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="D35" s="29">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E35" s="29">
-        <v>1028</v>
+        <v>463</v>
       </c>
       <c r="F35" s="29">
-        <v>23.91</v>
+        <v>15.43</v>
       </c>
       <c r="G35" s="29">
-        <v>179.72</v>
-      </c>
-      <c r="H35" s="29" t="s">
-        <v>183</v>
+        <v>159.11000000000001</v>
+      </c>
+      <c r="H35" s="29">
+        <v>41</v>
       </c>
       <c r="I35" s="29">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="J35" s="29">
-        <v>11.31</v>
+        <v>10.68</v>
       </c>
       <c r="K35" s="29">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L35" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M35" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="N35" s="29">
-        <v>0</v>
+      <c r="M35" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="32">
+        <v>10000000</v>
       </c>
       <c r="O35" s="28" t="s">
         <v>19</v>
@@ -11476,51 +11473,51 @@
         <v>20</v>
       </c>
       <c r="Q35" s="28" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="40.200000000000003" thickBot="1">
       <c r="A36" s="29">
-        <v>11616298</v>
+        <v>10984519</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C36" s="29">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="D36" s="29">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="E36" s="29">
-        <v>36</v>
+        <v>3072</v>
       </c>
       <c r="F36" s="29">
-        <v>18</v>
+        <v>29.26</v>
       </c>
       <c r="G36" s="29">
-        <v>120</v>
+        <v>213.63</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="I36" s="29">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="J36" s="29">
-        <v>9.34</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="K36" s="29">
-        <v>6</v>
+        <v>127</v>
       </c>
       <c r="L36" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M36" s="36" t="s">
-        <v>45</v>
+      <c r="M36" s="31" t="s">
+        <v>40</v>
       </c>
       <c r="N36" s="32">
-        <v>2000000</v>
+        <v>20000000</v>
       </c>
       <c r="O36" s="28" t="s">
         <v>19</v>
@@ -11528,176 +11525,70 @@
       <c r="P36" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q36" s="28" t="s">
+      <c r="Q36" s="38" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="40.200000000000003" thickBot="1">
-      <c r="A37" s="29">
-        <v>33758093</v>
-      </c>
-      <c r="B37" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="29">
-        <v>15</v>
-      </c>
-      <c r="D37" s="29">
-        <v>11</v>
-      </c>
-      <c r="E37" s="29">
-        <v>184</v>
-      </c>
-      <c r="F37" s="29">
-        <v>26.29</v>
-      </c>
-      <c r="G37" s="29">
-        <v>213.95</v>
-      </c>
-      <c r="H37" s="29">
-        <v>41</v>
-      </c>
-      <c r="I37" s="29">
-        <v>5</v>
-      </c>
-      <c r="J37" s="29">
-        <v>15.12</v>
-      </c>
-      <c r="K37" s="29">
-        <v>11</v>
-      </c>
-      <c r="L37" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="M37" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="N37" s="32">
-        <v>10000000</v>
-      </c>
-      <c r="O37" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="P37" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q37" s="28" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="40.200000000000003" thickBot="1">
-      <c r="A38" s="29">
-        <v>17365917</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="C38" s="29">
-        <v>9</v>
-      </c>
-      <c r="D38" s="29">
-        <v>8</v>
-      </c>
-      <c r="E38" s="29">
-        <v>61</v>
-      </c>
-      <c r="F38" s="29">
-        <v>10.17</v>
-      </c>
-      <c r="G38" s="29">
-        <v>164.86</v>
-      </c>
-      <c r="H38" s="29">
-        <v>18</v>
-      </c>
-      <c r="I38" s="29">
-        <v>2</v>
-      </c>
-      <c r="J38" s="29">
-        <v>10.76</v>
-      </c>
-      <c r="K38" s="29">
-        <v>4</v>
-      </c>
-      <c r="L38" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="M38" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="N38" s="32">
-        <v>2000000</v>
-      </c>
-      <c r="O38" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="P38" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q38" s="28" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" ht="40.200000000000003" thickBot="1">
-      <c r="A39" s="29">
-        <v>4779842</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="C39" s="29">
-        <v>154</v>
-      </c>
-      <c r="D39" s="29">
-        <v>131</v>
-      </c>
-      <c r="E39" s="29">
-        <v>2294</v>
-      </c>
-      <c r="F39" s="29">
-        <v>22.71</v>
-      </c>
-      <c r="G39" s="29">
-        <v>183.08</v>
-      </c>
-      <c r="H39" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="I39" s="29">
-        <v>59</v>
-      </c>
-      <c r="J39" s="29">
-        <v>10.5</v>
-      </c>
-      <c r="K39" s="29">
-        <v>46</v>
-      </c>
-      <c r="L39" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="M39" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="N39" s="32">
-        <v>20000000</v>
-      </c>
-      <c r="O39" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="P39" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q39" s="28" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" ht="40.200000000000003" thickBot="1">
-      <c r="A40" s="29">
-        <v>51819205</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>209</v>
-      </c>
+    <row r="37" spans="1:27" ht="13.8" thickBot="1">
+      <c r="A37" s="29"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="35"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+    </row>
+    <row r="38" spans="1:27" ht="13.8" thickBot="1">
+      <c r="A38" s="29"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="32"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+    </row>
+    <row r="39" spans="1:27" ht="13.8" thickBot="1">
+      <c r="A39" s="29"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="31"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+    </row>
+    <row r="40" spans="1:27" ht="13.8" thickBot="1">
+      <c r="A40" s="29"/>
+      <c r="B40" s="28"/>
       <c r="C40" s="28"/>
       <c r="D40" s="28"/>
       <c r="E40" s="28"/>
@@ -11706,133 +11597,51 @@
       <c r="H40" s="28"/>
       <c r="I40" s="28"/>
       <c r="J40" s="28"/>
-      <c r="K40" s="29">
-        <v>0</v>
-      </c>
-      <c r="L40" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="M40" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="N40" s="32">
-        <v>2000000</v>
-      </c>
-      <c r="O40" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="P40" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q40" s="28" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" ht="40.200000000000003" thickBot="1">
-      <c r="A41" s="29">
-        <v>24512366</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="29">
-        <v>47</v>
-      </c>
-      <c r="D41" s="29">
-        <v>38</v>
-      </c>
-      <c r="E41" s="29">
-        <v>439</v>
-      </c>
-      <c r="F41" s="29">
-        <v>15.14</v>
-      </c>
-      <c r="G41" s="29">
-        <v>181.4</v>
-      </c>
-      <c r="H41" s="29">
-        <v>51</v>
-      </c>
-      <c r="I41" s="29">
-        <v>25</v>
-      </c>
-      <c r="J41" s="29">
-        <v>12.77</v>
-      </c>
-      <c r="K41" s="29">
-        <v>16</v>
-      </c>
-      <c r="L41" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="M41" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="N41" s="29">
-        <v>0</v>
-      </c>
-      <c r="O41" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="P41" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q41" s="28" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" ht="27" thickBot="1">
-      <c r="A42" s="29">
-        <v>22819671</v>
-      </c>
-      <c r="B42" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="C42" s="29">
-        <v>51</v>
-      </c>
-      <c r="D42" s="29">
-        <v>37</v>
-      </c>
-      <c r="E42" s="29">
-        <v>264</v>
-      </c>
-      <c r="F42" s="29">
-        <v>9.7799999999999994</v>
-      </c>
-      <c r="G42" s="29">
-        <v>96.7</v>
-      </c>
-      <c r="H42" s="29">
-        <v>35</v>
-      </c>
-      <c r="I42" s="29">
-        <v>58</v>
-      </c>
-      <c r="J42" s="29">
-        <v>6.9</v>
-      </c>
-      <c r="K42" s="29">
-        <v>14</v>
-      </c>
-      <c r="L42" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="M42" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="N42" s="32">
-        <v>5000000</v>
-      </c>
-      <c r="O42" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="P42" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q42" s="28" t="s">
-        <v>42</v>
-      </c>
+      <c r="K40" s="29"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+    </row>
+    <row r="41" spans="1:27" ht="13.8" thickBot="1">
+      <c r="A41" s="29"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="33"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="28"/>
+      <c r="P41" s="28"/>
+      <c r="Q41" s="28"/>
+    </row>
+    <row r="42" spans="1:27" ht="13.8" thickBot="1">
+      <c r="A42" s="29"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="34"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
       <c r="R42" s="28"/>
       <c r="S42" s="28"/>
       <c r="T42" s="28"/>
@@ -11844,58 +11653,24 @@
       <c r="Z42" s="28"/>
       <c r="AA42" s="28"/>
     </row>
-    <row r="43" spans="1:27" ht="40.200000000000003" thickBot="1">
-      <c r="A43" s="29">
-        <v>29988182</v>
-      </c>
-      <c r="B43" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C43" s="29">
-        <v>46</v>
-      </c>
-      <c r="D43" s="29">
-        <v>36</v>
-      </c>
-      <c r="E43" s="29">
-        <v>463</v>
-      </c>
-      <c r="F43" s="29">
-        <v>15.43</v>
-      </c>
-      <c r="G43" s="29">
-        <v>159.11000000000001</v>
-      </c>
-      <c r="H43" s="29">
-        <v>41</v>
-      </c>
-      <c r="I43" s="29">
-        <v>13</v>
-      </c>
-      <c r="J43" s="29">
-        <v>10.68</v>
-      </c>
-      <c r="K43" s="29">
-        <v>26</v>
-      </c>
-      <c r="L43" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="M43" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="N43" s="32">
-        <v>10000000</v>
-      </c>
-      <c r="O43" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="P43" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q43" s="28" t="s">
-        <v>42</v>
-      </c>
+    <row r="43" spans="1:27" ht="13.8" thickBot="1">
+      <c r="A43" s="29"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="35"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
       <c r="R43" s="28"/>
       <c r="S43" s="28"/>
       <c r="T43" s="28"/>
@@ -11907,58 +11682,24 @@
       <c r="Z43" s="28"/>
       <c r="AA43" s="28"/>
     </row>
-    <row r="44" spans="1:27" ht="40.200000000000003" thickBot="1">
-      <c r="A44" s="29">
-        <v>10984519</v>
-      </c>
-      <c r="B44" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C44" s="29">
-        <v>187</v>
-      </c>
-      <c r="D44" s="29">
-        <v>152</v>
-      </c>
-      <c r="E44" s="29">
-        <v>3072</v>
-      </c>
-      <c r="F44" s="29">
-        <v>29.26</v>
-      </c>
-      <c r="G44" s="29">
-        <v>213.63</v>
-      </c>
-      <c r="H44" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="I44" s="29">
-        <v>105</v>
-      </c>
-      <c r="J44" s="29">
-        <v>9.0500000000000007</v>
-      </c>
-      <c r="K44" s="29">
-        <v>127</v>
-      </c>
-      <c r="L44" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="M44" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="N44" s="32">
-        <v>20000000</v>
-      </c>
-      <c r="O44" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="P44" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q44" s="28" t="s">
-        <v>204</v>
-      </c>
+    <row r="44" spans="1:27" ht="13.8" thickBot="1">
+      <c r="A44" s="29"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="29"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="31"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="28"/>
+      <c r="P44" s="28"/>
+      <c r="Q44" s="28"/>
       <c r="R44" s="28"/>
       <c r="S44" s="28"/>
       <c r="T44" s="28"/>
@@ -11975,52 +11716,43 @@
     <sortCondition ref="B1:B44"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="L4" r:id="rId1" display="https://cricheroes.com/player-profile/12060387/abhishek-sarkar/stats" xr:uid="{33F11253-B722-4D79-BF05-88461CC0ED8B}"/>
-    <hyperlink ref="L5" r:id="rId2" display="https://cricheroes.com/player-profile/10984703/aman-jaiswal/stats" xr:uid="{98EDD322-B719-4A90-97B7-7D63B2C69E7D}"/>
-    <hyperlink ref="L6" r:id="rId3" display="https://cricheroes.com/player-profile/34507530/ananya-roy/stats" xr:uid="{382A87D5-E999-430E-A6CE-1CD8AB505660}"/>
-    <hyperlink ref="L7" r:id="rId4" display="https://cricheroes.com/player-profile/42627107/anirban-guha/stats" xr:uid="{99AF0761-8D73-4F0F-A679-532AB6F90864}"/>
-    <hyperlink ref="L8" r:id="rId5" display="https://cricheroes.com/player-profile/33918878/anirban-paul/stats" xr:uid="{9FA0AEEC-C784-46A5-B576-714F018D4700}"/>
-    <hyperlink ref="L9" r:id="rId6" display="https://cricheroes.com/player-profile/11077697/ankit-jaiswal/stats" xr:uid="{8AF4DFD8-2240-4819-AE39-0623BA489BD2}"/>
-    <hyperlink ref="L10" r:id="rId7" display="https://cricheroes.com/player-profile/43016896/arijit/stats" xr:uid="{E38C92B8-606A-4241-A43F-7EE4629D4427}"/>
-    <hyperlink ref="L11" r:id="rId8" display="https://cricheroes.com/player-profile/19685723/arijit-roy/stats" xr:uid="{C90E0D7C-857B-471D-9ED4-E2246D6887BA}"/>
-    <hyperlink ref="L12" r:id="rId9" display="https://cricheroes.com/player-profile/44521368/avi-sengupta/stats" xr:uid="{07984E5E-6947-4CAD-BB24-3986A61F0D1D}"/>
-    <hyperlink ref="L2" r:id="rId10" display="https://cricheroes.com/player-profile/40256787/avijit-pal-cricket-bhojerhat/stats" xr:uid="{468F6F59-1967-4130-9279-20E7BB2C8D68}"/>
-    <hyperlink ref="L13" r:id="rId11" display="https://cricheroes.com/player-profile/2320856/balaram-shil/stats" xr:uid="{E98AE458-09D4-4FAA-B683-05D89B3D18C4}"/>
-    <hyperlink ref="L14" r:id="rId12" display="https://cricheroes.com/player-profile/37888165/bijon-mondal/stats" xr:uid="{4CBE1E11-4E4C-4D05-B73C-67FF6C97164E}"/>
-    <hyperlink ref="L15" r:id="rId13" display="https://cricheroes.com/player-profile/12060554/bony/stats" xr:uid="{717253EB-DE4B-4DB7-B8EF-CB56F7E69D84}"/>
-    <hyperlink ref="L16" r:id="rId14" display="https://cricheroes.com/player-profile/3371745/debashish-roy/stats" xr:uid="{287BC7C9-928A-48B2-80A0-0C3C5584DD74}"/>
-    <hyperlink ref="L17" r:id="rId15" display="https://cricheroes.com/player-profile/38392651/dhritiman-dey/stats" xr:uid="{B258818B-4812-4473-AF34-26FA6AF5BCBB}"/>
-    <hyperlink ref="L18" r:id="rId16" display="https://cricheroes.com/player-profile/23646088/dragleeoo/stats" xr:uid="{047CE59E-1215-499E-A757-28D66CCC477F}"/>
-    <hyperlink ref="L19" r:id="rId17" display="https://cricheroes.com/player-profile/21857884/harshit/stats" xr:uid="{FA14DCE2-0A0E-4495-B163-D6650B0E0EFA}"/>
-    <hyperlink ref="L20" r:id="rId18" display="https://cricheroes.com/player-profile/11374748/harshit-jaiswal/stats" xr:uid="{E375F391-ECA9-4983-B718-8C5141D8F05A}"/>
-    <hyperlink ref="L21" r:id="rId19" display="https://cricheroes.com/player-profile/49414345/indronil-das/stats" xr:uid="{5C36EF4F-AEFD-4120-8C7E-56B381A7FD15}"/>
-    <hyperlink ref="L22" r:id="rId20" display="https://cricheroes.com/player-profile/48762345/jewel-johnson/stats" xr:uid="{C9E993CC-9F06-48F2-9C85-5960CD914CEC}"/>
-    <hyperlink ref="L23" r:id="rId21" display="https://cricheroes.com/player-profile/4258050/jit/stats" xr:uid="{E8B9F009-A906-4387-9591-F45EF85AE3FF}"/>
-    <hyperlink ref="L24" r:id="rId22" display="https://cricheroes.com/player-profile/12060748/joy-mitra/stats" xr:uid="{5BF354A2-F2E4-47BF-9693-445767A5A188}"/>
-    <hyperlink ref="L25" r:id="rId23" display="https://cricheroes.com/player-profile/31751306/koushik/stats" xr:uid="{3B6834E0-28DA-4AFF-B4C8-CE61582559BE}"/>
-    <hyperlink ref="L26" r:id="rId24" display="https://cricheroes.com/player-profile/30299329/kuntal-das/stats" xr:uid="{C43EFBBF-2BE8-4315-9479-B03BAB79114E}"/>
-    <hyperlink ref="L27" r:id="rId25" display="https://cricheroes.com/player-profile/42598564/prince/stats" xr:uid="{13D31FD6-7B70-4EAF-8563-35361EC22E54}"/>
-    <hyperlink ref="L28" r:id="rId26" display="https://cricheroes.com/player-profile/45002297/rahul/stats" xr:uid="{A1821CD8-6673-456F-9B6A-5F45008DB5F8}"/>
-    <hyperlink ref="L29" r:id="rId27" display="https://cricheroes.com/player-profile/36055152/rohit-ghosh/stats" xr:uid="{A9A18EB1-1F36-47E4-8B92-0941B5BC66BC}"/>
-    <hyperlink ref="L31" r:id="rId28" display="https://cricheroes.com/player-profile/44011252/salman/stats" xr:uid="{EC4319D7-4950-48F1-945C-1878B0C42D00}"/>
-    <hyperlink ref="L32" r:id="rId29" display="https://cricheroes.com/player-profile/8026613/samir/stats" xr:uid="{E62954BC-6995-4776-8617-6C8BCF84CBD8}"/>
-    <hyperlink ref="L33" r:id="rId30" display="https://cricheroes.com/player-profile/46477829/sankar-ghosh/stats" xr:uid="{EEC8E057-4A6C-4DA5-B3B5-7E7716E2AAA6}"/>
-    <hyperlink ref="L34" r:id="rId31" display="https://cricheroes.com/player-profile/7183132/sarajit/stats" xr:uid="{E9DE11D4-71D5-4A5A-ABC3-0985071F0C3B}"/>
-    <hyperlink ref="L35" r:id="rId32" display="https://cricheroes.com/player-profile/10967531/sawon-bhattacharya/stats" xr:uid="{3A9904A8-CA4B-421D-A149-EFF32CC3AF36}"/>
-    <hyperlink ref="L30" r:id="rId33" display="https://cricheroes.com/player-profile/47133527/sen/stats" xr:uid="{698FC933-AE13-4601-A3A0-A27BBD95E728}"/>
-    <hyperlink ref="L36" r:id="rId34" display="https://cricheroes.com/player-profile/11616298/shantanu-chakraborty/stats" xr:uid="{F9A71DC0-2FB3-421E-8A57-9D9B8197FFAB}"/>
-    <hyperlink ref="L37" r:id="rId35" display="https://cricheroes.com/player-profile/33758093/shubham-kumar/stats" xr:uid="{37B417B5-4DD1-48D9-9F76-38C967F9E9B8}"/>
-    <hyperlink ref="L39" r:id="rId36" display="https://cricheroes.com/player-profile/4779842/subhasish-das/stats" xr:uid="{426FE9A2-A94A-4E7C-A0F6-22CF95A87BAC}"/>
-    <hyperlink ref="L41" r:id="rId37" display="https://cricheroes.com/player-profile/24512366/swapneel-chakraborty/stats" xr:uid="{3215937B-0246-4C96-939A-4E6B178C020A}"/>
-    <hyperlink ref="L42" r:id="rId38" display="https://cricheroes.com/player-profile/22819671/tiyas-chatterjee/stats" xr:uid="{3B77FFC1-CF8C-4569-B4DA-D0C208855E75}"/>
-    <hyperlink ref="L43" r:id="rId39" display="https://cricheroes.com/player-profile/29988182/tushal-shaw/stats" xr:uid="{8F6BE916-E902-43B6-9AC8-FBA4B48CD0B5}"/>
-    <hyperlink ref="L44" r:id="rId40" display="https://cricheroes.com/player-profile/10984519/ujjawal-jha/stats" xr:uid="{36C6D784-5C86-4BA7-83BF-A4C75AAE3181}"/>
-    <hyperlink ref="L3" r:id="rId41" display="https://cricheroes.com/player-profile/3336901/abhik-ganguly/stats" xr:uid="{EAEA2910-BAB2-4BAE-931B-9FA00ACB9F0D}"/>
-    <hyperlink ref="L38" r:id="rId42" display="https://cricheroes.com/player-profile/17365917/soumyojit/stats" xr:uid="{3878A601-4E9F-431E-91AA-99C5F34D7DC1}"/>
-    <hyperlink ref="L40" r:id="rId43" display="https://cricheroes.com/player-profile/51819205/sunil-kumar-shaw/stats" xr:uid="{0438B9FB-686C-4589-AE98-12F790624A32}"/>
+    <hyperlink ref="L2" r:id="rId1" display="https://cricheroes.com/player-profile/40256787/avijit-pal-cricket-bhojerhat/stats" xr:uid="{4CE2426B-99B3-489C-A0D2-54AA9372F686}"/>
+    <hyperlink ref="L3" r:id="rId2" display="https://cricheroes.com/player-profile/3336901/abhik-ganguly/stats" xr:uid="{FEEA0A2E-2FB8-4840-97C6-BCEA9AEF8A85}"/>
+    <hyperlink ref="L4" r:id="rId3" display="https://cricheroes.com/player-profile/12060387/abhishek-sarkar/stats" xr:uid="{CFE11FEE-F0FA-416C-A79B-9AB0A321C0AD}"/>
+    <hyperlink ref="L5" r:id="rId4" display="https://cricheroes.com/player-profile/10984703/aman-jaiswal/stats" xr:uid="{1E1FF177-088B-4ACF-BD76-28027A9A7C43}"/>
+    <hyperlink ref="L6" r:id="rId5" display="https://cricheroes.com/player-profile/34507530/ananya-roy/stats" xr:uid="{1350F4E2-0BD2-424F-B49E-3F2C9F7C52BF}"/>
+    <hyperlink ref="L7" r:id="rId6" display="https://cricheroes.com/player-profile/42627107/anirban-guha/stats" xr:uid="{3ED0DB73-9A20-4712-A32E-114EE696C6DA}"/>
+    <hyperlink ref="L8" r:id="rId7" display="https://cricheroes.com/player-profile/33918878/anirban-paul/stats" xr:uid="{91543FBF-696F-435A-9AEF-4AB895453828}"/>
+    <hyperlink ref="L9" r:id="rId8" display="https://cricheroes.com/player-profile/43016896/arijit/stats" xr:uid="{DF639C65-4AF7-4D74-95AB-87DD8C65D940}"/>
+    <hyperlink ref="L10" r:id="rId9" display="https://cricheroes.com/player-profile/19685723/arijit-roy/stats" xr:uid="{78924A43-0288-4A0E-9778-EB4F5C3EE02A}"/>
+    <hyperlink ref="L11" r:id="rId10" display="https://cricheroes.com/player-profile/44521368/avi-sengupta/stats" xr:uid="{DB8FFFF9-B77E-4AA8-8BD1-E4A511774CC3}"/>
+    <hyperlink ref="L12" r:id="rId11" display="https://cricheroes.com/player-profile/2320856/balaram-shil/stats" xr:uid="{A93CE85D-9CFC-4083-B83D-16865DA2315B}"/>
+    <hyperlink ref="L13" r:id="rId12" display="https://cricheroes.com/player-profile/37888165/bijon-mondal/stats" xr:uid="{EAF510C1-2213-4CE5-A75D-C586CBA54481}"/>
+    <hyperlink ref="L14" r:id="rId13" display="https://cricheroes.com/player-profile/12060554/bony/stats" xr:uid="{7E1E3A05-E120-4FB4-AC69-16446B049FD5}"/>
+    <hyperlink ref="L15" r:id="rId14" display="https://cricheroes.com/player-profile/3371745/debashish-roy/stats" xr:uid="{9AD038B9-02B0-4FAD-89EF-77964B0A1C2E}"/>
+    <hyperlink ref="L16" r:id="rId15" display="https://cricheroes.com/player-profile/38392651/dhritiman-dey/stats" xr:uid="{33BEA35D-8407-4AFB-8C1A-20D414DA0790}"/>
+    <hyperlink ref="L17" r:id="rId16" display="https://cricheroes.com/player-profile/11374748/harshit-jaiswal/stats" xr:uid="{2064DD22-EE26-4389-B504-4AE152F085AC}"/>
+    <hyperlink ref="L18" r:id="rId17" display="https://cricheroes.com/player-profile/49414345/indronil-das/stats" xr:uid="{949AD59D-C330-49A0-ABB3-E1F59682B525}"/>
+    <hyperlink ref="L19" r:id="rId18" display="https://cricheroes.com/player-profile/48762345/jewel-johnson/stats" xr:uid="{A8590DE5-BBF0-49E5-8E37-40B0DBD15406}"/>
+    <hyperlink ref="L20" r:id="rId19" display="https://cricheroes.com/player-profile/4258050/jit/stats" xr:uid="{1B33BBB0-B9EF-4D8D-B78B-A2BC2B99138A}"/>
+    <hyperlink ref="L21" r:id="rId20" display="https://cricheroes.com/player-profile/12060748/joy-mitra/stats" xr:uid="{DDC0A115-B420-4EC2-AE24-BB992FE318E7}"/>
+    <hyperlink ref="L22" r:id="rId21" display="https://cricheroes.com/player-profile/31751306/koushik/stats" xr:uid="{1F26B55E-1829-4F07-89AD-FD28FCE75419}"/>
+    <hyperlink ref="L23" r:id="rId22" display="https://cricheroes.com/player-profile/42598564/prince/stats" xr:uid="{DAC29F8B-E449-452B-B272-F30F9C4084F1}"/>
+    <hyperlink ref="L24" r:id="rId23" display="https://cricheroes.com/player-profile/45002297/rahul/stats" xr:uid="{48E4846E-4E59-4012-B61F-DF817D5E1D07}"/>
+    <hyperlink ref="L25" r:id="rId24" display="https://cricheroes.com/player-profile/36055152/rohit-ghosh/stats" xr:uid="{984199BB-9B16-457A-B1F1-3EA77E0B369B}"/>
+    <hyperlink ref="L26" r:id="rId25" display="https://cricheroes.com/player-profile/47133527/sen/stats" xr:uid="{925CE4FD-FA36-4897-979B-188548036FF8}"/>
+    <hyperlink ref="L27" r:id="rId26" display="https://cricheroes.com/player-profile/44011252/salman/stats" xr:uid="{2C1C8D67-96C0-4E22-B53E-CFE46623A209}"/>
+    <hyperlink ref="L28" r:id="rId27" display="https://cricheroes.com/player-profile/8026613/samir/stats" xr:uid="{12551EA6-1E3A-4DD7-BF39-8C9C8C8B2ECD}"/>
+    <hyperlink ref="L29" r:id="rId28" display="https://cricheroes.com/player-profile/7183132/sarajit/stats" xr:uid="{2732222C-43A4-4D65-A624-960274840938}"/>
+    <hyperlink ref="L30" r:id="rId29" display="https://cricheroes.com/player-profile/17365917/soumyojit/stats" xr:uid="{8D4E3AAE-C87C-4D7B-AF55-E1DC3A010F47}"/>
+    <hyperlink ref="L31" r:id="rId30" display="https://cricheroes.com/player-profile/4779842/subhasish-das/stats" xr:uid="{33D47004-31DD-4455-A30C-9F2CEDAD7A19}"/>
+    <hyperlink ref="L32" r:id="rId31" display="https://cricheroes.com/player-profile/51819205/sunil-kumar-shaw/stats" xr:uid="{7BB3AC1B-D7AA-4842-9A60-E9E39BFA15C8}"/>
+    <hyperlink ref="L34" r:id="rId32" display="https://cricheroes.com/player-profile/22819671/tiyas-chatterjee/stats" xr:uid="{6E5837D0-C690-49A9-BC19-C0EFE2698A72}"/>
+    <hyperlink ref="L35" r:id="rId33" display="https://cricheroes.com/player-profile/29988182/tushal-shaw/stats" xr:uid="{573BE1A5-2684-404C-BD4B-0AB0A802AEE3}"/>
+    <hyperlink ref="L36" r:id="rId34" display="https://cricheroes.com/player-profile/10984519/ujjawal-jha/stats" xr:uid="{6E18D6B4-756C-40D0-9585-45A1CC80C79E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId44"/>
+  <pageSetup orientation="portrait" r:id="rId35"/>
 </worksheet>
 </file>
 
@@ -12055,7 +11787,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="13.2">
       <c r="A2" s="25" t="s">
         <v>195</v>
       </c>
@@ -12072,7 +11804,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="13.2">
       <c r="A3" s="19">
         <v>1</v>
       </c>
@@ -12089,7 +11821,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" ht="13.2">
       <c r="A4" s="19">
         <v>2</v>
       </c>
@@ -12106,7 +11838,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="13.2">
       <c r="A5" s="19">
         <v>3</v>
       </c>
@@ -12123,7 +11855,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" ht="13.2">
       <c r="A6" s="19">
         <v>4</v>
       </c>
@@ -12140,7 +11872,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="13.2">
       <c r="A7" s="19">
         <v>5</v>
       </c>
@@ -12157,7 +11889,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="13.2">
       <c r="A8" s="19">
         <v>6</v>
       </c>
@@ -12174,7 +11906,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" ht="13.2">
       <c r="A9" s="19">
         <v>7</v>
       </c>
@@ -12191,7 +11923,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" ht="13.2">
       <c r="A10" s="19">
         <v>8</v>
       </c>
@@ -12205,7 +11937,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" ht="13.2">
       <c r="A11" s="19">
         <v>9</v>
       </c>
@@ -12219,7 +11951,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" ht="13.2">
       <c r="A12" s="19">
         <v>10</v>
       </c>
@@ -12233,7 +11965,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="13.2">
       <c r="A13" s="19">
         <v>11</v>
       </c>
@@ -12244,7 +11976,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" ht="13.2">
       <c r="A14" s="19">
         <v>12</v>
       </c>

--- a/Auction Tracker v3 latest.xlsx
+++ b/Auction Tracker v3 latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\auction-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDDF0EC-7530-4F70-B78C-73736ACBE268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCFF470-4BE1-47E1-9A9D-FAD2F5F71360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form responses 1" sheetId="1" r:id="rId1"/>

--- a/Auction Tracker v3 latest.xlsx
+++ b/Auction Tracker v3 latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\auction-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCFF470-4BE1-47E1-9A9D-FAD2F5F71360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E20823-5098-4532-A1AD-33E1A5432AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="214">
   <si>
     <t>Timestamp</t>
   </si>
@@ -674,6 +674,12 @@
   </si>
   <si>
     <t>Susovan Roy</t>
+  </si>
+  <si>
+    <t>Faisal Akhter</t>
+  </si>
+  <si>
+    <t>33*</t>
   </si>
 </sst>
 </file>
@@ -9749,7 +9755,7 @@
       <c r="L2" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="28" t="s">
         <v>45</v>
       </c>
       <c r="N2" s="32">
@@ -9802,7 +9808,7 @@
       <c r="L3" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M3" s="31" t="s">
+      <c r="M3" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N3" s="32">
@@ -9855,7 +9861,7 @@
       <c r="L4" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M4" s="31" t="s">
+      <c r="M4" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32">
@@ -9908,7 +9914,7 @@
       <c r="L5" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M5" s="33" t="s">
+      <c r="M5" s="28" t="s">
         <v>50</v>
       </c>
       <c r="N5" s="32">
@@ -9961,7 +9967,7 @@
       <c r="L6" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M6" s="34" t="s">
+      <c r="M6" s="28" t="s">
         <v>25</v>
       </c>
       <c r="N6" s="32">
@@ -10014,7 +10020,7 @@
       <c r="L7" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M7" s="34" t="s">
+      <c r="M7" s="28" t="s">
         <v>25</v>
       </c>
       <c r="N7" s="32">
@@ -10067,7 +10073,7 @@
       <c r="L8" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M8" s="35" t="s">
+      <c r="M8" s="28" t="s">
         <v>50</v>
       </c>
       <c r="N8" s="32">
@@ -10085,42 +10091,42 @@
     </row>
     <row r="9" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A9" s="29">
-        <v>43016896</v>
+        <v>11077697</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C9" s="29">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D9" s="29">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" s="29">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="F9" s="29">
-        <v>14.35</v>
+        <v>18.78</v>
       </c>
       <c r="G9" s="29">
-        <v>162.66999999999999</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>163</v>
+        <v>169</v>
+      </c>
+      <c r="H9" s="29">
+        <v>60</v>
       </c>
       <c r="I9" s="29">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J9" s="29">
-        <v>7.92</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="K9" s="29">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M9" s="35" t="s">
+      <c r="M9" s="28" t="s">
         <v>50</v>
       </c>
       <c r="N9" s="32">
@@ -10132,52 +10138,52 @@
       <c r="P9" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q9" s="38" t="s">
-        <v>204</v>
+      <c r="Q9" s="28" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A10" s="29">
-        <v>19685723</v>
+        <v>43016896</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="C10" s="29">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="D10" s="29">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="E10" s="29">
-        <v>589</v>
+        <v>488</v>
       </c>
       <c r="F10" s="29">
-        <v>10.91</v>
+        <v>14.35</v>
       </c>
       <c r="G10" s="29">
-        <v>130.88999999999999</v>
-      </c>
-      <c r="H10" s="29">
-        <v>37</v>
+        <v>162.66999999999999</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>163</v>
       </c>
       <c r="I10" s="29">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="J10" s="29">
-        <v>12.07</v>
+        <v>7.92</v>
       </c>
       <c r="K10" s="29">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L10" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M10" s="34" t="s">
-        <v>25</v>
+      <c r="M10" s="28" t="s">
+        <v>50</v>
       </c>
       <c r="N10" s="32">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="O10" s="28" t="s">
         <v>19</v>
@@ -10191,30 +10197,46 @@
     </row>
     <row r="11" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A11" s="29">
-        <v>44521368</v>
+        <v>19685723</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
+        <v>158</v>
+      </c>
+      <c r="C11" s="29">
+        <v>113</v>
+      </c>
+      <c r="D11" s="29">
+        <v>75</v>
+      </c>
+      <c r="E11" s="29">
+        <v>589</v>
+      </c>
+      <c r="F11" s="29">
+        <v>10.91</v>
+      </c>
+      <c r="G11" s="29">
+        <v>130.88999999999999</v>
+      </c>
+      <c r="H11" s="29">
+        <v>37</v>
+      </c>
+      <c r="I11" s="29">
+        <v>47</v>
+      </c>
+      <c r="J11" s="29">
+        <v>12.07</v>
+      </c>
       <c r="K11" s="29">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L11" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M11" s="36" t="s">
-        <v>45</v>
+      <c r="M11" s="28" t="s">
+        <v>25</v>
       </c>
       <c r="N11" s="32">
-        <v>2000000</v>
+        <v>5000000</v>
       </c>
       <c r="O11" s="28" t="s">
         <v>19</v>
@@ -10222,52 +10244,36 @@
       <c r="P11" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q11" s="28" t="s">
-        <v>205</v>
+      <c r="Q11" s="38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A12" s="29">
-        <v>2320856</v>
+        <v>44521368</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="29">
-        <v>648</v>
-      </c>
-      <c r="D12" s="29">
-        <v>433</v>
-      </c>
-      <c r="E12" s="29">
-        <v>6590</v>
-      </c>
-      <c r="F12" s="29">
-        <v>21.61</v>
-      </c>
-      <c r="G12" s="29">
-        <v>193.77</v>
-      </c>
-      <c r="H12" s="29">
-        <v>88</v>
-      </c>
-      <c r="I12" s="29">
-        <v>575</v>
-      </c>
-      <c r="J12" s="29">
-        <v>11.88</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
       <c r="K12" s="29">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="L12" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M12" s="31" t="s">
-        <v>40</v>
+      <c r="M12" s="28" t="s">
+        <v>45</v>
       </c>
       <c r="N12" s="32">
-        <v>20000000</v>
+        <v>2000000</v>
       </c>
       <c r="O12" s="28" t="s">
         <v>19</v>
@@ -10281,46 +10287,46 @@
     </row>
     <row r="13" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A13" s="29">
-        <v>37888165</v>
+        <v>2320856</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="C13" s="29">
-        <v>106</v>
+        <v>650</v>
       </c>
       <c r="D13" s="29">
-        <v>77</v>
+        <v>435</v>
       </c>
       <c r="E13" s="29">
-        <v>865</v>
+        <v>6623</v>
       </c>
       <c r="F13" s="29">
-        <v>17.3</v>
+        <v>21.57</v>
       </c>
       <c r="G13" s="29">
-        <v>190.95</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>166</v>
+        <v>193.49</v>
+      </c>
+      <c r="H13" s="29">
+        <v>88</v>
       </c>
       <c r="I13" s="29">
-        <v>39</v>
+        <v>576</v>
       </c>
       <c r="J13" s="29">
-        <v>11.7</v>
+        <v>11.86</v>
       </c>
       <c r="K13" s="29">
-        <v>61</v>
+        <v>394</v>
       </c>
       <c r="L13" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M13" s="34" t="s">
-        <v>25</v>
+      <c r="M13" s="28" t="s">
+        <v>40</v>
       </c>
       <c r="N13" s="32">
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
       <c r="O13" s="28" t="s">
         <v>19</v>
@@ -10334,46 +10340,46 @@
     </row>
     <row r="14" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A14" s="29">
-        <v>12060554</v>
+        <v>37888165</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="C14" s="29">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="D14" s="29">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E14" s="29">
-        <v>971</v>
+        <v>865</v>
       </c>
       <c r="F14" s="29">
-        <v>12.14</v>
+        <v>17.3</v>
       </c>
       <c r="G14" s="29">
-        <v>161.30000000000001</v>
-      </c>
-      <c r="H14" s="29">
-        <v>65</v>
+        <v>190.95</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>166</v>
       </c>
       <c r="I14" s="29">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J14" s="29">
-        <v>10.46</v>
+        <v>11.7</v>
       </c>
       <c r="K14" s="29">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="L14" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M14" s="35" t="s">
-        <v>50</v>
+      <c r="M14" s="28" t="s">
+        <v>25</v>
       </c>
       <c r="N14" s="32">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="O14" s="28" t="s">
         <v>19</v>
@@ -10382,51 +10388,51 @@
         <v>20</v>
       </c>
       <c r="Q14" s="28" t="s">
-        <v>42</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A15" s="29">
-        <v>3371745</v>
+        <v>12060554</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="C15" s="29">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D15" s="29">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E15" s="29">
-        <v>1711</v>
+        <v>971</v>
       </c>
       <c r="F15" s="29">
-        <v>21.12</v>
+        <v>12.14</v>
       </c>
       <c r="G15" s="29">
-        <v>131.21</v>
+        <v>161.30000000000001</v>
       </c>
       <c r="H15" s="29">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="I15" s="29">
-        <v>117</v>
+        <v>48</v>
       </c>
       <c r="J15" s="29">
-        <v>8.8800000000000008</v>
+        <v>10.46</v>
       </c>
       <c r="K15" s="29">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="L15" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M15" s="31" t="s">
-        <v>40</v>
+      <c r="M15" s="28" t="s">
+        <v>50</v>
       </c>
       <c r="N15" s="32">
-        <v>20000000</v>
+        <v>10000000</v>
       </c>
       <c r="O15" s="28" t="s">
         <v>19</v>
@@ -10435,51 +10441,51 @@
         <v>20</v>
       </c>
       <c r="Q15" s="28" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A16" s="29">
-        <v>38392651</v>
+        <v>3371745</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C16" s="29">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="D16" s="29">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="E16" s="29">
-        <v>623</v>
+        <v>1711</v>
       </c>
       <c r="F16" s="29">
-        <v>18.88</v>
+        <v>21.12</v>
       </c>
       <c r="G16" s="29">
-        <v>171.15</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>168</v>
+        <v>131.21</v>
+      </c>
+      <c r="H16" s="29">
+        <v>105</v>
       </c>
       <c r="I16" s="29">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="J16" s="29">
-        <v>10.25</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="K16" s="29">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L16" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M16" s="34" t="s">
-        <v>25</v>
+      <c r="M16" s="28" t="s">
+        <v>40</v>
       </c>
       <c r="N16" s="32">
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
       <c r="O16" s="28" t="s">
         <v>19</v>
@@ -10487,52 +10493,52 @@
       <c r="P16" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q16" s="38" t="s">
-        <v>204</v>
+      <c r="Q16" s="28" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A17" s="29">
-        <v>11374748</v>
+        <v>38392651</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="C17" s="29">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D17" s="29">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E17" s="29">
-        <v>725</v>
+        <v>623</v>
       </c>
       <c r="F17" s="29">
-        <v>30.21</v>
+        <v>18.88</v>
       </c>
       <c r="G17" s="29">
-        <v>183.54</v>
-      </c>
-      <c r="H17" s="29">
-        <v>52</v>
+        <v>171.15</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>168</v>
       </c>
       <c r="I17" s="29">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J17" s="29">
-        <v>8.98</v>
+        <v>10.25</v>
       </c>
       <c r="K17" s="29">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L17" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M17" s="31" t="s">
-        <v>40</v>
+      <c r="M17" s="28" t="s">
+        <v>25</v>
       </c>
       <c r="N17" s="32">
-        <v>20000000</v>
+        <v>5000000</v>
       </c>
       <c r="O17" s="28" t="s">
         <v>19</v>
@@ -10540,48 +10546,46 @@
       <c r="P17" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q17" s="28" t="s">
-        <v>205</v>
+      <c r="Q17" s="38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A18" s="29">
-        <v>49414345</v>
+        <v>10363516</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>97</v>
+        <v>212</v>
       </c>
       <c r="C18" s="29">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D18" s="29">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E18" s="29">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F18" s="29">
-        <v>17</v>
+        <v>10.29</v>
       </c>
       <c r="G18" s="29">
-        <v>151.79</v>
-      </c>
-      <c r="H18" s="29">
-        <v>39</v>
+        <v>118.03</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>213</v>
       </c>
       <c r="I18" s="29">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J18" s="29">
-        <v>11.33</v>
+        <v>8.24</v>
       </c>
       <c r="K18" s="29">
-        <v>2</v>
-      </c>
-      <c r="L18" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="M18" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28" t="s">
         <v>45</v>
       </c>
       <c r="N18" s="32">
@@ -10593,52 +10597,52 @@
       <c r="P18" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q18" s="38" t="s">
-        <v>204</v>
+      <c r="Q18" s="28" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A19" s="29">
-        <v>48762345</v>
+        <v>11374748</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="C19" s="29">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="D19" s="29">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E19" s="29">
-        <v>144</v>
+        <v>725</v>
       </c>
       <c r="F19" s="29">
-        <v>18</v>
+        <v>30.21</v>
       </c>
       <c r="G19" s="29">
-        <v>211.76</v>
+        <v>183.54</v>
       </c>
       <c r="H19" s="29">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="I19" s="29">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J19" s="29">
-        <v>11.6</v>
+        <v>8.98</v>
       </c>
       <c r="K19" s="29">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="L19" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M19" s="35" t="s">
-        <v>50</v>
+      <c r="M19" s="28" t="s">
+        <v>40</v>
       </c>
       <c r="N19" s="32">
-        <v>10000000</v>
+        <v>20000000</v>
       </c>
       <c r="O19" s="28" t="s">
         <v>19</v>
@@ -10646,52 +10650,52 @@
       <c r="P19" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q19" s="38" t="s">
-        <v>204</v>
+      <c r="Q19" s="28" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A20" s="29">
-        <v>4258050</v>
+        <v>49414345</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C20" s="29">
-        <v>207</v>
+        <v>9</v>
       </c>
       <c r="D20" s="29">
-        <v>175</v>
+        <v>6</v>
       </c>
       <c r="E20" s="29">
-        <v>1775</v>
+        <v>85</v>
       </c>
       <c r="F20" s="29">
-        <v>12.77</v>
+        <v>17</v>
       </c>
       <c r="G20" s="29">
-        <v>149.66</v>
-      </c>
-      <c r="H20" s="29" t="s">
-        <v>181</v>
+        <v>151.79</v>
+      </c>
+      <c r="H20" s="29">
+        <v>39</v>
       </c>
       <c r="I20" s="29">
-        <v>111</v>
+        <v>3</v>
       </c>
       <c r="J20" s="29">
-        <v>10.42</v>
+        <v>11.33</v>
       </c>
       <c r="K20" s="29">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="L20" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M20" s="35" t="s">
-        <v>50</v>
+      <c r="M20" s="28" t="s">
+        <v>45</v>
       </c>
       <c r="N20" s="32">
-        <v>10000000</v>
+        <v>2000000</v>
       </c>
       <c r="O20" s="28" t="s">
         <v>19</v>
@@ -10699,52 +10703,52 @@
       <c r="P20" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q20" s="28" t="s">
-        <v>42</v>
+      <c r="Q20" s="38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A21" s="29">
-        <v>12060748</v>
+        <v>48762345</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="C21" s="29">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="D21" s="29">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="E21" s="29">
-        <v>389</v>
+        <v>144</v>
       </c>
       <c r="F21" s="29">
-        <v>9.0500000000000007</v>
+        <v>18</v>
       </c>
       <c r="G21" s="29">
-        <v>136.01</v>
+        <v>211.76</v>
       </c>
       <c r="H21" s="29">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I21" s="29">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="J21" s="29">
-        <v>10.91</v>
+        <v>11.6</v>
       </c>
       <c r="K21" s="29">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="L21" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M21" s="34" t="s">
-        <v>25</v>
+      <c r="M21" s="28" t="s">
+        <v>50</v>
       </c>
       <c r="N21" s="32">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="O21" s="28" t="s">
         <v>19</v>
@@ -10752,44 +10756,48 @@
       <c r="P21" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q21" s="28" t="s">
-        <v>42</v>
+      <c r="Q21" s="38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A22" s="29">
-        <v>31751306</v>
+        <v>4258050</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>191</v>
+        <v>94</v>
       </c>
       <c r="C22" s="29">
-        <v>22</v>
+        <v>207</v>
       </c>
       <c r="D22" s="29">
-        <v>13</v>
+        <v>175</v>
       </c>
       <c r="E22" s="29">
-        <v>60</v>
+        <v>1775</v>
       </c>
       <c r="F22" s="29">
-        <v>7.5</v>
+        <v>12.77</v>
       </c>
       <c r="G22" s="29">
-        <v>93.75</v>
+        <v>149.66</v>
       </c>
       <c r="H22" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
+        <v>181</v>
+      </c>
+      <c r="I22" s="29">
+        <v>111</v>
+      </c>
+      <c r="J22" s="29">
+        <v>10.42</v>
+      </c>
       <c r="K22" s="29">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="L22" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M22" s="35" t="s">
+      <c r="M22" s="28" t="s">
         <v>50</v>
       </c>
       <c r="N22" s="32">
@@ -10807,46 +10815,46 @@
     </row>
     <row r="23" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A23" s="29">
-        <v>42598564</v>
+        <v>12060748</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C23" s="29">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="D23" s="29">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="E23" s="29">
-        <v>1570</v>
+        <v>389</v>
       </c>
       <c r="F23" s="29">
-        <v>19.38</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="G23" s="29">
-        <v>191.46</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>186</v>
+        <v>136.01</v>
+      </c>
+      <c r="H23" s="29">
+        <v>30</v>
       </c>
       <c r="I23" s="29">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J23" s="29">
-        <v>11.86</v>
+        <v>10.91</v>
       </c>
       <c r="K23" s="29">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="L23" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M23" s="35" t="s">
-        <v>50</v>
+      <c r="M23" s="28" t="s">
+        <v>25</v>
       </c>
       <c r="N23" s="32">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="O23" s="28" t="s">
         <v>19</v>
@@ -10854,52 +10862,48 @@
       <c r="P23" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q23" s="38" t="s">
-        <v>204</v>
+      <c r="Q23" s="28" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A24" s="29">
-        <v>45002297</v>
+        <v>31751306</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>71</v>
+        <v>191</v>
       </c>
       <c r="C24" s="29">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D24" s="29">
+        <v>13</v>
+      </c>
+      <c r="E24" s="29">
+        <v>60</v>
+      </c>
+      <c r="F24" s="29">
+        <v>7.5</v>
+      </c>
+      <c r="G24" s="29">
+        <v>93.75</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="29">
         <v>11</v>
-      </c>
-      <c r="E24" s="29">
-        <v>110</v>
-      </c>
-      <c r="F24" s="29">
-        <v>18.329999999999998</v>
-      </c>
-      <c r="G24" s="29">
-        <v>142.86000000000001</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="I24" s="29">
-        <v>13</v>
-      </c>
-      <c r="J24" s="29">
-        <v>8.73</v>
-      </c>
-      <c r="K24" s="29">
-        <v>6</v>
       </c>
       <c r="L24" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M24" s="34" t="s">
-        <v>25</v>
+      <c r="M24" s="28" t="s">
+        <v>50</v>
       </c>
       <c r="N24" s="32">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="O24" s="28" t="s">
         <v>19</v>
@@ -10913,46 +10917,46 @@
     </row>
     <row r="25" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A25" s="29">
-        <v>36055152</v>
+        <v>42598564</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="C25" s="29">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="D25" s="29">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="E25" s="29">
-        <v>411</v>
+        <v>1570</v>
       </c>
       <c r="F25" s="29">
-        <v>11.11</v>
+        <v>19.38</v>
       </c>
       <c r="G25" s="29">
-        <v>132.58000000000001</v>
+        <v>191.46</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="I25" s="29">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J25" s="29">
-        <v>12.89</v>
+        <v>11.86</v>
       </c>
       <c r="K25" s="29">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L25" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M25" s="36" t="s">
-        <v>45</v>
+      <c r="M25" s="28" t="s">
+        <v>50</v>
       </c>
       <c r="N25" s="32">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
       <c r="O25" s="28" t="s">
         <v>19</v>
@@ -10964,51 +10968,51 @@
         <v>204</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="27" thickBot="1">
+    <row r="26" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A26" s="29">
-        <v>47133527</v>
+        <v>45002297</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="C26" s="29">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D26" s="29">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E26" s="29">
-        <v>666</v>
+        <v>110</v>
       </c>
       <c r="F26" s="29">
-        <v>16.649999999999999</v>
+        <v>18.329999999999998</v>
       </c>
       <c r="G26" s="29">
-        <v>164.44</v>
-      </c>
-      <c r="H26" s="29">
-        <v>54</v>
+        <v>142.86000000000001</v>
+      </c>
+      <c r="H26" s="29" t="s">
+        <v>169</v>
       </c>
       <c r="I26" s="29">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="J26" s="29">
-        <v>10.14</v>
+        <v>8.73</v>
       </c>
       <c r="K26" s="29">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="L26" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M26" s="34" t="s">
+      <c r="M26" s="28" t="s">
         <v>25</v>
       </c>
       <c r="N26" s="32">
         <v>5000000</v>
       </c>
       <c r="O26" s="28" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="P26" s="28" t="s">
         <v>20</v>
@@ -11019,46 +11023,46 @@
     </row>
     <row r="27" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A27" s="29">
-        <v>44011252</v>
+        <v>36055152</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="C27" s="29">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D27" s="29">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E27" s="29">
-        <v>732</v>
+        <v>411</v>
       </c>
       <c r="F27" s="29">
-        <v>27.11</v>
+        <v>11.11</v>
       </c>
       <c r="G27" s="29">
-        <v>196.77</v>
+        <v>132.58000000000001</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="I27" s="29">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J27" s="29">
-        <v>11.04</v>
+        <v>12.89</v>
       </c>
       <c r="K27" s="29">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="L27" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M27" s="31" t="s">
-        <v>40</v>
+      <c r="M27" s="28" t="s">
+        <v>45</v>
       </c>
       <c r="N27" s="32">
-        <v>20000000</v>
+        <v>2000000</v>
       </c>
       <c r="O27" s="28" t="s">
         <v>19</v>
@@ -11066,55 +11070,55 @@
       <c r="P27" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q27" s="28" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="40.200000000000003" thickBot="1">
+      <c r="Q27" s="38" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="27" thickBot="1">
       <c r="A28" s="29">
-        <v>8026613</v>
+        <v>47133527</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C28" s="29">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="D28" s="29">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E28" s="29">
-        <v>86</v>
+        <v>666</v>
       </c>
       <c r="F28" s="29">
-        <v>14.33</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="G28" s="29">
-        <v>132.31</v>
+        <v>164.44</v>
       </c>
       <c r="H28" s="29">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="I28" s="29">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J28" s="29">
-        <v>18.75</v>
+        <v>10.14</v>
       </c>
       <c r="K28" s="29">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="L28" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M28" s="36" t="s">
-        <v>45</v>
+      <c r="M28" s="28" t="s">
+        <v>25</v>
       </c>
       <c r="N28" s="32">
-        <v>2000000</v>
+        <v>5000000</v>
       </c>
       <c r="O28" s="28" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="P28" s="28" t="s">
         <v>20</v>
@@ -11125,46 +11129,46 @@
     </row>
     <row r="29" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A29" s="29">
-        <v>7183132</v>
+        <v>44011252</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C29" s="29">
-        <v>261</v>
+        <v>55</v>
       </c>
       <c r="D29" s="29">
-        <v>224</v>
+        <v>37</v>
       </c>
       <c r="E29" s="29">
-        <v>4768</v>
+        <v>732</v>
       </c>
       <c r="F29" s="29">
-        <v>25.36</v>
+        <v>27.11</v>
       </c>
       <c r="G29" s="29">
-        <v>185.17</v>
+        <v>196.77</v>
       </c>
       <c r="H29" s="29" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I29" s="29">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="J29" s="29">
-        <v>8.98</v>
+        <v>11.04</v>
       </c>
       <c r="K29" s="29">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="L29" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M29" s="35" t="s">
-        <v>50</v>
+      <c r="M29" s="28" t="s">
+        <v>40</v>
       </c>
       <c r="N29" s="32">
-        <v>10000000</v>
+        <v>20000000</v>
       </c>
       <c r="O29" s="28" t="s">
         <v>19</v>
@@ -11172,48 +11176,48 @@
       <c r="P29" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q29" s="38" t="s">
-        <v>204</v>
+      <c r="Q29" s="28" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A30" s="29">
-        <v>17365917</v>
+        <v>8026613</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>210</v>
+        <v>103</v>
       </c>
       <c r="C30" s="29">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D30" s="29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E30" s="29">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F30" s="29">
-        <v>10.17</v>
+        <v>14.33</v>
       </c>
       <c r="G30" s="29">
-        <v>164.86</v>
+        <v>132.31</v>
       </c>
       <c r="H30" s="29">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="I30" s="29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="29">
-        <v>10.76</v>
+        <v>18.75</v>
       </c>
       <c r="K30" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L30" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M30" s="36" t="s">
+      <c r="M30" s="28" t="s">
         <v>45</v>
       </c>
       <c r="N30" s="32">
@@ -11231,46 +11235,46 @@
     </row>
     <row r="31" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A31" s="29">
-        <v>4779842</v>
+        <v>17365917</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="C31" s="29">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="D31" s="29">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="E31" s="29">
-        <v>2294</v>
+        <v>61</v>
       </c>
       <c r="F31" s="29">
-        <v>22.71</v>
+        <v>10.17</v>
       </c>
       <c r="G31" s="29">
-        <v>183.08</v>
-      </c>
-      <c r="H31" s="29" t="s">
-        <v>180</v>
+        <v>164.86</v>
+      </c>
+      <c r="H31" s="29">
+        <v>18</v>
       </c>
       <c r="I31" s="29">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="J31" s="29">
-        <v>10.5</v>
+        <v>10.76</v>
       </c>
       <c r="K31" s="29">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="L31" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M31" s="31" t="s">
-        <v>40</v>
+      <c r="M31" s="28" t="s">
+        <v>45</v>
       </c>
       <c r="N31" s="32">
-        <v>20000000</v>
+        <v>2000000</v>
       </c>
       <c r="O31" s="28" t="s">
         <v>19</v>
@@ -11278,36 +11282,52 @@
       <c r="P31" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q31" s="38" t="s">
-        <v>204</v>
+      <c r="Q31" s="28" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="40.200000000000003" thickBot="1">
       <c r="A32" s="29">
-        <v>51819205</v>
+        <v>4779842</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
+        <v>179</v>
+      </c>
+      <c r="C32" s="29">
+        <v>154</v>
+      </c>
+      <c r="D32" s="29">
+        <v>131</v>
+      </c>
+      <c r="E32" s="29">
+        <v>2294</v>
+      </c>
+      <c r="F32" s="29">
+        <v>22.71</v>
+      </c>
+      <c r="G32" s="29">
+        <v>183.08</v>
+      </c>
+      <c r="H32" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="I32" s="29">
+        <v>59</v>
+      </c>
+      <c r="J32" s="29">
+        <v>10.5</v>
+      </c>
       <c r="K32" s="29">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L32" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M32" s="36" t="s">
-        <v>45</v>
+      <c r="M32" s="28" t="s">
+        <v>40</v>
       </c>
       <c r="N32" s="32">
-        <v>2000000</v>
+        <v>20000000</v>
       </c>
       <c r="O32" s="28" t="s">
         <v>19</v>
@@ -11315,50 +11335,36 @@
       <c r="P32" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q32" s="28" t="s">
-        <v>42</v>
+      <c r="Q32" s="38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="40.200000000000003" thickBot="1">
       <c r="A33" s="29">
-        <v>12061243</v>
+        <v>51819205</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="C33" s="29">
-        <v>231</v>
-      </c>
-      <c r="D33" s="29">
-        <v>211</v>
-      </c>
-      <c r="E33" s="29">
-        <v>4736</v>
-      </c>
-      <c r="F33" s="29">
-        <v>28.19</v>
-      </c>
-      <c r="G33" s="29">
-        <v>217.25</v>
-      </c>
-      <c r="H33" s="29">
-        <v>94</v>
-      </c>
-      <c r="I33" s="29">
-        <v>111</v>
-      </c>
-      <c r="J33" s="29">
-        <v>10.85</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
       <c r="K33" s="29">
-        <v>119</v>
-      </c>
-      <c r="L33" s="28"/>
-      <c r="M33" s="33" t="s">
-        <v>40</v>
+        <v>0</v>
+      </c>
+      <c r="L33" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="M33" s="28" t="s">
+        <v>45</v>
       </c>
       <c r="N33" s="32">
-        <v>20000000</v>
+        <v>2000000</v>
       </c>
       <c r="O33" s="28" t="s">
         <v>19</v>
@@ -11366,111 +11372,109 @@
       <c r="P33" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q33" s="38" t="s">
+      <c r="Q33" s="28" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="40.200000000000003" thickBot="1">
+      <c r="A34" s="29">
+        <v>12061243</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="C34" s="29">
+        <v>231</v>
+      </c>
+      <c r="D34" s="29">
+        <v>211</v>
+      </c>
+      <c r="E34" s="29">
+        <v>4736</v>
+      </c>
+      <c r="F34" s="29">
+        <v>28.19</v>
+      </c>
+      <c r="G34" s="29">
+        <v>217.25</v>
+      </c>
+      <c r="H34" s="29">
+        <v>94</v>
+      </c>
+      <c r="I34" s="29">
+        <v>111</v>
+      </c>
+      <c r="J34" s="29">
+        <v>10.85</v>
+      </c>
+      <c r="K34" s="29">
+        <v>119</v>
+      </c>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="N34" s="32">
+        <v>20000000</v>
+      </c>
+      <c r="O34" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="P34" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q34" s="38" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="27" thickBot="1">
-      <c r="A34" s="29">
+    <row r="35" spans="1:27" ht="27" thickBot="1">
+      <c r="A35" s="29">
         <v>22819671</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B35" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <v>51</v>
       </c>
-      <c r="D34" s="29">
+      <c r="D35" s="29">
         <v>37</v>
       </c>
-      <c r="E34" s="29">
+      <c r="E35" s="29">
         <v>264</v>
       </c>
-      <c r="F34" s="29">
+      <c r="F35" s="29">
         <v>9.7799999999999994</v>
       </c>
-      <c r="G34" s="29">
+      <c r="G35" s="29">
         <v>96.7</v>
       </c>
-      <c r="H34" s="29">
+      <c r="H35" s="29">
         <v>35</v>
       </c>
-      <c r="I34" s="29">
+      <c r="I35" s="29">
         <v>58</v>
       </c>
-      <c r="J34" s="29">
+      <c r="J35" s="29">
         <v>6.9</v>
       </c>
-      <c r="K34" s="29">
+      <c r="K35" s="29">
         <v>14</v>
-      </c>
-      <c r="L34" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="M34" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="N34" s="32">
-        <v>5000000</v>
-      </c>
-      <c r="O34" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="P34" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q34" s="28" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="40.200000000000003" thickBot="1">
-      <c r="A35" s="29">
-        <v>29988182</v>
-      </c>
-      <c r="B35" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C35" s="29">
-        <v>46</v>
-      </c>
-      <c r="D35" s="29">
-        <v>36</v>
-      </c>
-      <c r="E35" s="29">
-        <v>463</v>
-      </c>
-      <c r="F35" s="29">
-        <v>15.43</v>
-      </c>
-      <c r="G35" s="29">
-        <v>159.11000000000001</v>
-      </c>
-      <c r="H35" s="29">
-        <v>41</v>
-      </c>
-      <c r="I35" s="29">
-        <v>13</v>
-      </c>
-      <c r="J35" s="29">
-        <v>10.68</v>
-      </c>
-      <c r="K35" s="29">
-        <v>26</v>
       </c>
       <c r="L35" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M35" s="35" t="s">
-        <v>50</v>
+      <c r="M35" s="28" t="s">
+        <v>25</v>
       </c>
       <c r="N35" s="32">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="O35" s="28" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="P35" s="28" t="s">
-        <v>20</v>
+        <v>208</v>
       </c>
       <c r="Q35" s="28" t="s">
         <v>42</v>
@@ -11478,46 +11482,46 @@
     </row>
     <row r="36" spans="1:27" ht="40.200000000000003" thickBot="1">
       <c r="A36" s="29">
-        <v>10984519</v>
+        <v>29988182</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="C36" s="29">
-        <v>187</v>
+        <v>46</v>
       </c>
       <c r="D36" s="29">
-        <v>152</v>
+        <v>36</v>
       </c>
       <c r="E36" s="29">
-        <v>3072</v>
+        <v>463</v>
       </c>
       <c r="F36" s="29">
-        <v>29.26</v>
+        <v>15.43</v>
       </c>
       <c r="G36" s="29">
-        <v>213.63</v>
-      </c>
-      <c r="H36" s="29" t="s">
-        <v>174</v>
+        <v>159.11000000000001</v>
+      </c>
+      <c r="H36" s="29">
+        <v>41</v>
       </c>
       <c r="I36" s="29">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="J36" s="29">
-        <v>9.0500000000000007</v>
+        <v>10.68</v>
       </c>
       <c r="K36" s="29">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="L36" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="M36" s="31" t="s">
-        <v>40</v>
+      <c r="M36" s="28" t="s">
+        <v>50</v>
       </c>
       <c r="N36" s="32">
-        <v>20000000</v>
+        <v>10000000</v>
       </c>
       <c r="O36" s="28" t="s">
         <v>19</v>
@@ -11525,28 +11529,62 @@
       <c r="P36" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="Q36" s="38" t="s">
+      <c r="Q36" s="28" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="40.200000000000003" thickBot="1">
+      <c r="A37" s="29">
+        <v>10984519</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="29">
+        <v>187</v>
+      </c>
+      <c r="D37" s="29">
+        <v>152</v>
+      </c>
+      <c r="E37" s="29">
+        <v>3072</v>
+      </c>
+      <c r="F37" s="29">
+        <v>29.26</v>
+      </c>
+      <c r="G37" s="29">
+        <v>213.63</v>
+      </c>
+      <c r="H37" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="I37" s="29">
+        <v>105</v>
+      </c>
+      <c r="J37" s="29">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="K37" s="29">
+        <v>127</v>
+      </c>
+      <c r="L37" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="M37" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="N37" s="32">
+        <v>20000000</v>
+      </c>
+      <c r="O37" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="P37" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q37" s="38" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="37" spans="1:27" ht="13.8" thickBot="1">
-      <c r="A37" s="29"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="35"/>
-      <c r="N37" s="32"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
     </row>
     <row r="38" spans="1:27" ht="13.8" thickBot="1">
       <c r="A38" s="29"/>
@@ -11716,40 +11754,40 @@
     <sortCondition ref="B1:B44"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="L2" r:id="rId1" display="https://cricheroes.com/player-profile/40256787/avijit-pal-cricket-bhojerhat/stats" xr:uid="{4CE2426B-99B3-489C-A0D2-54AA9372F686}"/>
-    <hyperlink ref="L3" r:id="rId2" display="https://cricheroes.com/player-profile/3336901/abhik-ganguly/stats" xr:uid="{FEEA0A2E-2FB8-4840-97C6-BCEA9AEF8A85}"/>
-    <hyperlink ref="L4" r:id="rId3" display="https://cricheroes.com/player-profile/12060387/abhishek-sarkar/stats" xr:uid="{CFE11FEE-F0FA-416C-A79B-9AB0A321C0AD}"/>
-    <hyperlink ref="L5" r:id="rId4" display="https://cricheroes.com/player-profile/10984703/aman-jaiswal/stats" xr:uid="{1E1FF177-088B-4ACF-BD76-28027A9A7C43}"/>
-    <hyperlink ref="L6" r:id="rId5" display="https://cricheroes.com/player-profile/34507530/ananya-roy/stats" xr:uid="{1350F4E2-0BD2-424F-B49E-3F2C9F7C52BF}"/>
-    <hyperlink ref="L7" r:id="rId6" display="https://cricheroes.com/player-profile/42627107/anirban-guha/stats" xr:uid="{3ED0DB73-9A20-4712-A32E-114EE696C6DA}"/>
-    <hyperlink ref="L8" r:id="rId7" display="https://cricheroes.com/player-profile/33918878/anirban-paul/stats" xr:uid="{91543FBF-696F-435A-9AEF-4AB895453828}"/>
-    <hyperlink ref="L9" r:id="rId8" display="https://cricheroes.com/player-profile/43016896/arijit/stats" xr:uid="{DF639C65-4AF7-4D74-95AB-87DD8C65D940}"/>
-    <hyperlink ref="L10" r:id="rId9" display="https://cricheroes.com/player-profile/19685723/arijit-roy/stats" xr:uid="{78924A43-0288-4A0E-9778-EB4F5C3EE02A}"/>
-    <hyperlink ref="L11" r:id="rId10" display="https://cricheroes.com/player-profile/44521368/avi-sengupta/stats" xr:uid="{DB8FFFF9-B77E-4AA8-8BD1-E4A511774CC3}"/>
-    <hyperlink ref="L12" r:id="rId11" display="https://cricheroes.com/player-profile/2320856/balaram-shil/stats" xr:uid="{A93CE85D-9CFC-4083-B83D-16865DA2315B}"/>
-    <hyperlink ref="L13" r:id="rId12" display="https://cricheroes.com/player-profile/37888165/bijon-mondal/stats" xr:uid="{EAF510C1-2213-4CE5-A75D-C586CBA54481}"/>
-    <hyperlink ref="L14" r:id="rId13" display="https://cricheroes.com/player-profile/12060554/bony/stats" xr:uid="{7E1E3A05-E120-4FB4-AC69-16446B049FD5}"/>
-    <hyperlink ref="L15" r:id="rId14" display="https://cricheroes.com/player-profile/3371745/debashish-roy/stats" xr:uid="{9AD038B9-02B0-4FAD-89EF-77964B0A1C2E}"/>
-    <hyperlink ref="L16" r:id="rId15" display="https://cricheroes.com/player-profile/38392651/dhritiman-dey/stats" xr:uid="{33BEA35D-8407-4AFB-8C1A-20D414DA0790}"/>
-    <hyperlink ref="L17" r:id="rId16" display="https://cricheroes.com/player-profile/11374748/harshit-jaiswal/stats" xr:uid="{2064DD22-EE26-4389-B504-4AE152F085AC}"/>
-    <hyperlink ref="L18" r:id="rId17" display="https://cricheroes.com/player-profile/49414345/indronil-das/stats" xr:uid="{949AD59D-C330-49A0-ABB3-E1F59682B525}"/>
-    <hyperlink ref="L19" r:id="rId18" display="https://cricheroes.com/player-profile/48762345/jewel-johnson/stats" xr:uid="{A8590DE5-BBF0-49E5-8E37-40B0DBD15406}"/>
-    <hyperlink ref="L20" r:id="rId19" display="https://cricheroes.com/player-profile/4258050/jit/stats" xr:uid="{1B33BBB0-B9EF-4D8D-B78B-A2BC2B99138A}"/>
-    <hyperlink ref="L21" r:id="rId20" display="https://cricheroes.com/player-profile/12060748/joy-mitra/stats" xr:uid="{DDC0A115-B420-4EC2-AE24-BB992FE318E7}"/>
-    <hyperlink ref="L22" r:id="rId21" display="https://cricheroes.com/player-profile/31751306/koushik/stats" xr:uid="{1F26B55E-1829-4F07-89AD-FD28FCE75419}"/>
-    <hyperlink ref="L23" r:id="rId22" display="https://cricheroes.com/player-profile/42598564/prince/stats" xr:uid="{DAC29F8B-E449-452B-B272-F30F9C4084F1}"/>
-    <hyperlink ref="L24" r:id="rId23" display="https://cricheroes.com/player-profile/45002297/rahul/stats" xr:uid="{48E4846E-4E59-4012-B61F-DF817D5E1D07}"/>
-    <hyperlink ref="L25" r:id="rId24" display="https://cricheroes.com/player-profile/36055152/rohit-ghosh/stats" xr:uid="{984199BB-9B16-457A-B1F1-3EA77E0B369B}"/>
-    <hyperlink ref="L26" r:id="rId25" display="https://cricheroes.com/player-profile/47133527/sen/stats" xr:uid="{925CE4FD-FA36-4897-979B-188548036FF8}"/>
-    <hyperlink ref="L27" r:id="rId26" display="https://cricheroes.com/player-profile/44011252/salman/stats" xr:uid="{2C1C8D67-96C0-4E22-B53E-CFE46623A209}"/>
-    <hyperlink ref="L28" r:id="rId27" display="https://cricheroes.com/player-profile/8026613/samir/stats" xr:uid="{12551EA6-1E3A-4DD7-BF39-8C9C8C8B2ECD}"/>
-    <hyperlink ref="L29" r:id="rId28" display="https://cricheroes.com/player-profile/7183132/sarajit/stats" xr:uid="{2732222C-43A4-4D65-A624-960274840938}"/>
-    <hyperlink ref="L30" r:id="rId29" display="https://cricheroes.com/player-profile/17365917/soumyojit/stats" xr:uid="{8D4E3AAE-C87C-4D7B-AF55-E1DC3A010F47}"/>
-    <hyperlink ref="L31" r:id="rId30" display="https://cricheroes.com/player-profile/4779842/subhasish-das/stats" xr:uid="{33D47004-31DD-4455-A30C-9F2CEDAD7A19}"/>
-    <hyperlink ref="L32" r:id="rId31" display="https://cricheroes.com/player-profile/51819205/sunil-kumar-shaw/stats" xr:uid="{7BB3AC1B-D7AA-4842-9A60-E9E39BFA15C8}"/>
-    <hyperlink ref="L34" r:id="rId32" display="https://cricheroes.com/player-profile/22819671/tiyas-chatterjee/stats" xr:uid="{6E5837D0-C690-49A9-BC19-C0EFE2698A72}"/>
-    <hyperlink ref="L35" r:id="rId33" display="https://cricheroes.com/player-profile/29988182/tushal-shaw/stats" xr:uid="{573BE1A5-2684-404C-BD4B-0AB0A802AEE3}"/>
-    <hyperlink ref="L36" r:id="rId34" display="https://cricheroes.com/player-profile/10984519/ujjawal-jha/stats" xr:uid="{6E18D6B4-756C-40D0-9585-45A1CC80C79E}"/>
+    <hyperlink ref="L2" r:id="rId1" display="https://cricheroes.com/player-profile/40256787/avijit-pal-cricket-bhojerhat/stats" xr:uid="{02A15B69-C85A-4EC1-B29E-655994A36F52}"/>
+    <hyperlink ref="L3" r:id="rId2" display="https://cricheroes.com/player-profile/3336901/abhik-ganguly/stats" xr:uid="{3C9EC480-51CD-4D17-9509-8A962176E7AD}"/>
+    <hyperlink ref="L4" r:id="rId3" display="https://cricheroes.com/player-profile/12060387/abhishek-sarkar/stats" xr:uid="{6D84264B-6EB5-46C2-9D5D-C287B90A8116}"/>
+    <hyperlink ref="L5" r:id="rId4" display="https://cricheroes.com/player-profile/10984703/aman-jaiswal/stats" xr:uid="{E7B0BCBB-DEB3-4237-ABE7-BFD5C5523CC6}"/>
+    <hyperlink ref="L6" r:id="rId5" display="https://cricheroes.com/player-profile/34507530/ananya-roy/stats" xr:uid="{5957DF51-29F3-4508-9E03-9B15877EFDBF}"/>
+    <hyperlink ref="L7" r:id="rId6" display="https://cricheroes.com/player-profile/42627107/anirban-guha/stats" xr:uid="{2DF4DC06-BCAC-43B6-8C82-A341BC829908}"/>
+    <hyperlink ref="L8" r:id="rId7" display="https://cricheroes.com/player-profile/33918878/anirban-paul/stats" xr:uid="{EB718BCF-8DD7-47CB-B606-45197A8C2D12}"/>
+    <hyperlink ref="L9" r:id="rId8" display="https://cricheroes.com/player-profile/11077697/ankit-jaiswal/stats" xr:uid="{42315738-8DE0-4F8D-AF48-EEF5104FE3C9}"/>
+    <hyperlink ref="L10" r:id="rId9" display="https://cricheroes.com/player-profile/43016896/arijit/stats" xr:uid="{F31CC324-263A-41CF-A016-C561FABAEEB1}"/>
+    <hyperlink ref="L11" r:id="rId10" display="https://cricheroes.com/player-profile/19685723/arijit-roy/stats" xr:uid="{B1BCC170-C8D8-42D5-99B0-DB881FFF7006}"/>
+    <hyperlink ref="L12" r:id="rId11" display="https://cricheroes.com/player-profile/44521368/avi-sengupta/stats" xr:uid="{42BCE993-8295-445D-AFB9-9BBA884695FA}"/>
+    <hyperlink ref="L13" r:id="rId12" display="https://cricheroes.com/player-profile/2320856/balaram-shil/stats" xr:uid="{127DCD86-92C0-4A82-8F3C-84348CE1F759}"/>
+    <hyperlink ref="L14" r:id="rId13" display="https://cricheroes.com/player-profile/37888165/bijon-mondal/stats" xr:uid="{E31C343C-08B0-499C-AB27-08CCDBEF9ADF}"/>
+    <hyperlink ref="L15" r:id="rId14" display="https://cricheroes.com/player-profile/12060554/bony/stats" xr:uid="{C69ECE90-A1C3-47AB-B7C2-C3D9763841DD}"/>
+    <hyperlink ref="L16" r:id="rId15" display="https://cricheroes.com/player-profile/3371745/debashish-roy/stats" xr:uid="{D3C2C40D-08E7-4F49-BEF6-1CA1D31576ED}"/>
+    <hyperlink ref="L17" r:id="rId16" display="https://cricheroes.com/player-profile/38392651/dhritiman-dey/stats" xr:uid="{DCA178D7-F6CB-49B4-8EA1-78B6AD14DDE0}"/>
+    <hyperlink ref="L19" r:id="rId17" display="https://cricheroes.com/player-profile/11374748/harshit-jaiswal/stats" xr:uid="{60E75967-3D45-4223-8134-FF45E6398569}"/>
+    <hyperlink ref="L20" r:id="rId18" display="https://cricheroes.com/player-profile/49414345/indronil-das/stats" xr:uid="{D99913DA-1974-48FE-87A6-0E88FB4BAFE4}"/>
+    <hyperlink ref="L21" r:id="rId19" display="https://cricheroes.com/player-profile/48762345/jewel-johnson/stats" xr:uid="{CC79DC7A-FA31-46C4-BCD2-A8773CF45C3A}"/>
+    <hyperlink ref="L22" r:id="rId20" display="https://cricheroes.com/player-profile/4258050/jit/stats" xr:uid="{26A9E615-D145-4337-9A77-01D7BF5ACFCE}"/>
+    <hyperlink ref="L23" r:id="rId21" display="https://cricheroes.com/player-profile/12060748/joy-mitra/stats" xr:uid="{CDB9BC9F-6A92-48C0-ABF6-FD748EC39108}"/>
+    <hyperlink ref="L24" r:id="rId22" display="https://cricheroes.com/player-profile/31751306/koushik/stats" xr:uid="{674E9417-28DF-43BC-9BD7-CA8262B8D8C7}"/>
+    <hyperlink ref="L25" r:id="rId23" display="https://cricheroes.com/player-profile/42598564/prince/stats" xr:uid="{F636E783-0829-4844-864D-D0669452FB15}"/>
+    <hyperlink ref="L26" r:id="rId24" display="https://cricheroes.com/player-profile/45002297/rahul/stats" xr:uid="{E1252678-0181-43A5-9206-2DE5A66AA0A4}"/>
+    <hyperlink ref="L27" r:id="rId25" display="https://cricheroes.com/player-profile/36055152/rohit-ghosh/stats" xr:uid="{E45173F6-F847-4DD7-84F3-7A7091E1772D}"/>
+    <hyperlink ref="L28" r:id="rId26" display="https://cricheroes.com/player-profile/47133527/sen/stats" xr:uid="{FAED70F6-C7AF-46D8-81D0-93310FA9135E}"/>
+    <hyperlink ref="L29" r:id="rId27" display="https://cricheroes.com/player-profile/44011252/salman/stats" xr:uid="{FFC7BD4F-D801-4621-A558-2C1655224B1B}"/>
+    <hyperlink ref="L30" r:id="rId28" display="https://cricheroes.com/player-profile/8026613/samir/stats" xr:uid="{DEB0ADB6-8847-4303-ADC0-057DEA99C660}"/>
+    <hyperlink ref="L31" r:id="rId29" display="https://cricheroes.com/player-profile/17365917/soumyojit/stats" xr:uid="{280D3787-42B2-4085-A92B-C559035CE438}"/>
+    <hyperlink ref="L32" r:id="rId30" display="https://cricheroes.com/player-profile/4779842/subhasish-das/stats" xr:uid="{C5C79569-FFCA-419A-A308-D2EE75626FBE}"/>
+    <hyperlink ref="L33" r:id="rId31" display="https://cricheroes.com/player-profile/51819205/sunil-kumar-shaw/stats" xr:uid="{7A968CC6-CC6C-4993-94F8-5928766DBAFE}"/>
+    <hyperlink ref="L35" r:id="rId32" display="https://cricheroes.com/player-profile/22819671/tiyas-chatterjee/stats" xr:uid="{0B6C9721-4DB9-4706-A3E0-0FF5A69B2AFB}"/>
+    <hyperlink ref="L36" r:id="rId33" display="https://cricheroes.com/player-profile/29988182/tushal-shaw/stats" xr:uid="{75551A7C-6EFF-4546-A60D-2C94B1A43CD8}"/>
+    <hyperlink ref="L37" r:id="rId34" display="https://cricheroes.com/player-profile/10984519/ujjawal-jha/stats" xr:uid="{8A81AC79-3595-472D-B8C7-B9A743A5E102}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId35"/>
